--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EFFE10-3475-4383-ADA4-DBBB02F10BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E13AF0-5B5B-40EB-B977-153893F4BBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="694">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -775,7 +775,7 @@
     <t>elc_spv_POL_001</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 1</t>
+    <t>solar electricity near Zielona Gora (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -784,1036 +784,1162 @@
     <t>elc_spv_POL_002</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 2</t>
+    <t>solar electricity near Opole (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 3</t>
+    <t>solar electricity near Wroclaw (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 4</t>
+    <t>solar electricity near Gorzow Wielkopolski (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 5</t>
+    <t>solar electricity near Pila (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 6</t>
+    <t>solar electricity near Olsztyn (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 7</t>
+    <t>solar electricity near Koszalin (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 8</t>
+    <t>solar electricity near Gdansk (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 9</t>
+    <t>solar electricity near Bialystok (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 10</t>
+    <t>solar electricity near Suwalki (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 11</t>
+    <t>solar electricity near Bialystok (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 12</t>
+    <t>solar electricity near Przemysl (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 13</t>
+    <t>solar electricity near Zamosc (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 14</t>
+    <t>solar electricity near Krakow (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 15</t>
+    <t>solar electricity near Katowice (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 16</t>
+    <t>solar electricity near Kalisz (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 17</t>
+    <t>solar electricity near Bydgoszcz (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 18</t>
+    <t>solar electricity near Warsaw (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 19</t>
+    <t>solar electricity near Radom (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 20</t>
+    <t>solar electricity near Warsaw (cluster 20)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 1</t>
+    <t>wind offshore electricity near Gdansk (cluster 1)</t>
   </si>
   <si>
     <t>elc_wof_POL_002</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 2</t>
+    <t>wind offshore electricity near Gdansk (cluster 2)</t>
   </si>
   <si>
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 3</t>
+    <t>wind offshore electricity near Gdansk (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 4</t>
+    <t>wind offshore electricity near Slupsk (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 5</t>
+    <t>wind offshore electricity near Gdansk (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 6</t>
+    <t>wind offshore electricity near Gdansk (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 7</t>
+    <t>wind offshore electricity near Koszalin (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_POL_008</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 8</t>
+    <t>wind offshore electricity near Koszalin (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 9</t>
+    <t>wind offshore electricity near Koszalin (cluster 9)</t>
   </si>
   <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 10</t>
+    <t>wind offshore electricity near Koszalin (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 1</t>
+    <t>wind onshore electricity near Warsaw (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 2</t>
+    <t>wind onshore electricity near Kielce (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 3</t>
+    <t>wind onshore electricity near Siedlce (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 4</t>
+    <t>wind onshore electricity near Zamosc (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 5</t>
+    <t>wind onshore electricity near Suwalki (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 6</t>
+    <t>wind onshore electricity near Wloclawek (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 7</t>
+    <t>wind onshore electricity near Olsztyn (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 8</t>
+    <t>wind onshore electricity near Olsztyn (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 9</t>
+    <t>wind onshore electricity near Elblag (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 10</t>
+    <t>wind onshore electricity near Koszalin (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 11</t>
+    <t>wind onshore electricity near Legnica (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 12</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 13</t>
+    <t>wind onshore electricity near Legnica (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 14</t>
+    <t>wind onshore electricity near Pila (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 15</t>
+    <t>wind onshore electricity near Krakow (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 16</t>
+    <t>wind onshore electricity near Rzeszow (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 17</t>
+    <t>wind onshore electricity near Tarnow (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 18</t>
+    <t>wind onshore electricity near Walbrzych (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 19</t>
+    <t>wind onshore electricity near Krakow (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 20</t>
+    <t>wind onshore electricity near Rybnik (cluster 20)</t>
   </si>
   <si>
     <t>~fi_comm</t>
   </si>
   <si>
-    <t>e_PL15-400_POL</t>
+    <t>e_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL17-400 (Bialystok, 26 km)</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
+    <t>e_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
+  </si>
+  <si>
+    <t>e_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/111615226-220 (Legnica, 74 km)</t>
+  </si>
+  <si>
+    <t>e_Bydgoszcz_POL</t>
   </si>
   <si>
     <t>grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
   </si>
   <si>
-    <t>lo</t>
-  </si>
-  <si>
-    <t>e_PL18-400_POL</t>
+    <t>e_Chelm_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/194903381-400 (Chelm, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Debica_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Elk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/112614319-400 (Gdansk, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/86494356-400 (Gdansk, 54 km)</t>
+  </si>
+  <si>
+    <t>e_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/293489607-400 (Katowice, 21 km)</t>
+  </si>
+  <si>
+    <t>e_GorzowWielkopolski_POL</t>
   </si>
   <si>
     <t>grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
   </si>
   <si>
-    <t>e_PL34-400_POL</t>
+    <t>e_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/170259740-220 (Elk, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Katowice_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/40946790-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>e_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>e_Kielce_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/199098050-220 (Kielce, 16 km)</t>
+  </si>
+  <si>
+    <t>e_Konin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/178838661-220 (Koszalin, 40 km)</t>
+  </si>
+  <si>
+    <t>e_Krakow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/87667718-220 (Krakow, 12 km)</t>
+  </si>
+  <si>
+    <t>e_Krosno_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
+  </si>
+  <si>
+    <t>e_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>grid node -- PL7-400 (Grudziadz, 8 km)</t>
+  </si>
+  <si>
+    <t>e_Legnica_POL</t>
   </si>
   <si>
     <t>grid node -- PL34-400 (Wroclaw, 43 km)</t>
   </si>
   <si>
-    <t>e_PL36-400_POL</t>
+    <t>e_Lomza_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>e_Lubin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>e_Mielec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/199098053-220 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>e_Olesnica_POL</t>
   </si>
   <si>
     <t>grid node -- PL36-400 (Wroclaw, 46 km)</t>
   </si>
   <si>
-    <t>e_PL46-220_POL</t>
+    <t>e_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Opole_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>e_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>e_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+  </si>
+  <si>
+    <t>e_Plock_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/658600169-400 (Plock, 4 km)</t>
+  </si>
+  <si>
+    <t>e_Police_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/165763717-220 (Szczecin, 15 km)</t>
+  </si>
+  <si>
+    <t>e_Poznan_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>e_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/88544449-220 (Lublin, 46 km)</t>
+  </si>
+  <si>
+    <t>e_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
+  </si>
+  <si>
+    <t>e_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
+  </si>
+  <si>
+    <t>e_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/183945016-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>e_Swidnica_POL</t>
   </si>
   <si>
     <t>grid node -- PL46-220 (Wroclaw, 58 km)</t>
   </si>
   <si>
-    <t>e_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- PL7-400 (Grudziadz, 8 km)</t>
-  </si>
-  <si>
-    <t>e_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
-  </si>
-  <si>
-    <t>e_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/111615226-380 (Legnica, 74 km)</t>
-  </si>
-  <si>
-    <t>e_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/112614319-400 (Gdansk, 4 km)</t>
-  </si>
-  <si>
-    <t>e_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
-    <t>e_w158232924-220_POL</t>
+    <t>e_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/39428977-400 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>e_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/191038569-220 (Tarnow, 5 km)</t>
+  </si>
+  <si>
+    <t>e_Ustka_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/255314292 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/29115701-220 (Warsaw, 9 km)</t>
+  </si>
+  <si>
+    <t>e_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
+  </si>
+  <si>
+    <t>e_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
+  </si>
+  <si>
+    <t>e_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>grid node -- way/173613665-220 (Zamosc, 3 km)</t>
+  </si>
+  <si>
+    <t>e_ZielonaGora_POL</t>
   </si>
   <si>
     <t>grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
-    <t>e_w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/165763717-220 (Szczecin, 15 km)</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
-  </si>
-  <si>
-    <t>e_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/170259740-220 (Elk, 6 km)</t>
-  </si>
-  <si>
-    <t>e_w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
-  </si>
-  <si>
-    <t>e_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
-  </si>
-  <si>
-    <t>e_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/173613665-220 (Zamosc, 3 km)</t>
-  </si>
-  <si>
-    <t>e_w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>e_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>e_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/183945016-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>e_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/191038569-220 (Tarnow, 5 km)</t>
-  </si>
-  <si>
-    <t>e_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/194903381-400 (Chelm, 4 km)</t>
-  </si>
-  <si>
-    <t>e_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
-  </si>
-  <si>
-    <t>e_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/199098050-220 (Kielce, 16 km)</t>
-  </si>
-  <si>
-    <t>e_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/199098053-220 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>e_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
-  </si>
-  <si>
-    <t>e_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
-  </si>
-  <si>
-    <t>e_w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
-  </si>
-  <si>
-    <t>e_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>e_w255314292_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>e_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/293489607-400 (Katowice, 21 km)</t>
-  </si>
-  <si>
-    <t>e_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>e_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>e_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/39428977-400 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>e_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/40946790-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>e_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
-  </si>
-  <si>
-    <t>e_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
-  </si>
-  <si>
-    <t>e_w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/658600169-400 (Plock, 4 km)</t>
-  </si>
-  <si>
-    <t>e_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/87667718-220 (Krakow, 12 km)</t>
-  </si>
-  <si>
-    <t>e_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/88544449-220 (Lublin, 46 km)</t>
-  </si>
-  <si>
-    <t>h_PL15-400_POL</t>
+    <t>h_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL17-400 (Bialystok, 26 km)</t>
+  </si>
+  <si>
+    <t>h_BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
+  </si>
+  <si>
+    <t>h_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/111615226-220 (Legnica, 74 km)</t>
+  </si>
+  <si>
+    <t>h_Bydgoszcz_POL</t>
   </si>
   <si>
     <t>heat at grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
   </si>
   <si>
-    <t>h_PL18-400_POL</t>
+    <t>h_Chelm_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/194903381-400 (Chelm, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Debica_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Elk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/303870256-400 (Elk, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Gdansk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
+  </si>
+  <si>
+    <t>h_Gliwice_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/293489607-400 (Katowice, 21 km)</t>
+  </si>
+  <si>
+    <t>h_GorzowWielkopolski_POL</t>
   </si>
   <si>
     <t>heat at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
   </si>
   <si>
-    <t>h_PL34-400_POL</t>
+    <t>h_Grajewo_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170259740-220 (Elk, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Katowice_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/40946790-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>h_KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/336990960-220 (Opole, 7 km)</t>
+  </si>
+  <si>
+    <t>h_Kielce_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/199098050-220 (Kielce, 16 km)</t>
+  </si>
+  <si>
+    <t>h_Konin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Koszalin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
+  </si>
+  <si>
+    <t>h_Krakow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/87667718-220 (Krakow, 12 km)</t>
+  </si>
+  <si>
+    <t>h_Krosno_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
+  </si>
+  <si>
+    <t>h_Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- PL7-400 (Grudziadz, 8 km)</t>
+  </si>
+  <si>
+    <t>h_Legnica_POL</t>
   </si>
   <si>
     <t>heat at grid node -- PL34-400 (Wroclaw, 43 km)</t>
   </si>
   <si>
-    <t>h_PL36-400_POL</t>
+    <t>h_Lomza_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/121656686-220 (Lomza, 31 km)</t>
+  </si>
+  <si>
+    <t>h_Lubin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/180535363-220 (Lubin, 33 km)</t>
+  </si>
+  <si>
+    <t>h_Mielec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/199098053-220 (Mielec, 19 km)</t>
+  </si>
+  <si>
+    <t>h_Olesnica_POL</t>
   </si>
   <si>
     <t>heat at grid node -- PL36-400 (Wroclaw, 46 km)</t>
   </si>
   <si>
-    <t>h_PL46-220_POL</t>
+    <t>h_Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Opole_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
+  </si>
+  <si>
+    <t>h_OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
+  </si>
+  <si>
+    <t>h_PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
+  </si>
+  <si>
+    <t>h_Plock_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/658600169-400 (Plock, 4 km)</t>
+  </si>
+  <si>
+    <t>h_Police_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
+  </si>
+  <si>
+    <t>h_Poznan_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>h_Pulawy_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/88544449-220 (Lublin, 46 km)</t>
+  </si>
+  <si>
+    <t>h_Radomsko_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
+  </si>
+  <si>
+    <t>h_Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
+  </si>
+  <si>
+    <t>h_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/183945016-220 (Katowice, 19 km)</t>
+  </si>
+  <si>
+    <t>h_Swidnica_POL</t>
   </si>
   <si>
     <t>heat at grid node -- PL46-220 (Wroclaw, 58 km)</t>
   </si>
   <si>
-    <t>h_PL7-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- PL7-400 (Grudziadz, 8 km)</t>
-  </si>
-  <si>
-    <t>h_w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
-  </si>
-  <si>
-    <t>h_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/111615226-380 (Legnica, 74 km)</t>
-  </si>
-  <si>
-    <t>h_w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
-  </si>
-  <si>
-    <t>h_w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/121656686-220 (Lomza, 31 km)</t>
-  </si>
-  <si>
-    <t>h_w158232924-220_POL</t>
+    <t>h_Szczecin_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
+  </si>
+  <si>
+    <t>h_Tarnow_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
+  </si>
+  <si>
+    <t>h_Ustka_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/255314292 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
+  </si>
+  <si>
+    <t>h_Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
+  </si>
+  <si>
+    <t>h_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
+  </si>
+  <si>
+    <t>h_Zamosc_POL</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
+  </si>
+  <si>
+    <t>h_ZielonaGora_POL</t>
   </si>
   <si>
     <t>heat at grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
-    <t>h_w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
-  </si>
-  <si>
-    <t>h_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
-  </si>
-  <si>
-    <t>h_w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170259740-220 (Elk, 6 km)</t>
-  </si>
-  <si>
-    <t>h_w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
-  </si>
-  <si>
-    <t>h_w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
-  </si>
-  <si>
-    <t>h_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
-  </si>
-  <si>
-    <t>h_w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
-  </si>
-  <si>
-    <t>h_w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/180535363-220 (Lubin, 33 km)</t>
-  </si>
-  <si>
-    <t>h_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/183945016-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>h_w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
-  </si>
-  <si>
-    <t>h_w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/194903381-400 (Chelm, 4 km)</t>
-  </si>
-  <si>
-    <t>h_w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
-  </si>
-  <si>
-    <t>h_w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/199098050-220 (Kielce, 16 km)</t>
-  </si>
-  <si>
-    <t>h_w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/199098053-220 (Mielec, 19 km)</t>
-  </si>
-  <si>
-    <t>h_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
-  </si>
-  <si>
-    <t>h_w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
-  </si>
-  <si>
-    <t>h_w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
-  </si>
-  <si>
-    <t>h_w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
-  </si>
-  <si>
-    <t>h_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255277953-400 (Opole, 10 km)</t>
-  </si>
-  <si>
-    <t>h_w255314292_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/255314292 (Slupsk, 10 km)</t>
-  </si>
-  <si>
-    <t>h_w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/293489607-400 (Katowice, 21 km)</t>
-  </si>
-  <si>
-    <t>h_w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/303870256-400 (Elk, 8 km)</t>
-  </si>
-  <si>
-    <t>h_w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/336990960-220 (Opole, 7 km)</t>
-  </si>
-  <si>
-    <t>h_w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
-  </si>
-  <si>
-    <t>h_w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/40946790-220 (Katowice, 19 km)</t>
-  </si>
-  <si>
-    <t>h_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
-  </si>
-  <si>
-    <t>h_w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
-  </si>
-  <si>
-    <t>h_w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/658600169-400 (Plock, 4 km)</t>
-  </si>
-  <si>
-    <t>h_w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/87667718-220 (Krakow, 12 km)</t>
-  </si>
-  <si>
-    <t>h_w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/88544449-220 (Lublin, 46 km)</t>
-  </si>
-  <si>
-    <t>co2_PL15-400_POL</t>
+    <t>co2_Bydgoszcz_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
   </si>
   <si>
-    <t>co2_PL18-400_POL</t>
+    <t>co2_Bialystok_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- PL17-400 (Bialystok, 26 km)</t>
+  </si>
+  <si>
+    <t>co2_GorzowWielkopolski_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL18-400 (Gorzow Wielkopolski, 15 km)</t>
   </si>
   <si>
-    <t>co2_PL34-400_POL</t>
+    <t>co2_Legnica_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL34-400 (Wroclaw, 43 km)</t>
   </si>
   <si>
-    <t>co2_PL36-400_POL</t>
+    <t>co2_Olesnica_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL36-400 (Wroclaw, 46 km)</t>
   </si>
   <si>
-    <t>co2_PL46-220_POL</t>
+    <t>co2_Swidnica_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL46-220 (Wroclaw, 58 km)</t>
   </si>
   <si>
-    <t>co2_PL7-400_POL</t>
+    <t>co2_Kwidzyn_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- PL7-400 (Grudziadz, 8 km)</t>
   </si>
   <si>
-    <t>co2_w101915790-220_POL</t>
+    <t>co2_Slupsk_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- relation/18085709-400 (Slupsk, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Olsztyn_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/101915790-220 (Olsztyn, 4 km)</t>
   </si>
   <si>
-    <t>co2_w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>co2 captured at grid node -- way/111615226-380 (Legnica, 74 km)</t>
-  </si>
-  <si>
-    <t>co2_w112614319-400_POL</t>
+    <t>co2_Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/111615226-220 (Legnica, 74 km)</t>
+  </si>
+  <si>
+    <t>co2_Gdansk_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/112614319-400 (Gdansk, 4 km)</t>
   </si>
   <si>
-    <t>co2_w121656686-220_POL</t>
+    <t>co2_Lomza_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/121656686-220 (Lomza, 31 km)</t>
   </si>
   <si>
-    <t>co2_w158232924-220_POL</t>
+    <t>co2_ZielonaGora_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/158232924-220 (Zielona Gora, 15 km)</t>
   </si>
   <si>
-    <t>co2_w165763717-220_POL</t>
+    <t>co2_Police_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/165763717-220 (Szczecin, 15 km)</t>
   </si>
   <si>
-    <t>co2_w166838338-400_POL</t>
+    <t>co2_Krosno_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/166838338-400 (Rzeszow, 40 km)</t>
   </si>
   <si>
-    <t>co2_w170259740-220_POL</t>
+    <t>co2_Grajewo_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/170259740-220 (Elk, 6 km)</t>
   </si>
   <si>
-    <t>co2_w170316833-220_POL</t>
+    <t>co2_PiotrkowTrybunalsk_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/170316833-220 (Piotrkow Trybunalski, 3 km)</t>
   </si>
   <si>
-    <t>co2_w171917072-400_POL</t>
+    <t>co2_Radomsko_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/171917072-400 (Czestochowa, 41 km)</t>
   </si>
   <si>
-    <t>co2_w173613665-220_POL</t>
+    <t>co2_Zamosc_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/173613665-220 (Zamosc, 3 km)</t>
   </si>
   <si>
-    <t>co2_w178838661-220_POL</t>
+    <t>co2_Koszalin_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/178838661-220 (Koszalin, 40 km)</t>
   </si>
   <si>
-    <t>co2_w180535363-220_POL</t>
+    <t>co2_Lubin_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/180535363-220 (Lubin, 33 km)</t>
   </si>
   <si>
-    <t>co2_w183945016-220_POL</t>
+    <t>co2_Sosnowiec_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/183945016-220 (Katowice, 19 km)</t>
   </si>
   <si>
-    <t>co2_w191038569-220_POL</t>
+    <t>co2_Tarnow_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/191038569-220 (Tarnow, 5 km)</t>
   </si>
   <si>
-    <t>co2_w194903381-400_POL</t>
+    <t>co2_Chelm_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/194903381-400 (Chelm, 4 km)</t>
   </si>
   <si>
-    <t>co2_w198635989-220_POL</t>
+    <t>co2_Debica_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/198635989-220 (Rzeszow, 6 km)</t>
   </si>
   <si>
-    <t>co2_w199098050-220_POL</t>
+    <t>co2_Kielce_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/199098050-220 (Kielce, 16 km)</t>
   </si>
   <si>
-    <t>co2_w199098053-220_POL</t>
+    <t>co2_Mielec_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/199098053-220 (Mielec, 19 km)</t>
   </si>
   <si>
-    <t>co2_w215282393-400_POL</t>
+    <t>co2_Rzeszow_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/215282393-400 (Rzeszow, 20 km)</t>
   </si>
   <si>
-    <t>co2_w216060722-220_POL</t>
+    <t>co2_Czestochowa_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/216060722-220 (Czestochowa, 4 km)</t>
   </si>
   <si>
-    <t>co2_w245964556-220_POL</t>
+    <t>co2_Wloclawek_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/245964556-220 (Wloclawek, 10 km)</t>
   </si>
   <si>
-    <t>co2_w254235846-400_POL</t>
+    <t>co2_OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/254235846-400 (Ostrowiec Swietokrzyski, 4 km)</t>
   </si>
   <si>
-    <t>co2_w255277953-400_POL</t>
+    <t>co2_Opole_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/255277953-400 (Opole, 10 km)</t>
   </si>
   <si>
-    <t>co2_w255314292_POL</t>
+    <t>co2_Konin_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/255284259-220 (Konin, 10 km)</t>
+  </si>
+  <si>
+    <t>co2_Ustka_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/255314292 (Slupsk, 10 km)</t>
   </si>
   <si>
-    <t>co2_w293489607-400_POL</t>
+    <t>co2_Warsaw_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/29115701-220 (Warsaw, 9 km)</t>
+  </si>
+  <si>
+    <t>co2_Gliwice_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/293489607-400 (Katowice, 21 km)</t>
   </si>
   <si>
-    <t>co2_w303870256-400_POL</t>
+    <t>co2_Elk_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/303870256-400 (Elk, 8 km)</t>
   </si>
   <si>
-    <t>co2_w336990960-220_POL</t>
+    <t>co2_Poznan_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/32036484-220 (Poznan, 11 km)</t>
+  </si>
+  <si>
+    <t>co2_KedzierzynKozle_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/336990960-220 (Opole, 7 km)</t>
   </si>
   <si>
-    <t>co2_w39428977-400_POL</t>
+    <t>co2_Szczecin_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/39428977-400 (Szczecin, 27 km)</t>
   </si>
   <si>
-    <t>co2_w40946790-220_POL</t>
+    <t>co2_Katowice_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/40946790-220 (Katowice, 19 km)</t>
   </si>
   <si>
-    <t>co2_w44389929-220_POL</t>
+    <t>co2_BielskoBiala_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/44389929-220 (Bielsko-Biala, 12 km)</t>
   </si>
   <si>
-    <t>co2_w46092396-400_POL</t>
+    <t>co2_Grudziadz_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/46092396-400 (Grudziadz, 6 km)</t>
   </si>
   <si>
-    <t>co2_w658600169-400_POL</t>
+    <t>co2_Plock_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/658600169-400 (Plock, 4 km)</t>
   </si>
   <si>
-    <t>co2_w87667718-220_POL</t>
+    <t>co2_Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/79033485-400 (Wroclaw, 13 km)</t>
+  </si>
+  <si>
+    <t>co2_Gdynia_POL</t>
+  </si>
+  <si>
+    <t>co2 captured at grid node -- way/86494356-400 (Gdansk, 54 km)</t>
+  </si>
+  <si>
+    <t>co2_Krakow_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/87667718-220 (Krakow, 12 km)</t>
   </si>
   <si>
-    <t>co2_w88544449-220_POL</t>
+    <t>co2_Pulawy_POL</t>
   </si>
   <si>
     <t>co2 captured at grid node -- way/88544449-220 (Lublin, 46 km)</t>
@@ -4411,8 +4537,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3757BC-0265-40A9-9A63-04EFCA6ADF8F}">
-  <dimension ref="B3:H75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86F90C9-4194-43B9-91B0-71CB208CACFF}">
+  <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
@@ -4448,13 +4574,13 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="D5" t="s">
         <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
@@ -4471,13 +4597,13 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
@@ -4494,13 +4620,13 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
@@ -4517,13 +4643,13 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
@@ -4540,13 +4666,13 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
@@ -4563,13 +4689,13 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
@@ -4586,13 +4712,13 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
@@ -4609,13 +4735,13 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>524</v>
+        <v>552</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
@@ -4632,13 +4758,13 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
@@ -4655,13 +4781,13 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
@@ -4678,13 +4804,13 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
@@ -4701,13 +4827,13 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>532</v>
+        <v>560</v>
       </c>
       <c r="D16" t="s">
         <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>533</v>
+        <v>561</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
@@ -4724,13 +4850,13 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="D17" t="s">
         <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
@@ -4747,13 +4873,13 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="D18" t="s">
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -4770,13 +4896,13 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>538</v>
+        <v>566</v>
       </c>
       <c r="D19" t="s">
         <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
@@ -4793,13 +4919,13 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>540</v>
+        <v>568</v>
       </c>
       <c r="D20" t="s">
         <v>241</v>
       </c>
       <c r="E20" t="s">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
@@ -4816,13 +4942,13 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="D21" t="s">
         <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
@@ -4839,13 +4965,13 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="D22" t="s">
         <v>241</v>
       </c>
       <c r="E22" t="s">
-        <v>545</v>
+        <v>573</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
@@ -4862,13 +4988,13 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="D23" t="s">
         <v>241</v>
       </c>
       <c r="E23" t="s">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
@@ -4885,13 +5011,13 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="D24" t="s">
         <v>241</v>
       </c>
       <c r="E24" t="s">
-        <v>549</v>
+        <v>577</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
@@ -4908,13 +5034,13 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="D25" t="s">
         <v>241</v>
       </c>
       <c r="E25" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
@@ -4931,13 +5057,13 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>552</v>
+        <v>580</v>
       </c>
       <c r="D26" t="s">
         <v>241</v>
       </c>
       <c r="E26" t="s">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
@@ -4954,13 +5080,13 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="D27" t="s">
         <v>241</v>
       </c>
       <c r="E27" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
@@ -4977,13 +5103,13 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="D28" t="s">
         <v>241</v>
       </c>
       <c r="E28" t="s">
-        <v>557</v>
+        <v>585</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
@@ -5000,13 +5126,13 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="D29" t="s">
         <v>241</v>
       </c>
       <c r="E29" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
@@ -5023,13 +5149,13 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="D30" t="s">
         <v>241</v>
       </c>
       <c r="E30" t="s">
-        <v>561</v>
+        <v>589</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
@@ -5046,13 +5172,13 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="D31" t="s">
         <v>241</v>
       </c>
       <c r="E31" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
@@ -5069,13 +5195,13 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="D32" t="s">
         <v>241</v>
       </c>
       <c r="E32" t="s">
-        <v>565</v>
+        <v>593</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
@@ -5092,13 +5218,13 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="D33" t="s">
         <v>241</v>
       </c>
       <c r="E33" t="s">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
@@ -5115,13 +5241,13 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="D34" t="s">
         <v>241</v>
       </c>
       <c r="E34" t="s">
-        <v>569</v>
+        <v>597</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
@@ -5138,13 +5264,13 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="D35" t="s">
         <v>241</v>
       </c>
       <c r="E35" t="s">
-        <v>571</v>
+        <v>599</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
@@ -5161,13 +5287,13 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>572</v>
+        <v>600</v>
       </c>
       <c r="D36" t="s">
         <v>241</v>
       </c>
       <c r="E36" t="s">
-        <v>573</v>
+        <v>601</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
@@ -5184,13 +5310,13 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="D37" t="s">
         <v>241</v>
       </c>
       <c r="E37" t="s">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
@@ -5207,13 +5333,13 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>576</v>
+        <v>604</v>
       </c>
       <c r="D38" t="s">
         <v>241</v>
       </c>
       <c r="E38" t="s">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
@@ -5230,13 +5356,13 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>578</v>
+        <v>606</v>
       </c>
       <c r="D39" t="s">
         <v>241</v>
       </c>
       <c r="E39" t="s">
-        <v>579</v>
+        <v>607</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
@@ -5253,13 +5379,13 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="D40" t="s">
         <v>241</v>
       </c>
       <c r="E40" t="s">
-        <v>581</v>
+        <v>609</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
@@ -5276,13 +5402,13 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="D41" t="s">
         <v>241</v>
       </c>
       <c r="E41" t="s">
-        <v>583</v>
+        <v>611</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
@@ -5299,13 +5425,13 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="D42" t="s">
         <v>241</v>
       </c>
       <c r="E42" t="s">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
@@ -5322,13 +5448,13 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="D43" t="s">
         <v>241</v>
       </c>
       <c r="E43" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
@@ -5345,13 +5471,13 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="D44" t="s">
         <v>241</v>
       </c>
       <c r="E44" t="s">
-        <v>589</v>
+        <v>617</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
@@ -5368,13 +5494,13 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
       <c r="D45" t="s">
         <v>241</v>
       </c>
       <c r="E45" t="s">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
@@ -5391,13 +5517,13 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="D46" t="s">
         <v>241</v>
       </c>
       <c r="E46" t="s">
-        <v>593</v>
+        <v>621</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
@@ -5414,13 +5540,13 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="D47" t="s">
         <v>241</v>
       </c>
       <c r="E47" t="s">
-        <v>595</v>
+        <v>623</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
@@ -5437,13 +5563,13 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
       <c r="D48" t="s">
         <v>241</v>
       </c>
       <c r="E48" t="s">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
@@ -5460,13 +5586,13 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>598</v>
+        <v>626</v>
       </c>
       <c r="D49" t="s">
         <v>241</v>
       </c>
       <c r="E49" t="s">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
@@ -5483,13 +5609,13 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>600</v>
+        <v>628</v>
       </c>
       <c r="D50" t="s">
         <v>241</v>
       </c>
       <c r="E50" t="s">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
@@ -5506,13 +5632,13 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>602</v>
+        <v>630</v>
       </c>
       <c r="D51" t="s">
         <v>241</v>
       </c>
       <c r="E51" t="s">
-        <v>603</v>
+        <v>631</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
@@ -5529,13 +5655,13 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>604</v>
+        <v>632</v>
       </c>
       <c r="D52" t="s">
         <v>241</v>
       </c>
       <c r="E52" t="s">
-        <v>605</v>
+        <v>633</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
@@ -5552,13 +5678,13 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>606</v>
+        <v>634</v>
       </c>
       <c r="D53" t="s">
         <v>241</v>
       </c>
       <c r="E53" t="s">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
@@ -5575,13 +5701,13 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="D54" t="s">
         <v>241</v>
       </c>
       <c r="E54" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
@@ -5598,13 +5724,13 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="D55" t="s">
         <v>241</v>
       </c>
       <c r="E55" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
@@ -5621,13 +5747,13 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="D56" t="s">
         <v>241</v>
       </c>
       <c r="E56" t="s">
-        <v>613</v>
+        <v>641</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
@@ -5644,13 +5770,13 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>614</v>
+        <v>642</v>
       </c>
       <c r="D57" t="s">
         <v>241</v>
       </c>
       <c r="E57" t="s">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
@@ -5667,13 +5793,13 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="D58" t="s">
         <v>241</v>
       </c>
       <c r="E58" t="s">
-        <v>617</v>
+        <v>645</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
@@ -5690,13 +5816,13 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="D59" t="s">
         <v>241</v>
       </c>
       <c r="E59" t="s">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
@@ -5713,13 +5839,13 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="D60" t="s">
         <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
@@ -5736,13 +5862,13 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="D61" t="s">
         <v>241</v>
       </c>
       <c r="E61" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
@@ -5759,13 +5885,13 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>624</v>
+        <v>652</v>
       </c>
       <c r="D62" t="s">
         <v>241</v>
       </c>
       <c r="E62" t="s">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
@@ -5782,13 +5908,13 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="D63" t="s">
         <v>241</v>
       </c>
       <c r="E63" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
@@ -5805,13 +5931,13 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="D64" t="s">
         <v>241</v>
       </c>
       <c r="E64" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
@@ -5828,13 +5954,13 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="D65" t="s">
         <v>241</v>
       </c>
       <c r="E65" t="s">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
@@ -5851,13 +5977,13 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="D66" t="s">
         <v>241</v>
       </c>
       <c r="E66" t="s">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
@@ -5874,13 +6000,13 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>634</v>
+        <v>662</v>
       </c>
       <c r="D67" t="s">
         <v>241</v>
       </c>
       <c r="E67" t="s">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
@@ -5897,13 +6023,13 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="D68" t="s">
         <v>241</v>
       </c>
       <c r="E68" t="s">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
@@ -5920,13 +6046,13 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="D69" t="s">
         <v>241</v>
       </c>
       <c r="E69" t="s">
-        <v>639</v>
+        <v>667</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
@@ -5943,13 +6069,13 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="D70" t="s">
         <v>241</v>
       </c>
       <c r="E70" t="s">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
@@ -5966,13 +6092,13 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>642</v>
+        <v>670</v>
       </c>
       <c r="D71" t="s">
         <v>241</v>
       </c>
       <c r="E71" t="s">
-        <v>643</v>
+        <v>671</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
@@ -5989,13 +6115,13 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>644</v>
+        <v>672</v>
       </c>
       <c r="D72" t="s">
         <v>241</v>
       </c>
       <c r="E72" t="s">
-        <v>645</v>
+        <v>673</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
@@ -6012,13 +6138,13 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
       <c r="D73" t="s">
         <v>241</v>
       </c>
       <c r="E73" t="s">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
@@ -6035,13 +6161,13 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="D74" t="s">
         <v>241</v>
       </c>
       <c r="E74" t="s">
-        <v>649</v>
+        <v>677</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
@@ -6058,13 +6184,13 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="D75" t="s">
         <v>241</v>
       </c>
       <c r="E75" t="s">
-        <v>651</v>
+        <v>679</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
@@ -6073,6 +6199,167 @@
         <v>347</v>
       </c>
       <c r="H75" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8">
+      <c r="B76" t="s">
+        <v>192</v>
+      </c>
+      <c r="C76" t="s">
+        <v>680</v>
+      </c>
+      <c r="D76" t="s">
+        <v>241</v>
+      </c>
+      <c r="E76" t="s">
+        <v>681</v>
+      </c>
+      <c r="F76" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" t="s">
+        <v>347</v>
+      </c>
+      <c r="H76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8">
+      <c r="B77" t="s">
+        <v>192</v>
+      </c>
+      <c r="C77" t="s">
+        <v>682</v>
+      </c>
+      <c r="D77" t="s">
+        <v>241</v>
+      </c>
+      <c r="E77" t="s">
+        <v>683</v>
+      </c>
+      <c r="F77" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" t="s">
+        <v>347</v>
+      </c>
+      <c r="H77" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8">
+      <c r="B78" t="s">
+        <v>192</v>
+      </c>
+      <c r="C78" t="s">
+        <v>684</v>
+      </c>
+      <c r="D78" t="s">
+        <v>241</v>
+      </c>
+      <c r="E78" t="s">
+        <v>685</v>
+      </c>
+      <c r="F78" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" t="s">
+        <v>347</v>
+      </c>
+      <c r="H78" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="B79" t="s">
+        <v>192</v>
+      </c>
+      <c r="C79" t="s">
+        <v>686</v>
+      </c>
+      <c r="D79" t="s">
+        <v>241</v>
+      </c>
+      <c r="E79" t="s">
+        <v>687</v>
+      </c>
+      <c r="F79" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" t="s">
+        <v>347</v>
+      </c>
+      <c r="H79" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
+      <c r="B80" t="s">
+        <v>192</v>
+      </c>
+      <c r="C80" t="s">
+        <v>688</v>
+      </c>
+      <c r="D80" t="s">
+        <v>241</v>
+      </c>
+      <c r="E80" t="s">
+        <v>689</v>
+      </c>
+      <c r="F80" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" t="s">
+        <v>347</v>
+      </c>
+      <c r="H80" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
+      <c r="B81" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81" t="s">
+        <v>690</v>
+      </c>
+      <c r="D81" t="s">
+        <v>241</v>
+      </c>
+      <c r="E81" t="s">
+        <v>691</v>
+      </c>
+      <c r="F81" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" t="s">
+        <v>347</v>
+      </c>
+      <c r="H81" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8">
+      <c r="B82" t="s">
+        <v>192</v>
+      </c>
+      <c r="C82" t="s">
+        <v>692</v>
+      </c>
+      <c r="D82" t="s">
+        <v>241</v>
+      </c>
+      <c r="E82" t="s">
+        <v>693</v>
+      </c>
+      <c r="F82" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" t="s">
+        <v>347</v>
+      </c>
+      <c r="H82" t="s">
         <v>195</v>
       </c>
     </row>
@@ -6082,8 +6369,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10557E4-196F-4833-AE62-83F120F598A6}">
-  <dimension ref="B3:I45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF627726-365E-491E-B0DB-693FF4E7ECDF}">
+  <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -6122,13 +6409,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="D5" t="s">
         <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6148,13 +6435,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6174,13 +6461,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6200,13 +6487,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6226,13 +6513,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6252,13 +6539,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6278,13 +6565,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6304,13 +6591,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6330,13 +6617,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6356,13 +6643,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6382,13 +6669,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -6408,13 +6695,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D16" t="s">
         <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -6434,13 +6721,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="D17" t="s">
         <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -6460,13 +6747,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="D18" t="s">
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -6486,13 +6773,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="D19" t="s">
         <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -6512,13 +6799,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="D20" t="s">
         <v>241</v>
       </c>
       <c r="E20" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -6538,13 +6825,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="D21" t="s">
         <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -6564,13 +6851,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="D22" t="s">
         <v>241</v>
       </c>
       <c r="E22" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -6590,13 +6877,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="D23" t="s">
         <v>241</v>
       </c>
       <c r="E23" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -6616,13 +6903,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="D24" t="s">
         <v>241</v>
       </c>
       <c r="E24" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -6642,13 +6929,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="D25" t="s">
         <v>241</v>
       </c>
       <c r="E25" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -6668,13 +6955,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="D26" t="s">
         <v>241</v>
       </c>
       <c r="E26" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -6694,13 +6981,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="D27" t="s">
         <v>241</v>
       </c>
       <c r="E27" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -6720,13 +7007,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="D28" t="s">
         <v>241</v>
       </c>
       <c r="E28" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -6746,13 +7033,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="D29" t="s">
         <v>241</v>
       </c>
       <c r="E29" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -6772,13 +7059,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="D30" t="s">
         <v>241</v>
       </c>
       <c r="E30" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -6798,13 +7085,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="D31" t="s">
         <v>241</v>
       </c>
       <c r="E31" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -6824,13 +7111,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="D32" t="s">
         <v>241</v>
       </c>
       <c r="E32" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -6850,13 +7137,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="D33" t="s">
         <v>241</v>
       </c>
       <c r="E33" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -6876,13 +7163,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="D34" t="s">
         <v>241</v>
       </c>
       <c r="E34" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -6902,13 +7189,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="D35" t="s">
         <v>241</v>
       </c>
       <c r="E35" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -6928,13 +7215,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="D36" t="s">
         <v>241</v>
       </c>
       <c r="E36" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -6954,13 +7241,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="D37" t="s">
         <v>241</v>
       </c>
       <c r="E37" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -6980,13 +7267,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="D38" t="s">
         <v>241</v>
       </c>
       <c r="E38" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7006,13 +7293,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="D39" t="s">
         <v>241</v>
       </c>
       <c r="E39" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7032,13 +7319,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="D40" t="s">
         <v>241</v>
       </c>
       <c r="E40" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7058,13 +7345,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="D41" t="s">
         <v>241</v>
       </c>
       <c r="E41" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7084,13 +7371,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="D42" t="s">
         <v>241</v>
       </c>
       <c r="E42" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7110,13 +7397,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="D43" t="s">
         <v>241</v>
       </c>
       <c r="E43" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7136,13 +7423,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D44" t="s">
         <v>241</v>
       </c>
       <c r="E44" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7162,13 +7449,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="D45" t="s">
         <v>241</v>
       </c>
       <c r="E45" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7180,6 +7467,188 @@
         <v>347</v>
       </c>
       <c r="I45" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
+        <v>524</v>
+      </c>
+      <c r="D46" t="s">
+        <v>241</v>
+      </c>
+      <c r="E46" t="s">
+        <v>525</v>
+      </c>
+      <c r="F46" t="s">
+        <v>233</v>
+      </c>
+      <c r="G46" t="s">
+        <v>232</v>
+      </c>
+      <c r="H46" t="s">
+        <v>347</v>
+      </c>
+      <c r="I46" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>526</v>
+      </c>
+      <c r="D47" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" t="s">
+        <v>527</v>
+      </c>
+      <c r="F47" t="s">
+        <v>233</v>
+      </c>
+      <c r="G47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I47" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>528</v>
+      </c>
+      <c r="D48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" t="s">
+        <v>529</v>
+      </c>
+      <c r="F48" t="s">
+        <v>233</v>
+      </c>
+      <c r="G48" t="s">
+        <v>232</v>
+      </c>
+      <c r="H48" t="s">
+        <v>347</v>
+      </c>
+      <c r="I48" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>530</v>
+      </c>
+      <c r="D49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E49" t="s">
+        <v>531</v>
+      </c>
+      <c r="F49" t="s">
+        <v>233</v>
+      </c>
+      <c r="G49" t="s">
+        <v>232</v>
+      </c>
+      <c r="H49" t="s">
+        <v>347</v>
+      </c>
+      <c r="I49" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" t="s">
+        <v>532</v>
+      </c>
+      <c r="D50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E50" t="s">
+        <v>533</v>
+      </c>
+      <c r="F50" t="s">
+        <v>233</v>
+      </c>
+      <c r="G50" t="s">
+        <v>232</v>
+      </c>
+      <c r="H50" t="s">
+        <v>347</v>
+      </c>
+      <c r="I50" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>534</v>
+      </c>
+      <c r="D51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E51" t="s">
+        <v>535</v>
+      </c>
+      <c r="F51" t="s">
+        <v>233</v>
+      </c>
+      <c r="G51" t="s">
+        <v>232</v>
+      </c>
+      <c r="H51" t="s">
+        <v>347</v>
+      </c>
+      <c r="I51" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>536</v>
+      </c>
+      <c r="D52" t="s">
+        <v>241</v>
+      </c>
+      <c r="E52" t="s">
+        <v>537</v>
+      </c>
+      <c r="F52" t="s">
+        <v>233</v>
+      </c>
+      <c r="G52" t="s">
+        <v>232</v>
+      </c>
+      <c r="H52" t="s">
+        <v>347</v>
+      </c>
+      <c r="I52" t="s">
         <v>245</v>
       </c>
     </row>
@@ -7189,8 +7658,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA8C66F2-73FF-4A03-A8A5-CD7337EAD8D1}">
-  <dimension ref="B3:I45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4EFA016-7380-4021-AED7-1B0718B4939B}">
+  <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -8287,6 +8756,188 @@
         <v>347</v>
       </c>
       <c r="I45" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" t="s">
+        <v>428</v>
+      </c>
+      <c r="D46" t="s">
+        <v>241</v>
+      </c>
+      <c r="E46" t="s">
+        <v>429</v>
+      </c>
+      <c r="F46" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" t="s">
+        <v>35</v>
+      </c>
+      <c r="H46" t="s">
+        <v>347</v>
+      </c>
+      <c r="I46" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" t="s">
+        <v>430</v>
+      </c>
+      <c r="D47" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" t="s">
+        <v>431</v>
+      </c>
+      <c r="F47" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47" t="s">
+        <v>347</v>
+      </c>
+      <c r="I47" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" t="s">
+        <v>432</v>
+      </c>
+      <c r="D48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" t="s">
+        <v>433</v>
+      </c>
+      <c r="F48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H48" t="s">
+        <v>347</v>
+      </c>
+      <c r="I48" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" t="s">
+        <v>434</v>
+      </c>
+      <c r="D49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E49" t="s">
+        <v>435</v>
+      </c>
+      <c r="F49" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" t="s">
+        <v>347</v>
+      </c>
+      <c r="I49" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" t="s">
+        <v>436</v>
+      </c>
+      <c r="D50" t="s">
+        <v>241</v>
+      </c>
+      <c r="E50" t="s">
+        <v>437</v>
+      </c>
+      <c r="F50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" t="s">
+        <v>35</v>
+      </c>
+      <c r="H50" t="s">
+        <v>347</v>
+      </c>
+      <c r="I50" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>438</v>
+      </c>
+      <c r="D51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E51" t="s">
+        <v>439</v>
+      </c>
+      <c r="F51" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H51" t="s">
+        <v>347</v>
+      </c>
+      <c r="I51" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>440</v>
+      </c>
+      <c r="D52" t="s">
+        <v>241</v>
+      </c>
+      <c r="E52" t="s">
+        <v>441</v>
+      </c>
+      <c r="F52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" t="s">
+        <v>35</v>
+      </c>
+      <c r="H52" t="s">
+        <v>347</v>
+      </c>
+      <c r="I52" t="s">
         <v>245</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB64DA1E-2E06-4354-8BC1-334070F3E3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F30560-E731-4396-9C99-6A2552B89BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="695">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1661,6 +1661,9 @@
   </si>
   <si>
     <t>co2 captured at grid node -- PL15-400 (Bydgoszcz, 10 km)</t>
+  </si>
+  <si>
+    <t>fx</t>
   </si>
   <si>
     <t>co2_Bialystok_POL</t>
@@ -4537,7 +4540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F982C190-0169-4829-AB5C-257ADAF63623}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A512C370-07F4-49A8-A49B-8FAC9783A63B}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -4586,7 +4589,7 @@
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4597,19 +4600,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4620,19 +4623,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4643,19 +4646,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4666,19 +4669,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -4689,19 +4692,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -4712,19 +4715,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -4735,19 +4738,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -4758,19 +4761,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -4781,19 +4784,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -4804,19 +4807,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -4827,19 +4830,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D16" t="s">
         <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -4850,19 +4853,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D17" t="s">
         <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -4873,19 +4876,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D18" t="s">
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -4896,19 +4899,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D19" t="s">
         <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -4919,19 +4922,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D20" t="s">
         <v>241</v>
       </c>
       <c r="E20" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -4942,19 +4945,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D21" t="s">
         <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -4965,19 +4968,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D22" t="s">
         <v>241</v>
       </c>
       <c r="E22" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -4988,19 +4991,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D23" t="s">
         <v>241</v>
       </c>
       <c r="E23" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5011,19 +5014,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D24" t="s">
         <v>241</v>
       </c>
       <c r="E24" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5034,19 +5037,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D25" t="s">
         <v>241</v>
       </c>
       <c r="E25" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5057,19 +5060,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D26" t="s">
         <v>241</v>
       </c>
       <c r="E26" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5080,19 +5083,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D27" t="s">
         <v>241</v>
       </c>
       <c r="E27" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5103,19 +5106,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D28" t="s">
         <v>241</v>
       </c>
       <c r="E28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5126,19 +5129,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D29" t="s">
         <v>241</v>
       </c>
       <c r="E29" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5149,19 +5152,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D30" t="s">
         <v>241</v>
       </c>
       <c r="E30" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5172,19 +5175,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D31" t="s">
         <v>241</v>
       </c>
       <c r="E31" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5195,19 +5198,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D32" t="s">
         <v>241</v>
       </c>
       <c r="E32" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5218,19 +5221,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D33" t="s">
         <v>241</v>
       </c>
       <c r="E33" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5241,19 +5244,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D34" t="s">
         <v>241</v>
       </c>
       <c r="E34" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5264,19 +5267,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D35" t="s">
         <v>241</v>
       </c>
       <c r="E35" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5287,19 +5290,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D36" t="s">
         <v>241</v>
       </c>
       <c r="E36" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5310,19 +5313,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D37" t="s">
         <v>241</v>
       </c>
       <c r="E37" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5333,19 +5336,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D38" t="s">
         <v>241</v>
       </c>
       <c r="E38" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5356,19 +5359,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D39" t="s">
         <v>241</v>
       </c>
       <c r="E39" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5379,19 +5382,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D40" t="s">
         <v>241</v>
       </c>
       <c r="E40" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5402,19 +5405,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D41" t="s">
         <v>241</v>
       </c>
       <c r="E41" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5425,19 +5428,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D42" t="s">
         <v>241</v>
       </c>
       <c r="E42" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5448,19 +5451,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D43" t="s">
         <v>241</v>
       </c>
       <c r="E43" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5471,19 +5474,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D44" t="s">
         <v>241</v>
       </c>
       <c r="E44" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5494,19 +5497,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D45" t="s">
         <v>241</v>
       </c>
       <c r="E45" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5517,19 +5520,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D46" t="s">
         <v>241</v>
       </c>
       <c r="E46" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5540,19 +5543,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D47" t="s">
         <v>241</v>
       </c>
       <c r="E47" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5563,19 +5566,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D48" t="s">
         <v>241</v>
       </c>
       <c r="E48" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5586,19 +5589,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D49" t="s">
         <v>241</v>
       </c>
       <c r="E49" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5609,19 +5612,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D50" t="s">
         <v>241</v>
       </c>
       <c r="E50" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5632,19 +5635,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D51" t="s">
         <v>241</v>
       </c>
       <c r="E51" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5655,19 +5658,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D52" t="s">
         <v>241</v>
       </c>
       <c r="E52" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -5678,19 +5681,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D53" t="s">
         <v>241</v>
       </c>
       <c r="E53" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -5701,19 +5704,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D54" t="s">
         <v>241</v>
       </c>
       <c r="E54" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -5724,19 +5727,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D55" t="s">
         <v>241</v>
       </c>
       <c r="E55" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -5747,19 +5750,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D56" t="s">
         <v>241</v>
       </c>
       <c r="E56" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -5770,19 +5773,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D57" t="s">
         <v>241</v>
       </c>
       <c r="E57" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -5793,19 +5796,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D58" t="s">
         <v>241</v>
       </c>
       <c r="E58" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -5816,19 +5819,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D59" t="s">
         <v>241</v>
       </c>
       <c r="E59" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -5839,19 +5842,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D60" t="s">
         <v>241</v>
       </c>
       <c r="E60" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -5862,19 +5865,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D61" t="s">
         <v>241</v>
       </c>
       <c r="E61" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -5885,19 +5888,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D62" t="s">
         <v>241</v>
       </c>
       <c r="E62" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -5908,19 +5911,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D63" t="s">
         <v>241</v>
       </c>
       <c r="E63" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -5931,19 +5934,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D64" t="s">
         <v>241</v>
       </c>
       <c r="E64" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -5954,19 +5957,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D65" t="s">
         <v>241</v>
       </c>
       <c r="E65" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -5977,19 +5980,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D66" t="s">
         <v>241</v>
       </c>
       <c r="E66" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -6000,19 +6003,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D67" t="s">
         <v>241</v>
       </c>
       <c r="E67" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6023,19 +6026,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D68" t="s">
         <v>241</v>
       </c>
       <c r="E68" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6046,19 +6049,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D69" t="s">
         <v>241</v>
       </c>
       <c r="E69" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6069,19 +6072,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D70" t="s">
         <v>241</v>
       </c>
       <c r="E70" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6092,19 +6095,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D71" t="s">
         <v>241</v>
       </c>
       <c r="E71" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6115,19 +6118,19 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D72" t="s">
         <v>241</v>
       </c>
       <c r="E72" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H72" t="s">
         <v>195</v>
@@ -6138,19 +6141,19 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D73" t="s">
         <v>241</v>
       </c>
       <c r="E73" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H73" t="s">
         <v>195</v>
@@ -6161,19 +6164,19 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D74" t="s">
         <v>241</v>
       </c>
       <c r="E74" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H74" t="s">
         <v>195</v>
@@ -6184,19 +6187,19 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D75" t="s">
         <v>241</v>
       </c>
       <c r="E75" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H75" t="s">
         <v>195</v>
@@ -6207,19 +6210,19 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D76" t="s">
         <v>241</v>
       </c>
       <c r="E76" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H76" t="s">
         <v>195</v>
@@ -6230,19 +6233,19 @@
         <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D77" t="s">
         <v>241</v>
       </c>
       <c r="E77" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H77" t="s">
         <v>195</v>
@@ -6253,19 +6256,19 @@
         <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D78" t="s">
         <v>241</v>
       </c>
       <c r="E78" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H78" t="s">
         <v>195</v>
@@ -6276,19 +6279,19 @@
         <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D79" t="s">
         <v>241</v>
       </c>
       <c r="E79" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H79" t="s">
         <v>195</v>
@@ -6299,19 +6302,19 @@
         <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D80" t="s">
         <v>241</v>
       </c>
       <c r="E80" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H80" t="s">
         <v>195</v>
@@ -6322,19 +6325,19 @@
         <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D81" t="s">
         <v>241</v>
       </c>
       <c r="E81" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H81" t="s">
         <v>195</v>
@@ -6345,19 +6348,19 @@
         <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D82" t="s">
         <v>241</v>
       </c>
       <c r="E82" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>347</v>
+        <v>540</v>
       </c>
       <c r="H82" t="s">
         <v>195</v>
@@ -6369,7 +6372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55D442E4-B980-4536-8025-9A06220FB660}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7E50A2-DEC6-4191-9551-D44EBE4CA37E}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7658,7 +7661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E1E426D-6528-4E28-A29F-BE8FFD86C4BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BCE6363-E035-495E-B815-A5FA64EDCB80}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F30560-E731-4396-9C99-6A2552B89BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8E6FAE-0AA5-452E-B935-F6C3695D9A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4540,7 +4540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A512C370-07F4-49A8-A49B-8FAC9783A63B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553AFDE8-49F5-47DE-AC95-E7F666E7B399}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6372,7 +6372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E7E50A2-DEC6-4191-9551-D44EBE4CA37E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E03CEBF-0D0F-4E76-B615-E17AF1B77644}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7661,7 +7661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BCE6363-E035-495E-B815-A5FA64EDCB80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0993959F-1605-4859-B6BD-7F06985445BB}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8E6FAE-0AA5-452E-B935-F6C3695D9A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C8F601-7DC3-4930-8218-814EF66B0E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4540,7 +4540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553AFDE8-49F5-47DE-AC95-E7F666E7B399}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FDCD04-8EFA-45CB-8350-D871939484E1}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6372,7 +6372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E03CEBF-0D0F-4E76-B615-E17AF1B77644}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A1ADA2-E3A9-4377-92AF-01A5F184CB3F}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7661,7 +7661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0993959F-1605-4859-B6BD-7F06985445BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C524E112-F116-4C80-9F10-EC1F66C5B8DA}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C8F601-7DC3-4930-8218-814EF66B0E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC93E4AA-2D42-46CD-B32D-E795FBD727A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4540,7 +4540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67FDCD04-8EFA-45CB-8350-D871939484E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F61CFE5-FA6A-44D3-9ABB-4E08443580B4}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6372,7 +6372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A1ADA2-E3A9-4377-92AF-01A5F184CB3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373C631D-5B2D-4CA6-9FBD-1EAD4E9ADD4B}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7661,7 +7661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C524E112-F116-4C80-9F10-EC1F66C5B8DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4948D684-090D-4E5C-A6EA-8EEDB463F6CA}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC93E4AA-2D42-46CD-B32D-E795FBD727A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E2CDCB-EB0E-4CFC-8306-BDF2F71F0AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4540,7 +4540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F61CFE5-FA6A-44D3-9ABB-4E08443580B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA44D992-8E53-461B-92C7-3D93B2364653}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6372,7 +6372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373C631D-5B2D-4CA6-9FBD-1EAD4E9ADD4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2699F9-AFEE-47D9-A6B9-F679B7306E63}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7661,7 +7661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4948D684-090D-4E5C-A6EA-8EEDB463F6CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC5D490-DDC1-4C79-970C-08B966417751}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E2CDCB-EB0E-4CFC-8306-BDF2F71F0AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98879F5-FE67-47B6-882E-7504DD845EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4540,7 +4540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA44D992-8E53-461B-92C7-3D93B2364653}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C27E2A-C866-4AFC-BBBE-ACAC3D6842BE}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6372,7 +6372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2699F9-AFEE-47D9-A6B9-F679B7306E63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB32F317-009B-4E7B-A5A3-8D0AFD924DB4}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7661,7 +7661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAC5D490-DDC1-4C79-970C-08B966417751}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5B5BF7E-D4D3-4BB2-9207-DD418794C317}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98879F5-FE67-47B6-882E-7504DD845EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE87A75B-E95C-4BFD-B78D-B04500F8480F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="697">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -2126,6 +2126,12 @@
   </si>
   <si>
     <t>co2 delivered to sink -- T8 (national overlay)</t>
+  </si>
+  <si>
+    <t>ELCnH</t>
+  </si>
+  <si>
+    <t>&gt;10 hours of surplus electricity from VRE generation</t>
   </si>
 </sst>
 </file>
@@ -10225,14 +10231,11 @@
       </c>
     </row>
     <row r="42" spans="2:19">
-      <c r="B42" t="s">
-        <v>192</v>
-      </c>
       <c r="C42" t="s">
-        <v>225</v>
+        <v>695</v>
       </c>
       <c r="D42" t="s">
-        <v>226</v>
+        <v>696</v>
       </c>
       <c r="E42" t="s">
         <v>84</v>
@@ -10240,6 +10243,9 @@
       <c r="F42" t="s">
         <v>222</v>
       </c>
+      <c r="G42" t="s">
+        <v>25</v>
+      </c>
       <c r="M42" t="s">
         <v>17</v>
       </c>
@@ -10263,17 +10269,20 @@
       </c>
     </row>
     <row r="43" spans="2:19">
+      <c r="B43" t="s">
+        <v>192</v>
+      </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D43" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="F43" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="M43" t="s">
         <v>17</v>
@@ -10298,6 +10307,18 @@
       </c>
     </row>
     <row r="44" spans="2:19">
+      <c r="C44" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" t="s">
+        <v>228</v>
+      </c>
+      <c r="E44" t="s">
+        <v>229</v>
+      </c>
+      <c r="F44" t="s">
+        <v>185</v>
+      </c>
       <c r="M44" t="s">
         <v>17</v>
       </c>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE87A75B-E95C-4BFD-B78D-B04500F8480F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5D061D-C1A8-4E2A-8436-BBF004E4CA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -766,6 +766,12 @@
     <t>heat used in industry</t>
   </si>
   <si>
+    <t>ELCnH</t>
+  </si>
+  <si>
+    <t>&gt;10 hours of surplus electricity from VRE generation</t>
+  </si>
+  <si>
     <t>POL</t>
   </si>
   <si>
@@ -2126,12 +2132,6 @@
   </si>
   <si>
     <t>co2 delivered to sink -- T8 (national overlay)</t>
-  </si>
-  <si>
-    <t>ELCnH</t>
-  </si>
-  <si>
-    <t>&gt;10 hours of surplus electricity from VRE generation</t>
   </si>
 </sst>
 </file>
@@ -2159,14 +2159,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2174,7 +2174,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2182,21 +2182,21 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2430,7 +2430,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2438,7 +2438,7 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2446,28 +2446,28 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2520,14 +2520,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4164,9 +4164,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4174,39 +4174,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -4258,7 +4258,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -4310,7 +4310,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4369,6 +4369,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -4377,13 +4384,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -4448,31 +4448,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4522,7 +4502,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -4546,13 +4526,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C27E2A-C866-4AFC-BBBE-ACAC3D6842BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50B0468-B1D4-4B71-A53D-134E57B00074}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4563,7 +4543,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -4583,19 +4563,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4606,19 +4586,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4629,19 +4609,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4652,19 +4632,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4675,19 +4655,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -4698,19 +4678,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -4721,19 +4701,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -4744,19 +4724,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -4767,19 +4747,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -4790,19 +4770,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -4813,19 +4793,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -4836,19 +4816,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -4859,19 +4839,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -4882,19 +4862,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D18" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -4905,19 +4885,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -4928,19 +4908,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -4951,19 +4931,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -4974,19 +4954,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -4997,19 +4977,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5020,19 +5000,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5043,19 +5023,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5066,19 +5046,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5089,19 +5069,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5112,19 +5092,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5135,19 +5115,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D29" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5158,19 +5138,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5181,19 +5161,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5204,19 +5184,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5227,19 +5207,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5250,19 +5230,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5273,19 +5253,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D35" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5296,19 +5276,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5319,19 +5299,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D37" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5342,19 +5322,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5365,19 +5345,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5388,19 +5368,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D40" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5411,19 +5391,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D41" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5434,19 +5414,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5457,19 +5437,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5480,19 +5460,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D44" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5503,19 +5483,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D45" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5526,19 +5506,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5549,19 +5529,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5572,19 +5552,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D48" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5595,19 +5575,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5618,19 +5598,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5641,19 +5621,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5664,19 +5644,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -5687,19 +5667,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -5710,19 +5690,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -5733,19 +5713,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D55" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -5756,19 +5736,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D56" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -5779,19 +5759,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D57" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -5802,19 +5782,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D58" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -5825,19 +5805,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D59" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -5848,19 +5828,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D60" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -5871,19 +5851,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D61" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -5894,19 +5874,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D62" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -5917,19 +5897,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D63" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -5940,19 +5920,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D64" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -5963,19 +5943,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D65" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -5986,19 +5966,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D66" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -6009,19 +5989,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D67" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6032,19 +6012,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D68" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6055,19 +6035,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D69" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6078,19 +6058,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D70" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6101,19 +6081,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D71" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6124,19 +6104,19 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D72" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H72" t="s">
         <v>195</v>
@@ -6147,19 +6127,19 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D73" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H73" t="s">
         <v>195</v>
@@ -6170,19 +6150,19 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D74" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H74" t="s">
         <v>195</v>
@@ -6193,19 +6173,19 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D75" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H75" t="s">
         <v>195</v>
@@ -6216,19 +6196,19 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D76" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H76" t="s">
         <v>195</v>
@@ -6239,19 +6219,19 @@
         <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D77" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H77" t="s">
         <v>195</v>
@@ -6262,19 +6242,19 @@
         <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H78" t="s">
         <v>195</v>
@@ -6285,19 +6265,19 @@
         <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D79" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H79" t="s">
         <v>195</v>
@@ -6308,19 +6288,19 @@
         <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D80" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H80" t="s">
         <v>195</v>
@@ -6331,19 +6311,19 @@
         <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H81" t="s">
         <v>195</v>
@@ -6354,19 +6334,19 @@
         <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D82" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H82" t="s">
         <v>195</v>
@@ -6378,13 +6358,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB32F317-009B-4E7B-A5A3-8D0AFD924DB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46907262-9D9A-4F09-B611-F46884B3AC4A}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6395,7 +6375,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -6418,13 +6398,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6433,10 +6413,10 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="2:9">
@@ -6444,13 +6424,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6459,10 +6439,10 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="2:9">
@@ -6470,13 +6450,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6485,10 +6465,10 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -6496,13 +6476,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6511,10 +6491,10 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -6522,13 +6502,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6537,10 +6517,10 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -6548,13 +6528,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6563,10 +6543,10 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="2:9">
@@ -6574,13 +6554,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6589,10 +6569,10 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="2:9">
@@ -6600,13 +6580,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6615,10 +6595,10 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="2:9">
@@ -6626,13 +6606,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6641,10 +6621,10 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="2:9">
@@ -6652,13 +6632,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6667,10 +6647,10 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="2:9">
@@ -6678,13 +6658,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -6693,10 +6673,10 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="2:9">
@@ -6704,13 +6684,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -6719,10 +6699,10 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I16" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -6730,13 +6710,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -6745,10 +6725,10 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -6756,13 +6736,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D18" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -6771,10 +6751,10 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="2:9">
@@ -6782,13 +6762,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -6797,10 +6777,10 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="2:9">
@@ -6808,13 +6788,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -6823,10 +6803,10 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="2:9">
@@ -6834,13 +6814,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -6849,10 +6829,10 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -6860,13 +6840,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -6875,10 +6855,10 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I22" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -6886,13 +6866,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -6901,10 +6881,10 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I23" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="2:9">
@@ -6912,13 +6892,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -6927,10 +6907,10 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I24" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="2:9">
@@ -6938,13 +6918,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -6953,10 +6933,10 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I25" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="2:9">
@@ -6964,13 +6944,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -6979,10 +6959,10 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="2:9">
@@ -6990,13 +6970,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -7005,10 +6985,10 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I27" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -7016,13 +6996,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7031,10 +7011,10 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="2:9">
@@ -7042,13 +7022,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D29" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7057,10 +7037,10 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I29" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="2:9">
@@ -7068,13 +7048,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7083,10 +7063,10 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I30" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="2:9">
@@ -7094,13 +7074,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7109,10 +7089,10 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="2:9">
@@ -7120,13 +7100,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7135,10 +7115,10 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I32" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="2:9">
@@ -7146,13 +7126,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7161,10 +7141,10 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I33" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -7172,13 +7152,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7187,10 +7167,10 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="2:9">
@@ -7198,13 +7178,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D35" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7213,10 +7193,10 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="2:9">
@@ -7224,13 +7204,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7239,10 +7219,10 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I36" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="2:9">
@@ -7250,13 +7230,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D37" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7265,10 +7245,10 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I37" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" spans="2:9">
@@ -7276,13 +7256,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7291,10 +7271,10 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="2:9">
@@ -7302,13 +7282,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7317,10 +7297,10 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I39" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="2:9">
@@ -7328,13 +7308,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D40" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7343,10 +7323,10 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I40" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="2:9">
@@ -7354,13 +7334,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D41" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7369,10 +7349,10 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I41" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="2:9">
@@ -7380,13 +7360,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7395,10 +7375,10 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I42" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="2:9">
@@ -7406,13 +7386,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7421,10 +7401,10 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I43" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="2:9">
@@ -7432,13 +7412,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D44" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7447,10 +7427,10 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="2:9">
@@ -7458,13 +7438,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D45" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7473,10 +7453,10 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I45" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="2:9">
@@ -7484,13 +7464,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7499,10 +7479,10 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I46" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="2:9">
@@ -7510,13 +7490,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7525,10 +7505,10 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I47" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48" spans="2:9">
@@ -7536,13 +7516,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D48" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7551,10 +7531,10 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I48" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" spans="2:9">
@@ -7562,13 +7542,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7577,10 +7557,10 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I49" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="2:9">
@@ -7588,13 +7568,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7603,10 +7583,10 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I50" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="2:9">
@@ -7614,13 +7594,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7629,10 +7609,10 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="2:9">
@@ -7640,13 +7620,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7655,10 +7635,10 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -7667,13 +7647,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5B5BF7E-D4D3-4BB2-9207-DD418794C317}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007B4802-7D1F-4CC0-8DC6-66034607196D}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -7684,7 +7664,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -7707,13 +7687,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -7722,10 +7702,10 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="2:9">
@@ -7733,13 +7713,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -7748,10 +7728,10 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="2:9">
@@ -7759,13 +7739,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -7774,10 +7754,10 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -7785,13 +7765,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -7800,10 +7780,10 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -7811,13 +7791,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -7826,10 +7806,10 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -7837,13 +7817,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -7852,10 +7832,10 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="2:9">
@@ -7863,13 +7843,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -7878,10 +7858,10 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="2:9">
@@ -7889,13 +7869,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -7904,10 +7884,10 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="2:9">
@@ -7915,13 +7895,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -7930,10 +7910,10 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="2:9">
@@ -7941,13 +7921,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -7956,10 +7936,10 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="2:9">
@@ -7967,13 +7947,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -7982,10 +7962,10 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="2:9">
@@ -7993,13 +7973,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -8008,10 +7988,10 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I16" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -8019,13 +7999,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8034,10 +8014,10 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -8045,13 +8025,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D18" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8060,10 +8040,10 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="2:9">
@@ -8071,13 +8051,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8086,10 +8066,10 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="2:9">
@@ -8097,13 +8077,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8112,10 +8092,10 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="2:9">
@@ -8123,13 +8103,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8138,10 +8118,10 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -8149,13 +8129,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8164,10 +8144,10 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I22" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -8175,13 +8155,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8190,10 +8170,10 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I23" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="2:9">
@@ -8201,13 +8181,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8216,10 +8196,10 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I24" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="2:9">
@@ -8227,13 +8207,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8242,10 +8222,10 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I25" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="2:9">
@@ -8253,13 +8233,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -8268,10 +8248,10 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="2:9">
@@ -8279,13 +8259,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8294,10 +8274,10 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I27" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -8305,13 +8285,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8320,10 +8300,10 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="2:9">
@@ -8331,13 +8311,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D29" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8346,10 +8326,10 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I29" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="2:9">
@@ -8357,13 +8337,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8372,10 +8352,10 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I30" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="2:9">
@@ -8383,13 +8363,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8398,10 +8378,10 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="2:9">
@@ -8409,13 +8389,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -8424,10 +8404,10 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I32" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="2:9">
@@ -8435,13 +8415,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8450,10 +8430,10 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I33" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -8461,13 +8441,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -8476,10 +8456,10 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="2:9">
@@ -8487,13 +8467,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D35" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -8502,10 +8482,10 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="2:9">
@@ -8513,13 +8493,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -8528,10 +8508,10 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I36" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="2:9">
@@ -8539,13 +8519,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D37" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -8554,10 +8534,10 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I37" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" spans="2:9">
@@ -8565,13 +8545,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -8580,10 +8560,10 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="2:9">
@@ -8591,13 +8571,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -8606,10 +8586,10 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I39" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="2:9">
@@ -8617,13 +8597,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D40" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -8632,10 +8612,10 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I40" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="2:9">
@@ -8643,13 +8623,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D41" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -8658,10 +8638,10 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I41" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="2:9">
@@ -8669,13 +8649,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -8684,10 +8664,10 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I42" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="2:9">
@@ -8695,13 +8675,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -8710,10 +8690,10 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I43" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="2:9">
@@ -8721,13 +8701,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D44" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -8736,10 +8716,10 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="2:9">
@@ -8747,13 +8727,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D45" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -8762,10 +8742,10 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I45" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="2:9">
@@ -8773,13 +8753,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -8788,10 +8768,10 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I46" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="2:9">
@@ -8799,13 +8779,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -8814,10 +8794,10 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I47" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48" spans="2:9">
@@ -8825,13 +8805,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D48" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -8840,10 +8820,10 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I48" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" spans="2:9">
@@ -8851,13 +8831,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -8866,10 +8846,10 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I49" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="2:9">
@@ -8877,13 +8857,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -8892,10 +8872,10 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I50" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="2:9">
@@ -8903,13 +8883,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -8918,10 +8898,10 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="2:9">
@@ -8929,13 +8909,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -8944,10 +8924,10 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -8970,7 +8950,7 @@
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:19" ht="17.649999999999999" thickBot="1">
+    <row r="3" spans="2:19" ht="17.25" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -9021,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>11</v>
@@ -9050,13 +9030,13 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q5" t="s">
         <v>25</v>
@@ -9065,7 +9045,7 @@
         <v>35</v>
       </c>
       <c r="S5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="2:19">
@@ -9082,13 +9062,13 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q6" t="s">
         <v>25</v>
@@ -9097,7 +9077,7 @@
         <v>35</v>
       </c>
       <c r="S6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="2:19">
@@ -9114,13 +9094,13 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q7" t="s">
         <v>25</v>
@@ -9129,7 +9109,7 @@
         <v>35</v>
       </c>
       <c r="S7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="2:19">
@@ -9146,13 +9126,13 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q8" t="s">
         <v>25</v>
@@ -9161,7 +9141,7 @@
         <v>35</v>
       </c>
       <c r="S8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="2:19">
@@ -9178,13 +9158,13 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q9" t="s">
         <v>25</v>
@@ -9193,7 +9173,7 @@
         <v>35</v>
       </c>
       <c r="S9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="2:19">
@@ -9210,13 +9190,13 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q10" t="s">
         <v>25</v>
@@ -9225,7 +9205,7 @@
         <v>35</v>
       </c>
       <c r="S10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="2:19">
@@ -9242,13 +9222,13 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="s">
         <v>25</v>
@@ -9257,7 +9237,7 @@
         <v>35</v>
       </c>
       <c r="S11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="2:19">
@@ -9274,13 +9254,13 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q12" t="s">
         <v>25</v>
@@ -9289,7 +9269,7 @@
         <v>35</v>
       </c>
       <c r="S12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="2:19">
@@ -9306,13 +9286,13 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q13" t="s">
         <v>25</v>
@@ -9321,7 +9301,7 @@
         <v>35</v>
       </c>
       <c r="S13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="2:19">
@@ -9341,13 +9321,13 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q14" t="s">
         <v>25</v>
@@ -9356,7 +9336,7 @@
         <v>35</v>
       </c>
       <c r="S14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="2:19">
@@ -9376,13 +9356,13 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O15" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q15" t="s">
         <v>25</v>
@@ -9391,7 +9371,7 @@
         <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="2:19">
@@ -9420,13 +9400,13 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P16" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q16" t="s">
         <v>25</v>
@@ -9435,7 +9415,7 @@
         <v>35</v>
       </c>
       <c r="S16" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="2:19">
@@ -9461,13 +9441,13 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P17" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q17" t="s">
         <v>25</v>
@@ -9476,7 +9456,7 @@
         <v>35</v>
       </c>
       <c r="S17" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="2:19">
@@ -9496,13 +9476,13 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O18" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P18" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q18" t="s">
         <v>25</v>
@@ -9511,7 +9491,7 @@
         <v>35</v>
       </c>
       <c r="S18" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="2:19">
@@ -9531,13 +9511,13 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O19" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q19" t="s">
         <v>25</v>
@@ -9546,7 +9526,7 @@
         <v>35</v>
       </c>
       <c r="S19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="2:19">
@@ -9566,13 +9546,13 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P20" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q20" t="s">
         <v>25</v>
@@ -9581,7 +9561,7 @@
         <v>35</v>
       </c>
       <c r="S20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="2:19">
@@ -9601,13 +9581,13 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P21" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q21" t="s">
         <v>25</v>
@@ -9616,7 +9596,7 @@
         <v>35</v>
       </c>
       <c r="S21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="2:19">
@@ -9642,13 +9622,13 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q22" t="s">
         <v>25</v>
@@ -9657,7 +9637,7 @@
         <v>35</v>
       </c>
       <c r="S22" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="2:19">
@@ -9677,13 +9657,13 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q23" t="s">
         <v>25</v>
@@ -9692,7 +9672,7 @@
         <v>35</v>
       </c>
       <c r="S23" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="2:19">
@@ -9712,13 +9692,13 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q24" t="s">
         <v>25</v>
@@ -9727,7 +9707,7 @@
         <v>35</v>
       </c>
       <c r="S24" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="2:19">
@@ -9747,13 +9727,13 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q25" t="s">
         <v>25</v>
@@ -9762,7 +9742,7 @@
         <v>35</v>
       </c>
       <c r="S25" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="2:19">
@@ -9779,13 +9759,13 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O26" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q26" t="s">
         <v>25</v>
@@ -9794,7 +9774,7 @@
         <v>35</v>
       </c>
       <c r="S26" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="2:19">
@@ -9811,13 +9791,13 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q27" t="s">
         <v>25</v>
@@ -9826,7 +9806,7 @@
         <v>35</v>
       </c>
       <c r="S27" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="2:19">
@@ -9834,13 +9814,13 @@
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q28" t="s">
         <v>25</v>
@@ -9849,7 +9829,7 @@
         <v>35</v>
       </c>
       <c r="S28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="2:19">
@@ -9857,13 +9837,13 @@
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O29" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q29" t="s">
         <v>25</v>
@@ -9872,10 +9852,10 @@
         <v>35</v>
       </c>
       <c r="S29" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="30" spans="2:19" ht="17.649999999999999" thickBot="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" ht="17.25" thickBot="1">
       <c r="B30" s="3" t="s">
         <v>212</v>
       </c>
@@ -9885,13 +9865,13 @@
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P30" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q30" t="s">
         <v>25</v>
@@ -9900,7 +9880,7 @@
         <v>35</v>
       </c>
       <c r="S30" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="2:19" ht="15" thickTop="1" thickBot="1">
@@ -9917,13 +9897,13 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P31" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q31" t="s">
         <v>25</v>
@@ -9932,7 +9912,7 @@
         <v>35</v>
       </c>
       <c r="S31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="2:19">
@@ -9949,13 +9929,13 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O32" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q32" t="s">
         <v>25</v>
@@ -9964,7 +9944,7 @@
         <v>35</v>
       </c>
       <c r="S32" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="2:19">
@@ -9972,13 +9952,13 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O33" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P33" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q33" t="s">
         <v>25</v>
@@ -9987,7 +9967,7 @@
         <v>35</v>
       </c>
       <c r="S33" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="2:19">
@@ -9995,13 +9975,13 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O34" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q34" t="s">
         <v>25</v>
@@ -10010,7 +9990,7 @@
         <v>35</v>
       </c>
       <c r="S34" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="2:19">
@@ -10018,13 +9998,13 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O35" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P35" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q35" t="s">
         <v>25</v>
@@ -10033,7 +10013,7 @@
         <v>35</v>
       </c>
       <c r="S35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="2:19">
@@ -10041,13 +10021,13 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P36" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q36" t="s">
         <v>25</v>
@@ -10056,7 +10036,7 @@
         <v>35</v>
       </c>
       <c r="S36" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="2:19">
@@ -10064,13 +10044,13 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O37" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P37" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q37" t="s">
         <v>25</v>
@@ -10079,10 +10059,10 @@
         <v>35</v>
       </c>
       <c r="S37" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="38" spans="2:19" ht="17.649999999999999" thickBot="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" ht="17.25" thickBot="1">
       <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
@@ -10092,13 +10072,13 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O38" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q38" t="s">
         <v>25</v>
@@ -10107,7 +10087,7 @@
         <v>35</v>
       </c>
       <c r="S38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="2:19" ht="15" thickTop="1" thickBot="1">
@@ -10133,13 +10113,13 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P39" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q39" t="s">
         <v>25</v>
@@ -10148,7 +10128,7 @@
         <v>35</v>
       </c>
       <c r="S39" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="2:19">
@@ -10174,13 +10154,13 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O40" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P40" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q40" t="s">
         <v>25</v>
@@ -10189,7 +10169,7 @@
         <v>35</v>
       </c>
       <c r="S40" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="2:19">
@@ -10212,13 +10192,13 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O41" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P41" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q41" t="s">
         <v>25</v>
@@ -10227,15 +10207,15 @@
         <v>35</v>
       </c>
       <c r="S41" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="2:19">
       <c r="C42" t="s">
-        <v>695</v>
+        <v>241</v>
       </c>
       <c r="D42" t="s">
-        <v>696</v>
+        <v>242</v>
       </c>
       <c r="E42" t="s">
         <v>84</v>
@@ -10250,13 +10230,13 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P42" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q42" t="s">
         <v>25</v>
@@ -10265,7 +10245,7 @@
         <v>35</v>
       </c>
       <c r="S42" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="2:19">
@@ -10288,13 +10268,13 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P43" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q43" t="s">
         <v>25</v>
@@ -10303,7 +10283,7 @@
         <v>35</v>
       </c>
       <c r="S43" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="2:19">
@@ -10323,13 +10303,13 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O44" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P44" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q44" t="s">
         <v>25</v>
@@ -10338,7 +10318,7 @@
         <v>35</v>
       </c>
       <c r="S44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="2:19">
@@ -10346,13 +10326,13 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O45" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P45" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q45" t="s">
         <v>25</v>
@@ -10361,7 +10341,7 @@
         <v>35</v>
       </c>
       <c r="S45" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="2:19">
@@ -10369,13 +10349,13 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P46" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q46" t="s">
         <v>25</v>
@@ -10384,7 +10364,7 @@
         <v>35</v>
       </c>
       <c r="S46" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="2:19">
@@ -10392,13 +10372,13 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O47" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P47" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q47" t="s">
         <v>25</v>
@@ -10407,7 +10387,7 @@
         <v>35</v>
       </c>
       <c r="S47" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48" spans="2:19">
@@ -10415,13 +10395,13 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O48" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P48" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q48" t="s">
         <v>25</v>
@@ -10430,7 +10410,7 @@
         <v>35</v>
       </c>
       <c r="S48" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" spans="13:19">
@@ -10438,13 +10418,13 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q49" t="s">
         <v>25</v>
@@ -10453,7 +10433,7 @@
         <v>35</v>
       </c>
       <c r="S49" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="13:19">
@@ -10461,13 +10441,13 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O50" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P50" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q50" t="s">
         <v>25</v>
@@ -10476,7 +10456,7 @@
         <v>35</v>
       </c>
       <c r="S50" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="13:19">
@@ -10484,13 +10464,13 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P51" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q51" t="s">
         <v>25</v>
@@ -10499,7 +10479,7 @@
         <v>35</v>
       </c>
       <c r="S51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="13:19">
@@ -10507,13 +10487,13 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P52" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q52" t="s">
         <v>25</v>
@@ -10522,7 +10502,7 @@
         <v>35</v>
       </c>
       <c r="S52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="13:19">
@@ -10530,13 +10510,13 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O53" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P53" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q53" t="s">
         <v>25</v>
@@ -10545,7 +10525,7 @@
         <v>35</v>
       </c>
       <c r="S53" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="13:19">
@@ -10553,13 +10533,13 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P54" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q54" t="s">
         <v>25</v>
@@ -10568,7 +10548,7 @@
         <v>35</v>
       </c>
       <c r="S54" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -11464,7 +11444,7 @@
     <col min="15" max="16384" width="11.3984375" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="17.649999999999999" thickBot="1">
+    <row r="2" spans="1:14" ht="17.25" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
         <v>68</v>
@@ -13022,7 +13002,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="17.649999999999999" thickBot="1">
+    <row r="99" spans="5:10" ht="17.25" thickBot="1">
       <c r="E99" s="20" t="s">
         <v>182</v>
       </c>
@@ -13093,7 +13073,7 @@
     <col min="4" max="16384" width="8.86328125" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.649999999999999" thickBot="1">
+    <row r="3" spans="2:4" ht="17.25" thickBot="1">
       <c r="B3" s="20" t="s">
         <v>63</v>
       </c>
@@ -13290,7 +13270,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="17.649999999999999" thickBot="1">
+    <row r="25" spans="2:4" ht="17.25" thickBot="1">
       <c r="B25" s="20" t="s">
         <v>171</v>
       </c>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5D061D-C1A8-4E2A-8436-BBF004E4CA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B0A888-D9DB-4A49-928D-67E26D204B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4526,7 +4526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50B0468-B1D4-4B71-A53D-134E57B00074}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9E4C71-901F-4351-B311-A9CFD9D4B17E}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6358,7 +6358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46907262-9D9A-4F09-B611-F46884B3AC4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7432F9F-A752-4475-BC07-A7266FBB851F}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7647,7 +7647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007B4802-7D1F-4CC0-8DC6-66034607196D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018FAFA8-8CE2-45D4-91FC-450736FFAD14}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B0A888-D9DB-4A49-928D-67E26D204B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EACAF63-04C0-4ADE-B0C6-DF363F428B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -781,7 +781,7 @@
     <t>elc_spv_POL_001</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 1)</t>
+    <t>solar electricity near Bialystok (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -790,97 +790,97 @@
     <t>elc_spv_POL_002</t>
   </si>
   <si>
-    <t>solar electricity near Opole (cluster 2)</t>
+    <t>solar electricity near Suwalki (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 3)</t>
+    <t>solar electricity near Przemysl (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity near Gorzow Wielkopolski (cluster 4)</t>
+    <t>solar electricity near Krakow (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity near Pila (cluster 5)</t>
+    <t>solar electricity near Biala Podlaska (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 6)</t>
+    <t>solar electricity near Zamosc (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 7)</t>
+    <t>solar electricity near Szczecin (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 8)</t>
+    <t>solar electricity near Pila (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Bialystok (cluster 9)</t>
+    <t>solar electricity near Bydgoszcz (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity near Suwalki (cluster 10)</t>
+    <t>solar electricity near Olsztyn (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity near Bialystok (cluster 11)</t>
+    <t>solar electricity near Gdansk (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>solar electricity near Przemysl (cluster 12)</t>
+    <t>solar electricity near Poznan (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity near Zamosc (cluster 13)</t>
+    <t>solar electricity near Wroclaw (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 14)</t>
+    <t>solar electricity near Jelenia Gora (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity near Katowice (cluster 15)</t>
+    <t>solar electricity near Zielona Gora (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Kalisz (cluster 16)</t>
+    <t>solar electricity near Opole (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Bydgoszcz (cluster 17)</t>
+    <t>solar electricity near Katowice (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
@@ -892,13 +892,13 @@
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity near Radom (cluster 19)</t>
+    <t>solar electricity near Kielce (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 20)</t>
+    <t>solar electricity near Lodz (cluster 20)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -964,121 +964,121 @@
     <t>elc_won_POL_001</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 1)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kielce (cluster 2)</t>
+    <t>wind onshore electricity near Pila (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
-    <t>wind onshore electricity near Siedlce (cluster 3)</t>
+    <t>wind onshore electricity near Torun (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zamosc (cluster 4)</t>
+    <t>wind onshore electricity near Kalisz (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Suwalki (cluster 5)</t>
+    <t>wind onshore electricity near Lubin (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wloclawek (cluster 6)</t>
+    <t>wind onshore electricity near Legnica (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 7)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 8)</t>
+    <t>wind onshore electricity near Katowice (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Elblag (cluster 9)</t>
+    <t>wind onshore electricity near Rybnik (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Koszalin (cluster 10)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 11)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 12)</t>
+    <t>wind onshore electricity near Tarnow (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 13)</t>
+    <t>wind onshore electricity near Bielsko-Biala (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Pila (cluster 14)</t>
+    <t>wind onshore electricity near Krakow (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 15)</t>
+    <t>wind onshore electricity near Kielce (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 16)</t>
+    <t>wind onshore electricity near Zamosc (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Tarnow (cluster 17)</t>
+    <t>wind onshore electricity near Lublin (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 18)</t>
+    <t>wind onshore electricity near Lomza (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 19)</t>
+    <t>wind onshore electricity near Bialystok (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_POL_020</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rybnik (cluster 20)</t>
+    <t>wind onshore electricity near Suwalki (cluster 20)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4526,7 +4526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9E4C71-901F-4351-B311-A9CFD9D4B17E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6558FE15-93EE-422F-A93F-F68F4FE7C0FC}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6358,7 +6358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7432F9F-A752-4475-BC07-A7266FBB851F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9684A4-9612-44B0-A5CF-649FD971AC70}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7647,7 +7647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018FAFA8-8CE2-45D4-91FC-450736FFAD14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7486FD-0EE4-411B-AE6D-CE8C39687670}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EACAF63-04C0-4ADE-B0C6-DF363F428B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB160C7-1354-476E-B71D-D0586CDCBA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4526,7 +4526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6558FE15-93EE-422F-A93F-F68F4FE7C0FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BBDF007-0B63-4C3C-ABDF-D6FF61F13BFE}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6358,7 +6358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9684A4-9612-44B0-A5CF-649FD971AC70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A28E7E-98B1-47AE-BFDA-6D3968A2047B}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7647,7 +7647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7486FD-0EE4-411B-AE6D-CE8C39687670}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADEEAEFD-2B93-4F7B-AD7F-2AF13423D503}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB160C7-1354-476E-B71D-D0586CDCBA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1723BB6D-7AB5-42ED-B68C-E5694A87CA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="695">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -790,13 +790,13 @@
     <t>elc_spv_POL_002</t>
   </si>
   <si>
-    <t>solar electricity near Suwalki (cluster 2)</t>
+    <t>solar electricity near Elk (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
-    <t>solar electricity near Przemysl (cluster 3)</t>
+    <t>solar electricity near Rzeszow (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_POL_004</t>
@@ -808,19 +808,19 @@
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity near Biala Podlaska (cluster 5)</t>
+    <t>solar electricity near Lublin (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>solar electricity near Zamosc (cluster 6)</t>
+    <t>solar electricity near Lublin (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 7)</t>
+    <t>solar electricity near Stargard Szczecinski (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
@@ -832,7 +832,7 @@
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Bydgoszcz (cluster 9)</t>
+    <t>solar electricity near Torun (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
@@ -844,7 +844,7 @@
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 11)</t>
+    <t>solar electricity near Elblag (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
@@ -862,7 +862,7 @@
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Jelenia Gora (cluster 14)</t>
+    <t>solar electricity near Legnica (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
@@ -874,7 +874,7 @@
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Opole (cluster 16)</t>
+    <t>solar electricity near Wroclaw (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
@@ -892,7 +892,7 @@
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity near Kielce (cluster 19)</t>
+    <t>solar electricity near Radom (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
@@ -964,97 +964,97 @@
     <t>elc_won_POL_001</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 1)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
-    <t>wind onshore electricity near Pila (cluster 2)</t>
+    <t>wind onshore electricity near Rybnik (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
-    <t>wind onshore electricity near Torun (cluster 3)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kalisz (cluster 4)</t>
+    <t>wind onshore electricity near Poznan (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lubin (cluster 5)</t>
+    <t>wind onshore electricity near Elblag (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Legnica (cluster 6)</t>
+    <t>wind onshore electricity near Stargard Szczecinski (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 7)</t>
+    <t>wind onshore electricity near Slupsk (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 8)</t>
+    <t>wind onshore electricity near Pila (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rybnik (cluster 9)</t>
+    <t>wind onshore electricity near Bialystok (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 10)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 11)</t>
+    <t>wind onshore electricity near Siedlce (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Tarnow (cluster 12)</t>
+    <t>wind onshore electricity near Warsaw (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bielsko-Biala (cluster 13)</t>
+    <t>wind onshore electricity near Kalisz (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Krakow (cluster 14)</t>
+    <t>wind onshore electricity near Wloclawek (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kielce (cluster 15)</t>
+    <t>wind onshore electricity near Katowice (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zamosc (cluster 16)</t>
+    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
@@ -1066,19 +1066,13 @@
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lomza (cluster 18)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bialystok (cluster 19)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Suwalki (cluster 20)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 19)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4164,9 +4158,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4204,7 +4198,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4310,7 +4304,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4452,7 +4446,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4526,13 +4520,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BBDF007-0B63-4C3C-ABDF-D6FF61F13BFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D325BE-7E02-4CCB-8265-998299DC3271}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4563,19 +4557,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4586,19 +4580,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4609,19 +4603,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4632,19 +4626,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4655,19 +4649,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -4678,19 +4672,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -4701,19 +4695,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -4724,19 +4718,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -4747,19 +4741,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -4770,19 +4764,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -4793,19 +4787,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -4816,19 +4810,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -4839,19 +4833,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -4862,19 +4856,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -4885,19 +4879,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -4908,19 +4902,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -4931,19 +4925,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -4954,19 +4948,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -4977,19 +4971,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5000,19 +4994,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5023,19 +5017,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5046,19 +5040,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5069,19 +5063,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5092,19 +5086,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5115,19 +5109,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5138,19 +5132,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5161,19 +5155,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5184,19 +5178,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5207,19 +5201,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5230,19 +5224,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5253,19 +5247,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5276,19 +5270,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5299,19 +5293,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5322,19 +5316,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5345,19 +5339,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5368,19 +5362,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5391,19 +5385,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5414,19 +5408,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5437,19 +5431,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5460,19 +5454,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5483,19 +5477,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5506,19 +5500,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5529,19 +5523,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5552,19 +5546,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5575,19 +5569,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5598,19 +5592,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5621,19 +5615,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5644,19 +5638,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -5667,19 +5661,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -5690,19 +5684,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -5713,19 +5707,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -5736,19 +5730,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -5759,19 +5753,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -5782,19 +5776,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -5805,19 +5799,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -5828,19 +5822,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -5851,19 +5845,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -5874,19 +5868,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -5897,19 +5891,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -5920,19 +5914,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -5943,19 +5937,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -5966,19 +5960,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -5989,19 +5983,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6012,19 +6006,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6035,19 +6029,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6058,19 +6052,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6081,19 +6075,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6104,19 +6098,19 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H72" t="s">
         <v>195</v>
@@ -6127,19 +6121,19 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D73" t="s">
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H73" t="s">
         <v>195</v>
@@ -6150,19 +6144,19 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D74" t="s">
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H74" t="s">
         <v>195</v>
@@ -6173,19 +6167,19 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D75" t="s">
         <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H75" t="s">
         <v>195</v>
@@ -6196,19 +6190,19 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D76" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H76" t="s">
         <v>195</v>
@@ -6219,19 +6213,19 @@
         <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D77" t="s">
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H77" t="s">
         <v>195</v>
@@ -6242,19 +6236,19 @@
         <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D78" t="s">
         <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H78" t="s">
         <v>195</v>
@@ -6265,19 +6259,19 @@
         <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D79" t="s">
         <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H79" t="s">
         <v>195</v>
@@ -6288,19 +6282,19 @@
         <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D80" t="s">
         <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H80" t="s">
         <v>195</v>
@@ -6311,19 +6305,19 @@
         <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D81" t="s">
         <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H81" t="s">
         <v>195</v>
@@ -6334,19 +6328,19 @@
         <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D82" t="s">
         <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H82" t="s">
         <v>195</v>
@@ -6358,13 +6352,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A28E7E-98B1-47AE-BFDA-6D3968A2047B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB8E5D3-60F5-4E6A-A950-9E92868CAE06}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6398,13 +6392,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6413,7 +6407,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -6424,13 +6418,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6439,7 +6433,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -6450,13 +6444,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6465,7 +6459,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -6476,13 +6470,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6491,7 +6485,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -6502,13 +6496,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6517,7 +6511,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -6528,13 +6522,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6543,7 +6537,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -6554,13 +6548,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6569,7 +6563,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -6580,13 +6574,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6595,7 +6589,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -6606,13 +6600,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6621,7 +6615,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -6632,13 +6626,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6647,7 +6641,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -6658,13 +6652,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -6673,7 +6667,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -6684,13 +6678,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -6699,7 +6693,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -6710,13 +6704,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -6725,7 +6719,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -6736,13 +6730,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -6751,7 +6745,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -6762,13 +6756,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -6777,7 +6771,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -6788,13 +6782,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -6803,7 +6797,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -6814,13 +6808,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -6829,7 +6823,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -6840,13 +6834,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -6855,7 +6849,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -6866,13 +6860,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -6881,7 +6875,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -6892,13 +6886,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -6907,7 +6901,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -6918,13 +6912,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -6933,7 +6927,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -6944,13 +6938,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -6959,7 +6953,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -6970,13 +6964,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -6985,7 +6979,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -6996,13 +6990,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7011,7 +7005,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7022,13 +7016,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7037,7 +7031,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7048,13 +7042,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7063,7 +7057,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7074,13 +7068,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7089,7 +7083,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7100,13 +7094,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7115,7 +7109,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7126,13 +7120,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7141,7 +7135,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7152,13 +7146,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7167,7 +7161,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7178,13 +7172,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7193,7 +7187,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7204,13 +7198,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7219,7 +7213,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7230,13 +7224,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7245,7 +7239,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7256,13 +7250,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7271,7 +7265,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7282,13 +7276,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7297,7 +7291,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7308,13 +7302,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7323,7 +7317,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7334,13 +7328,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7349,7 +7343,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7360,13 +7354,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7375,7 +7369,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -7386,13 +7380,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7401,7 +7395,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -7412,13 +7406,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7427,7 +7421,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -7438,13 +7432,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7453,7 +7447,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -7464,13 +7458,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7479,7 +7473,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -7490,13 +7484,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7505,7 +7499,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -7516,13 +7510,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7531,7 +7525,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -7542,13 +7536,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7557,7 +7551,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -7568,13 +7562,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7583,7 +7577,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -7594,13 +7588,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7609,7 +7603,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -7620,13 +7614,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7635,7 +7629,7 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -7647,13 +7641,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADEEAEFD-2B93-4F7B-AD7F-2AF13423D503}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF01326-656F-4BB7-8D94-47ADAE58BF4A}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -7687,13 +7681,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -7702,7 +7696,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -7713,13 +7707,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -7728,7 +7722,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -7739,13 +7733,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -7754,7 +7748,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -7765,13 +7759,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -7780,7 +7774,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -7791,13 +7785,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -7806,7 +7800,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -7817,13 +7811,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -7832,7 +7826,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -7843,13 +7837,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -7858,7 +7852,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -7869,13 +7863,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -7884,7 +7878,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -7895,13 +7889,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -7910,7 +7904,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -7921,13 +7915,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -7936,7 +7930,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -7947,13 +7941,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -7962,7 +7956,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -7973,13 +7967,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -7988,7 +7982,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7999,13 +7993,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8014,7 +8008,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8025,13 +8019,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8040,7 +8034,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8051,13 +8045,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8066,7 +8060,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8077,13 +8071,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8092,7 +8086,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8103,13 +8097,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8118,7 +8112,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8129,13 +8123,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8144,7 +8138,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8155,13 +8149,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8170,7 +8164,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8181,13 +8175,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8196,7 +8190,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8207,13 +8201,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8222,7 +8216,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -8233,13 +8227,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -8248,7 +8242,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -8259,13 +8253,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8274,7 +8268,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -8285,13 +8279,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8300,7 +8294,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -8311,13 +8305,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8326,7 +8320,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -8337,13 +8331,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8352,7 +8346,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -8363,13 +8357,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8378,7 +8372,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -8389,13 +8383,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -8404,7 +8398,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -8415,13 +8409,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8430,7 +8424,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -8441,13 +8435,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -8456,7 +8450,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -8467,13 +8461,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -8482,7 +8476,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -8493,13 +8487,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -8508,7 +8502,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -8519,13 +8513,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -8534,7 +8528,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -8545,13 +8539,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -8560,7 +8554,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -8571,13 +8565,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -8586,7 +8580,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -8597,13 +8591,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -8612,7 +8606,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -8623,13 +8617,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -8638,7 +8632,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -8649,13 +8643,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -8664,7 +8658,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -8675,13 +8669,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -8690,7 +8684,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -8701,13 +8695,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -8716,7 +8710,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -8727,13 +8721,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -8742,7 +8736,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -8753,13 +8747,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -8768,7 +8762,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -8779,13 +8773,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -8794,7 +8788,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -8805,13 +8799,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -8820,7 +8814,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -8831,13 +8825,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -8846,7 +8840,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -8857,13 +8851,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -8872,7 +8866,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -8883,13 +8877,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -8898,7 +8892,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -8909,13 +8903,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -8924,7 +8918,7 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -8937,7 +8931,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S54"/>
+  <dimension ref="B3:S53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -10525,29 +10519,6 @@
         <v>35</v>
       </c>
       <c r="S53" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="54" spans="13:19">
-      <c r="M54" t="s">
-        <v>17</v>
-      </c>
-      <c r="N54" t="s">
-        <v>344</v>
-      </c>
-      <c r="O54" t="s">
-        <v>243</v>
-      </c>
-      <c r="P54" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>25</v>
-      </c>
-      <c r="R54" t="s">
-        <v>35</v>
-      </c>
-      <c r="S54" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1723BB6D-7AB5-42ED-B68C-E5694A87CA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27360764-C30E-4474-B836-841C3FD51C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="809">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -781,7 +781,7 @@
     <t>elc_spv_POL_001</t>
   </si>
   <si>
-    <t>solar electricity near Bialystok (cluster 1)</t>
+    <t>solar electricity near Bydgoszcz (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -790,115 +790,283 @@
     <t>elc_spv_POL_002</t>
   </si>
   <si>
-    <t>solar electricity near Elk (cluster 2)</t>
+    <t>solar electricity near Bialystok (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 3)</t>
+    <t>solar electricity near Gorzow Wielkopolski (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 4)</t>
+    <t>solar electricity near Walbrzych (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 5)</t>
+    <t>solar electricity near Wroclaw (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 6)</t>
+    <t>solar electricity near Walbrzych (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity near Stargard Szczecinski (cluster 7)</t>
+    <t>solar electricity near Olsztyn (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>solar electricity near Pila (cluster 8)</t>
+    <t>solar electricity near Slupsk (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Torun (cluster 9)</t>
+    <t>solar electricity near Olsztyn (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 10)</t>
+    <t>solar electricity near Jelenia Gora (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity near Elblag (cluster 11)</t>
+    <t>solar electricity near Gdansk (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>solar electricity near Poznan (cluster 12)</t>
+    <t>solar electricity near Lomza (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 13)</t>
+    <t>solar electricity near Zielona Gora (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Legnica (cluster 14)</t>
+    <t>solar electricity near Szczecin (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 15)</t>
+    <t>solar electricity near Rzeszow (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 16)</t>
+    <t>solar electricity near Suwalki (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Katowice (cluster 17)</t>
+    <t>solar electricity near Piotrkow Trybunalski (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 18)</t>
+    <t>solar electricity near Lodz (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity near Radom (cluster 19)</t>
+    <t>solar electricity near Zamosc (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 20)</t>
+    <t>solar electricity near Koszalin (cluster 20)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>solar electricity near Zielona Gora (cluster 21)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>solar electricity near Katowice (cluster 22)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>solar electricity near Tarnow (cluster 23)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>solar electricity near Chelm (cluster 24)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>solar electricity near Rzeszow (cluster 25)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>solar electricity near Kielce (cluster 26)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>solar electricity near Mielec (cluster 27)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>solar electricity near Rzeszow (cluster 28)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>solar electricity near Czestochowa (cluster 29)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>solar electricity near Torun (cluster 30)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>solar electricity near Opole (cluster 32)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>solar electricity near Kalisz (cluster 33)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>solar electricity near Koszalin (cluster 34)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>solar electricity near Warsaw (cluster 35)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>solar electricity near Katowice (cluster 36)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>solar electricity near Suwalki (cluster 37)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>solar electricity near Pila (cluster 38)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>solar electricity near Kedzierzyn-Kozle (cluster 39)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>solar electricity near Szczecin (cluster 40)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 41)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 42)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>solar electricity near Elblag (cluster 43)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>solar electricity near Plock (cluster 44)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>solar electricity near Wroclaw (cluster 45)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>solar electricity near Gdansk (cluster 46)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 47)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>solar electricity near Siedlce (cluster 48)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -916,25 +1084,25 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 3)</t>
+    <t>wind offshore electricity near Koszalin (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
-    <t>wind offshore electricity near Slupsk (cluster 4)</t>
+    <t>wind offshore electricity near Koszalin (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 5)</t>
+    <t>wind offshore electricity near Koszalin (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 6)</t>
+    <t>wind offshore electricity near Koszalin (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
@@ -946,133 +1114,307 @@
     <t>elc_wof_POL_008</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 8)</t>
+    <t>wind offshore electricity near Gdynia (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 9)</t>
+    <t>wind offshore electricity near Gdansk (cluster 9)</t>
   </si>
   <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 10)</t>
+    <t>wind offshore electricity near Gdansk (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 1)</t>
+    <t>wind onshore electricity near Bydgoszcz (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rybnik (cluster 2)</t>
+    <t>wind onshore electricity near Bialystok (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 3)</t>
+    <t>wind onshore electricity near Gorzow Wielkopolski (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Poznan (cluster 4)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Elblag (cluster 5)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Stargard Szczecinski (cluster 6)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Slupsk (cluster 7)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Pila (cluster 8)</t>
+    <t>wind onshore electricity near Slupsk (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bialystok (cluster 9)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 10)</t>
+    <t>wind onshore electricity near Jelenia Gora (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Siedlce (cluster 11)</t>
+    <t>wind onshore electricity near Gdansk (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 12)</t>
+    <t>wind onshore electricity near Lomza (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kalisz (cluster 13)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wloclawek (cluster 14)</t>
+    <t>wind onshore electricity near Szczecin (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 15)</t>
+    <t>wind onshore electricity near Przemysl (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 16)</t>
+    <t>wind onshore electricity near Suwalki (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lublin (cluster 17)</t>
+    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 18)</t>
+    <t>wind onshore electricity near Lodz (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 19)</t>
+    <t>wind onshore electricity near Zamosc (cluster 19)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Koszalin (cluster 20)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Zielona Gora (cluster 21)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Katowice (cluster 22)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Tarnow (cluster 23)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Chelm (cluster 24)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Rzeszow (cluster 25)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Kielce (cluster 26)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Mielec (cluster 27)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Rzeszow (cluster 28)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Czestochowa (cluster 29)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Torun (cluster 30)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Opole (cluster 32)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Konin (cluster 33)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Koszalin (cluster 34)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Warsaw (cluster 35)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Katowice (cluster 36)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Suwalki (cluster 37)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Pila (cluster 38)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 39)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Szczecin (cluster 40)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 41)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 42)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Elblag (cluster 43)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Plock (cluster 44)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Wroclaw (cluster 45)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Gdansk (cluster 46)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 47)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Siedlce (cluster 48)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4158,9 +4500,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4198,7 +4540,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4304,7 +4646,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4446,7 +4788,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4520,13 +4862,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D325BE-7E02-4CCB-8265-998299DC3271}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C26E361-6705-4186-BAC4-551AC7C1EA7E}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4557,19 +4899,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>538</v>
+        <v>652</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>539</v>
+        <v>653</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4580,19 +4922,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>541</v>
+        <v>655</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>542</v>
+        <v>656</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4603,19 +4945,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>543</v>
+        <v>657</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>544</v>
+        <v>658</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4626,19 +4968,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>545</v>
+        <v>659</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>546</v>
+        <v>660</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4649,19 +4991,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>547</v>
+        <v>661</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>548</v>
+        <v>662</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -4672,19 +5014,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>549</v>
+        <v>663</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>550</v>
+        <v>664</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -4695,19 +5037,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>551</v>
+        <v>665</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>552</v>
+        <v>666</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -4718,19 +5060,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>553</v>
+        <v>667</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>554</v>
+        <v>668</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -4741,19 +5083,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>555</v>
+        <v>669</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>556</v>
+        <v>670</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -4764,19 +5106,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>557</v>
+        <v>671</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>558</v>
+        <v>672</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -4787,19 +5129,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>559</v>
+        <v>673</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>560</v>
+        <v>674</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -4810,19 +5152,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>561</v>
+        <v>675</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>562</v>
+        <v>676</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -4833,19 +5175,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>563</v>
+        <v>677</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>564</v>
+        <v>678</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -4856,19 +5198,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>565</v>
+        <v>679</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>566</v>
+        <v>680</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -4879,19 +5221,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>567</v>
+        <v>681</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>568</v>
+        <v>682</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -4902,19 +5244,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>569</v>
+        <v>683</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>570</v>
+        <v>684</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -4925,19 +5267,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>571</v>
+        <v>685</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>572</v>
+        <v>686</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -4948,19 +5290,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>573</v>
+        <v>687</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>574</v>
+        <v>688</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -4971,19 +5313,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>575</v>
+        <v>689</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>576</v>
+        <v>690</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -4994,19 +5336,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>577</v>
+        <v>691</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>578</v>
+        <v>692</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5017,19 +5359,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>579</v>
+        <v>693</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>580</v>
+        <v>694</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5040,19 +5382,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>581</v>
+        <v>695</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>582</v>
+        <v>696</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5063,19 +5405,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>583</v>
+        <v>697</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>584</v>
+        <v>698</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5086,19 +5428,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>585</v>
+        <v>699</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>586</v>
+        <v>700</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5109,19 +5451,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>587</v>
+        <v>701</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>588</v>
+        <v>702</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5132,19 +5474,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>589</v>
+        <v>703</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>590</v>
+        <v>704</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5155,19 +5497,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>591</v>
+        <v>705</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>592</v>
+        <v>706</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5178,19 +5520,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>593</v>
+        <v>707</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>594</v>
+        <v>708</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5201,19 +5543,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>595</v>
+        <v>709</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>596</v>
+        <v>710</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5224,19 +5566,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>597</v>
+        <v>711</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>598</v>
+        <v>712</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5247,19 +5589,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>599</v>
+        <v>713</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>600</v>
+        <v>714</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5270,19 +5612,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>601</v>
+        <v>715</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>602</v>
+        <v>716</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5293,19 +5635,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>603</v>
+        <v>717</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>604</v>
+        <v>718</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5316,19 +5658,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>605</v>
+        <v>719</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>606</v>
+        <v>720</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5339,19 +5681,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>607</v>
+        <v>721</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>608</v>
+        <v>722</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5362,19 +5704,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>609</v>
+        <v>723</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>610</v>
+        <v>724</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5385,19 +5727,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>611</v>
+        <v>725</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>612</v>
+        <v>726</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5408,19 +5750,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>613</v>
+        <v>727</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>614</v>
+        <v>728</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5431,19 +5773,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>615</v>
+        <v>729</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>616</v>
+        <v>730</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5454,19 +5796,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>617</v>
+        <v>731</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>618</v>
+        <v>732</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5477,19 +5819,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>619</v>
+        <v>733</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>620</v>
+        <v>734</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5500,19 +5842,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>621</v>
+        <v>735</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>622</v>
+        <v>736</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5523,19 +5865,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>623</v>
+        <v>737</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>624</v>
+        <v>738</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5546,19 +5888,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>625</v>
+        <v>739</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>626</v>
+        <v>740</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5569,19 +5911,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>627</v>
+        <v>741</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>628</v>
+        <v>742</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5592,19 +5934,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>629</v>
+        <v>743</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>630</v>
+        <v>744</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5615,19 +5957,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>631</v>
+        <v>745</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>632</v>
+        <v>746</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5638,19 +5980,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>633</v>
+        <v>747</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>634</v>
+        <v>748</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -5661,19 +6003,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>635</v>
+        <v>749</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>636</v>
+        <v>750</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -5684,19 +6026,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>637</v>
+        <v>751</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>638</v>
+        <v>752</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -5707,19 +6049,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>639</v>
+        <v>753</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>640</v>
+        <v>754</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -5730,19 +6072,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>641</v>
+        <v>755</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>642</v>
+        <v>756</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -5753,19 +6095,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>643</v>
+        <v>757</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>644</v>
+        <v>758</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -5776,19 +6118,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>645</v>
+        <v>759</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>646</v>
+        <v>760</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -5799,19 +6141,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>647</v>
+        <v>761</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>648</v>
+        <v>762</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -5822,19 +6164,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>649</v>
+        <v>763</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>650</v>
+        <v>764</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -5845,19 +6187,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>651</v>
+        <v>765</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>652</v>
+        <v>766</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -5868,19 +6210,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>653</v>
+        <v>767</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>654</v>
+        <v>768</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -5891,19 +6233,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>655</v>
+        <v>769</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>656</v>
+        <v>770</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -5914,19 +6256,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>657</v>
+        <v>771</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>658</v>
+        <v>772</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -5937,19 +6279,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>659</v>
+        <v>773</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>660</v>
+        <v>774</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -5960,19 +6302,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>661</v>
+        <v>775</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>662</v>
+        <v>776</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -5983,19 +6325,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>663</v>
+        <v>777</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>664</v>
+        <v>778</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6006,19 +6348,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>665</v>
+        <v>779</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>666</v>
+        <v>780</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6029,19 +6371,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>667</v>
+        <v>781</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>668</v>
+        <v>782</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6052,19 +6394,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>669</v>
+        <v>783</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>670</v>
+        <v>784</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6075,19 +6417,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>671</v>
+        <v>785</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>672</v>
+        <v>786</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6098,19 +6440,19 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>673</v>
+        <v>787</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>674</v>
+        <v>788</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H72" t="s">
         <v>195</v>
@@ -6121,19 +6463,19 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>675</v>
+        <v>789</v>
       </c>
       <c r="D73" t="s">
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>676</v>
+        <v>790</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H73" t="s">
         <v>195</v>
@@ -6144,19 +6486,19 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>677</v>
+        <v>791</v>
       </c>
       <c r="D74" t="s">
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>678</v>
+        <v>792</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H74" t="s">
         <v>195</v>
@@ -6167,19 +6509,19 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>679</v>
+        <v>793</v>
       </c>
       <c r="D75" t="s">
         <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>680</v>
+        <v>794</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H75" t="s">
         <v>195</v>
@@ -6190,19 +6532,19 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>681</v>
+        <v>795</v>
       </c>
       <c r="D76" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>682</v>
+        <v>796</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H76" t="s">
         <v>195</v>
@@ -6213,19 +6555,19 @@
         <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>683</v>
+        <v>797</v>
       </c>
       <c r="D77" t="s">
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>684</v>
+        <v>798</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H77" t="s">
         <v>195</v>
@@ -6236,19 +6578,19 @@
         <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>685</v>
+        <v>799</v>
       </c>
       <c r="D78" t="s">
         <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>686</v>
+        <v>800</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H78" t="s">
         <v>195</v>
@@ -6259,19 +6601,19 @@
         <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>687</v>
+        <v>801</v>
       </c>
       <c r="D79" t="s">
         <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>688</v>
+        <v>802</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H79" t="s">
         <v>195</v>
@@ -6282,19 +6624,19 @@
         <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>689</v>
+        <v>803</v>
       </c>
       <c r="D80" t="s">
         <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>690</v>
+        <v>804</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H80" t="s">
         <v>195</v>
@@ -6305,19 +6647,19 @@
         <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>691</v>
+        <v>805</v>
       </c>
       <c r="D81" t="s">
         <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>692</v>
+        <v>806</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H81" t="s">
         <v>195</v>
@@ -6328,19 +6670,19 @@
         <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>693</v>
+        <v>807</v>
       </c>
       <c r="D82" t="s">
         <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>694</v>
+        <v>808</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="H82" t="s">
         <v>195</v>
@@ -6352,13 +6694,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB8E5D3-60F5-4E6A-A950-9E92868CAE06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225779BF-CE1E-4C54-B228-6D218E664B9F}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6392,13 +6734,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>556</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>443</v>
+        <v>557</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6407,7 +6749,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -6418,13 +6760,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>444</v>
+        <v>558</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>445</v>
+        <v>559</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6433,7 +6775,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -6444,13 +6786,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>446</v>
+        <v>560</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>447</v>
+        <v>561</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6459,7 +6801,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -6470,13 +6812,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>448</v>
+        <v>562</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>449</v>
+        <v>563</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6485,7 +6827,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -6496,13 +6838,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>450</v>
+        <v>564</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>451</v>
+        <v>565</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6511,7 +6853,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -6522,13 +6864,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>452</v>
+        <v>566</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>453</v>
+        <v>567</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6537,7 +6879,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -6548,13 +6890,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>454</v>
+        <v>568</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>455</v>
+        <v>569</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6563,7 +6905,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -6574,13 +6916,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>456</v>
+        <v>570</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>457</v>
+        <v>571</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6589,7 +6931,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -6600,13 +6942,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>458</v>
+        <v>572</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>459</v>
+        <v>573</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6615,7 +6957,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -6626,13 +6968,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>460</v>
+        <v>574</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>461</v>
+        <v>575</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6641,7 +6983,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -6652,13 +6994,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>462</v>
+        <v>576</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -6667,7 +7009,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -6678,13 +7020,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>464</v>
+        <v>578</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>465</v>
+        <v>579</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -6693,7 +7035,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -6704,13 +7046,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>466</v>
+        <v>580</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>467</v>
+        <v>581</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -6719,7 +7061,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -6730,13 +7072,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>468</v>
+        <v>582</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>469</v>
+        <v>583</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -6745,7 +7087,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -6756,13 +7098,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>470</v>
+        <v>584</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>471</v>
+        <v>585</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -6771,7 +7113,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -6782,13 +7124,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>472</v>
+        <v>586</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>473</v>
+        <v>587</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -6797,7 +7139,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -6808,13 +7150,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>474</v>
+        <v>588</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>475</v>
+        <v>589</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -6823,7 +7165,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -6834,13 +7176,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>476</v>
+        <v>590</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>477</v>
+        <v>591</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -6849,7 +7191,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -6860,13 +7202,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>478</v>
+        <v>592</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>479</v>
+        <v>593</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -6875,7 +7217,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -6886,13 +7228,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>480</v>
+        <v>594</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>481</v>
+        <v>595</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -6901,7 +7243,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -6912,13 +7254,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>482</v>
+        <v>596</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>483</v>
+        <v>597</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -6927,7 +7269,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -6938,13 +7280,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>485</v>
+        <v>599</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -6953,7 +7295,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -6964,13 +7306,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>486</v>
+        <v>600</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>487</v>
+        <v>601</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -6979,7 +7321,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -6990,13 +7332,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>488</v>
+        <v>602</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>489</v>
+        <v>603</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7005,7 +7347,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7016,13 +7358,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>490</v>
+        <v>604</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>491</v>
+        <v>605</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7031,7 +7373,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7042,13 +7384,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>492</v>
+        <v>606</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>493</v>
+        <v>607</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7057,7 +7399,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7068,13 +7410,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>494</v>
+        <v>608</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>495</v>
+        <v>609</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7083,7 +7425,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7094,13 +7436,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>496</v>
+        <v>610</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>497</v>
+        <v>611</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7109,7 +7451,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7120,13 +7462,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>498</v>
+        <v>612</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>499</v>
+        <v>613</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7135,7 +7477,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7146,13 +7488,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>500</v>
+        <v>614</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>501</v>
+        <v>615</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7161,7 +7503,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7172,13 +7514,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>502</v>
+        <v>616</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>503</v>
+        <v>617</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7187,7 +7529,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7198,13 +7540,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>504</v>
+        <v>618</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>505</v>
+        <v>619</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7213,7 +7555,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7224,13 +7566,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>506</v>
+        <v>620</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>507</v>
+        <v>621</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7239,7 +7581,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7250,13 +7592,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>508</v>
+        <v>622</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>509</v>
+        <v>623</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7265,7 +7607,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7276,13 +7618,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>510</v>
+        <v>624</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>511</v>
+        <v>625</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7291,7 +7633,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7302,13 +7644,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>512</v>
+        <v>626</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>513</v>
+        <v>627</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7317,7 +7659,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7328,13 +7670,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>514</v>
+        <v>628</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>515</v>
+        <v>629</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7343,7 +7685,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7354,13 +7696,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>516</v>
+        <v>630</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>517</v>
+        <v>631</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7369,7 +7711,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -7380,13 +7722,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>518</v>
+        <v>632</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>519</v>
+        <v>633</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7395,7 +7737,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -7406,13 +7748,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>520</v>
+        <v>634</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>521</v>
+        <v>635</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7421,7 +7763,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -7432,13 +7774,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>522</v>
+        <v>636</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>523</v>
+        <v>637</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7447,7 +7789,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -7458,13 +7800,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>524</v>
+        <v>638</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>525</v>
+        <v>639</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7473,7 +7815,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -7484,13 +7826,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>526</v>
+        <v>640</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>527</v>
+        <v>641</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7499,7 +7841,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -7510,13 +7852,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>528</v>
+        <v>642</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>529</v>
+        <v>643</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7525,7 +7867,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -7536,13 +7878,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>530</v>
+        <v>644</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>531</v>
+        <v>645</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7551,7 +7893,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -7562,13 +7904,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>532</v>
+        <v>646</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>533</v>
+        <v>647</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7577,7 +7919,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -7588,13 +7930,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>534</v>
+        <v>648</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>535</v>
+        <v>649</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7603,7 +7945,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -7614,13 +7956,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>536</v>
+        <v>650</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>537</v>
+        <v>651</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7629,7 +7971,7 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -7641,13 +7983,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF01326-656F-4BB7-8D94-47ADAE58BF4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A69EB4-A378-4D87-BFA0-7658C5139A2D}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -7681,13 +8023,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>459</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>346</v>
+        <v>460</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -7696,7 +8038,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -7707,13 +8049,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>348</v>
+        <v>462</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>349</v>
+        <v>463</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -7722,7 +8064,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -7733,13 +8075,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>464</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>351</v>
+        <v>465</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -7748,7 +8090,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -7759,13 +8101,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>352</v>
+        <v>466</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>353</v>
+        <v>467</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -7774,7 +8116,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -7785,13 +8127,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>354</v>
+        <v>468</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>355</v>
+        <v>469</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -7800,7 +8142,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -7811,13 +8153,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>356</v>
+        <v>470</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>357</v>
+        <v>471</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -7826,7 +8168,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -7837,13 +8179,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>472</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>359</v>
+        <v>473</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -7852,7 +8194,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -7863,13 +8205,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>360</v>
+        <v>474</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>361</v>
+        <v>475</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -7878,7 +8220,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -7889,13 +8231,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>476</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>363</v>
+        <v>477</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -7904,7 +8246,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -7915,13 +8257,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>364</v>
+        <v>478</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>365</v>
+        <v>479</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -7930,7 +8272,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -7941,13 +8283,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>366</v>
+        <v>480</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>367</v>
+        <v>481</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -7956,7 +8298,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -7967,13 +8309,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>368</v>
+        <v>482</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>369</v>
+        <v>483</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -7982,7 +8324,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7993,13 +8335,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>370</v>
+        <v>484</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>371</v>
+        <v>485</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8008,7 +8350,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8019,13 +8361,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>372</v>
+        <v>486</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>373</v>
+        <v>487</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8034,7 +8376,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8045,13 +8387,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>374</v>
+        <v>488</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>375</v>
+        <v>489</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8060,7 +8402,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8071,13 +8413,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>490</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>377</v>
+        <v>491</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8086,7 +8428,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8097,13 +8439,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>378</v>
+        <v>492</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>379</v>
+        <v>493</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8112,7 +8454,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8123,13 +8465,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>380</v>
+        <v>494</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>381</v>
+        <v>495</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8138,7 +8480,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8149,13 +8491,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>382</v>
+        <v>496</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>383</v>
+        <v>497</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8164,7 +8506,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8175,13 +8517,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>384</v>
+        <v>498</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>385</v>
+        <v>499</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8190,7 +8532,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8201,13 +8543,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>386</v>
+        <v>500</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>387</v>
+        <v>501</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8216,7 +8558,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -8227,13 +8569,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>388</v>
+        <v>502</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>389</v>
+        <v>503</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -8242,7 +8584,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -8253,13 +8595,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>390</v>
+        <v>504</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>391</v>
+        <v>505</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8268,7 +8610,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -8279,13 +8621,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>392</v>
+        <v>506</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>393</v>
+        <v>507</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8294,7 +8636,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -8305,13 +8647,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>394</v>
+        <v>508</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>395</v>
+        <v>509</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8320,7 +8662,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -8331,13 +8673,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>396</v>
+        <v>510</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>397</v>
+        <v>511</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8346,7 +8688,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -8357,13 +8699,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>398</v>
+        <v>512</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>399</v>
+        <v>513</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8372,7 +8714,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -8383,13 +8725,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>400</v>
+        <v>514</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -8398,7 +8740,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -8409,13 +8751,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>402</v>
+        <v>516</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>403</v>
+        <v>517</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8424,7 +8766,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -8435,13 +8777,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>404</v>
+        <v>518</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>405</v>
+        <v>519</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -8450,7 +8792,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -8461,13 +8803,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>406</v>
+        <v>520</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>407</v>
+        <v>521</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -8476,7 +8818,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -8487,13 +8829,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>408</v>
+        <v>522</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>409</v>
+        <v>523</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -8502,7 +8844,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -8513,13 +8855,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>410</v>
+        <v>524</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>411</v>
+        <v>525</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -8528,7 +8870,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -8539,13 +8881,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>412</v>
+        <v>526</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>413</v>
+        <v>527</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -8554,7 +8896,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -8565,13 +8907,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>414</v>
+        <v>528</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>415</v>
+        <v>529</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -8580,7 +8922,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -8591,13 +8933,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>416</v>
+        <v>530</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>417</v>
+        <v>531</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -8606,7 +8948,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -8617,13 +8959,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>418</v>
+        <v>532</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>419</v>
+        <v>533</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -8632,7 +8974,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -8643,13 +8985,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>420</v>
+        <v>534</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>421</v>
+        <v>535</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -8658,7 +9000,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -8669,13 +9011,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>422</v>
+        <v>536</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>423</v>
+        <v>537</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -8684,7 +9026,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -8695,13 +9037,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>424</v>
+        <v>538</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>425</v>
+        <v>539</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -8710,7 +9052,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -8721,13 +9063,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>426</v>
+        <v>540</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>427</v>
+        <v>541</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -8736,7 +9078,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -8747,13 +9089,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>428</v>
+        <v>542</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>429</v>
+        <v>543</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -8762,7 +9104,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -8773,13 +9115,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>430</v>
+        <v>544</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>431</v>
+        <v>545</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -8788,7 +9130,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -8799,13 +9141,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>432</v>
+        <v>546</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>433</v>
+        <v>547</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -8814,7 +9156,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -8825,13 +9167,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>434</v>
+        <v>548</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>435</v>
+        <v>549</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -8840,7 +9182,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -8851,13 +9193,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>436</v>
+        <v>550</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>437</v>
+        <v>551</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -8866,7 +9208,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -8877,13 +9219,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>438</v>
+        <v>552</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>439</v>
+        <v>553</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -8892,7 +9234,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -8903,13 +9245,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>440</v>
+        <v>554</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>441</v>
+        <v>555</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -8918,7 +9260,7 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>347</v>
+        <v>461</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -8931,7 +9273,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S53"/>
+  <dimension ref="B3:S110"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -10519,6 +10861,1317 @@
         <v>35</v>
       </c>
       <c r="S53" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="13:19">
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>344</v>
+      </c>
+      <c r="O54" t="s">
+        <v>243</v>
+      </c>
+      <c r="P54" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>25</v>
+      </c>
+      <c r="R54" t="s">
+        <v>35</v>
+      </c>
+      <c r="S54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="13:19">
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>346</v>
+      </c>
+      <c r="O55" t="s">
+        <v>243</v>
+      </c>
+      <c r="P55" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>25</v>
+      </c>
+      <c r="R55" t="s">
+        <v>35</v>
+      </c>
+      <c r="S55" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="13:19">
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>348</v>
+      </c>
+      <c r="O56" t="s">
+        <v>243</v>
+      </c>
+      <c r="P56" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>25</v>
+      </c>
+      <c r="R56" t="s">
+        <v>35</v>
+      </c>
+      <c r="S56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="13:19">
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>350</v>
+      </c>
+      <c r="O57" t="s">
+        <v>243</v>
+      </c>
+      <c r="P57" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>25</v>
+      </c>
+      <c r="R57" t="s">
+        <v>35</v>
+      </c>
+      <c r="S57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="13:19">
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>352</v>
+      </c>
+      <c r="O58" t="s">
+        <v>243</v>
+      </c>
+      <c r="P58" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>25</v>
+      </c>
+      <c r="R58" t="s">
+        <v>35</v>
+      </c>
+      <c r="S58" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="13:19">
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>354</v>
+      </c>
+      <c r="O59" t="s">
+        <v>243</v>
+      </c>
+      <c r="P59" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>25</v>
+      </c>
+      <c r="R59" t="s">
+        <v>35</v>
+      </c>
+      <c r="S59" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="13:19">
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>356</v>
+      </c>
+      <c r="O60" t="s">
+        <v>243</v>
+      </c>
+      <c r="P60" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>25</v>
+      </c>
+      <c r="R60" t="s">
+        <v>35</v>
+      </c>
+      <c r="S60" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="13:19">
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>358</v>
+      </c>
+      <c r="O61" t="s">
+        <v>243</v>
+      </c>
+      <c r="P61" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>25</v>
+      </c>
+      <c r="R61" t="s">
+        <v>35</v>
+      </c>
+      <c r="S61" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="62" spans="13:19">
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>360</v>
+      </c>
+      <c r="O62" t="s">
+        <v>243</v>
+      </c>
+      <c r="P62" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>25</v>
+      </c>
+      <c r="R62" t="s">
+        <v>35</v>
+      </c>
+      <c r="S62" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="63" spans="13:19">
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>362</v>
+      </c>
+      <c r="O63" t="s">
+        <v>243</v>
+      </c>
+      <c r="P63" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>25</v>
+      </c>
+      <c r="R63" t="s">
+        <v>35</v>
+      </c>
+      <c r="S63" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="64" spans="13:19">
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>364</v>
+      </c>
+      <c r="O64" t="s">
+        <v>243</v>
+      </c>
+      <c r="P64" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>25</v>
+      </c>
+      <c r="R64" t="s">
+        <v>35</v>
+      </c>
+      <c r="S64" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="65" spans="13:19">
+      <c r="M65" t="s">
+        <v>17</v>
+      </c>
+      <c r="N65" t="s">
+        <v>366</v>
+      </c>
+      <c r="O65" t="s">
+        <v>243</v>
+      </c>
+      <c r="P65" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>25</v>
+      </c>
+      <c r="R65" t="s">
+        <v>35</v>
+      </c>
+      <c r="S65" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" spans="13:19">
+      <c r="M66" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" t="s">
+        <v>368</v>
+      </c>
+      <c r="O66" t="s">
+        <v>243</v>
+      </c>
+      <c r="P66" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>25</v>
+      </c>
+      <c r="R66" t="s">
+        <v>35</v>
+      </c>
+      <c r="S66" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="67" spans="13:19">
+      <c r="M67" t="s">
+        <v>17</v>
+      </c>
+      <c r="N67" t="s">
+        <v>370</v>
+      </c>
+      <c r="O67" t="s">
+        <v>243</v>
+      </c>
+      <c r="P67" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>25</v>
+      </c>
+      <c r="R67" t="s">
+        <v>35</v>
+      </c>
+      <c r="S67" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="68" spans="13:19">
+      <c r="M68" t="s">
+        <v>17</v>
+      </c>
+      <c r="N68" t="s">
+        <v>372</v>
+      </c>
+      <c r="O68" t="s">
+        <v>243</v>
+      </c>
+      <c r="P68" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>25</v>
+      </c>
+      <c r="R68" t="s">
+        <v>35</v>
+      </c>
+      <c r="S68" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="69" spans="13:19">
+      <c r="M69" t="s">
+        <v>17</v>
+      </c>
+      <c r="N69" t="s">
+        <v>374</v>
+      </c>
+      <c r="O69" t="s">
+        <v>243</v>
+      </c>
+      <c r="P69" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>25</v>
+      </c>
+      <c r="R69" t="s">
+        <v>35</v>
+      </c>
+      <c r="S69" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="70" spans="13:19">
+      <c r="M70" t="s">
+        <v>17</v>
+      </c>
+      <c r="N70" t="s">
+        <v>376</v>
+      </c>
+      <c r="O70" t="s">
+        <v>243</v>
+      </c>
+      <c r="P70" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>25</v>
+      </c>
+      <c r="R70" t="s">
+        <v>35</v>
+      </c>
+      <c r="S70" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="71" spans="13:19">
+      <c r="M71" t="s">
+        <v>17</v>
+      </c>
+      <c r="N71" t="s">
+        <v>378</v>
+      </c>
+      <c r="O71" t="s">
+        <v>243</v>
+      </c>
+      <c r="P71" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>25</v>
+      </c>
+      <c r="R71" t="s">
+        <v>35</v>
+      </c>
+      <c r="S71" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="72" spans="13:19">
+      <c r="M72" t="s">
+        <v>17</v>
+      </c>
+      <c r="N72" t="s">
+        <v>380</v>
+      </c>
+      <c r="O72" t="s">
+        <v>243</v>
+      </c>
+      <c r="P72" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>25</v>
+      </c>
+      <c r="R72" t="s">
+        <v>35</v>
+      </c>
+      <c r="S72" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="73" spans="13:19">
+      <c r="M73" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73" t="s">
+        <v>382</v>
+      </c>
+      <c r="O73" t="s">
+        <v>243</v>
+      </c>
+      <c r="P73" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>25</v>
+      </c>
+      <c r="R73" t="s">
+        <v>35</v>
+      </c>
+      <c r="S73" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="74" spans="13:19">
+      <c r="M74" t="s">
+        <v>17</v>
+      </c>
+      <c r="N74" t="s">
+        <v>384</v>
+      </c>
+      <c r="O74" t="s">
+        <v>243</v>
+      </c>
+      <c r="P74" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>25</v>
+      </c>
+      <c r="R74" t="s">
+        <v>35</v>
+      </c>
+      <c r="S74" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75" spans="13:19">
+      <c r="M75" t="s">
+        <v>17</v>
+      </c>
+      <c r="N75" t="s">
+        <v>386</v>
+      </c>
+      <c r="O75" t="s">
+        <v>243</v>
+      </c>
+      <c r="P75" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>25</v>
+      </c>
+      <c r="R75" t="s">
+        <v>35</v>
+      </c>
+      <c r="S75" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="76" spans="13:19">
+      <c r="M76" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" t="s">
+        <v>388</v>
+      </c>
+      <c r="O76" t="s">
+        <v>243</v>
+      </c>
+      <c r="P76" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>25</v>
+      </c>
+      <c r="R76" t="s">
+        <v>35</v>
+      </c>
+      <c r="S76" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="13:19">
+      <c r="M77" t="s">
+        <v>17</v>
+      </c>
+      <c r="N77" t="s">
+        <v>390</v>
+      </c>
+      <c r="O77" t="s">
+        <v>243</v>
+      </c>
+      <c r="P77" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>25</v>
+      </c>
+      <c r="R77" t="s">
+        <v>35</v>
+      </c>
+      <c r="S77" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="78" spans="13:19">
+      <c r="M78" t="s">
+        <v>17</v>
+      </c>
+      <c r="N78" t="s">
+        <v>392</v>
+      </c>
+      <c r="O78" t="s">
+        <v>243</v>
+      </c>
+      <c r="P78" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>25</v>
+      </c>
+      <c r="R78" t="s">
+        <v>35</v>
+      </c>
+      <c r="S78" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="79" spans="13:19">
+      <c r="M79" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79" t="s">
+        <v>394</v>
+      </c>
+      <c r="O79" t="s">
+        <v>243</v>
+      </c>
+      <c r="P79" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>25</v>
+      </c>
+      <c r="R79" t="s">
+        <v>35</v>
+      </c>
+      <c r="S79" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="80" spans="13:19">
+      <c r="M80" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80" t="s">
+        <v>396</v>
+      </c>
+      <c r="O80" t="s">
+        <v>243</v>
+      </c>
+      <c r="P80" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>25</v>
+      </c>
+      <c r="R80" t="s">
+        <v>35</v>
+      </c>
+      <c r="S80" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81" spans="13:19">
+      <c r="M81" t="s">
+        <v>17</v>
+      </c>
+      <c r="N81" t="s">
+        <v>398</v>
+      </c>
+      <c r="O81" t="s">
+        <v>243</v>
+      </c>
+      <c r="P81" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>25</v>
+      </c>
+      <c r="R81" t="s">
+        <v>35</v>
+      </c>
+      <c r="S81" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="82" spans="13:19">
+      <c r="M82" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82" t="s">
+        <v>400</v>
+      </c>
+      <c r="O82" t="s">
+        <v>243</v>
+      </c>
+      <c r="P82" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>25</v>
+      </c>
+      <c r="R82" t="s">
+        <v>35</v>
+      </c>
+      <c r="S82" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="83" spans="13:19">
+      <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" t="s">
+        <v>402</v>
+      </c>
+      <c r="O83" t="s">
+        <v>243</v>
+      </c>
+      <c r="P83" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>25</v>
+      </c>
+      <c r="R83" t="s">
+        <v>35</v>
+      </c>
+      <c r="S83" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="84" spans="13:19">
+      <c r="M84" t="s">
+        <v>17</v>
+      </c>
+      <c r="N84" t="s">
+        <v>404</v>
+      </c>
+      <c r="O84" t="s">
+        <v>243</v>
+      </c>
+      <c r="P84" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>25</v>
+      </c>
+      <c r="R84" t="s">
+        <v>35</v>
+      </c>
+      <c r="S84" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="85" spans="13:19">
+      <c r="M85" t="s">
+        <v>17</v>
+      </c>
+      <c r="N85" t="s">
+        <v>406</v>
+      </c>
+      <c r="O85" t="s">
+        <v>243</v>
+      </c>
+      <c r="P85" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>25</v>
+      </c>
+      <c r="R85" t="s">
+        <v>35</v>
+      </c>
+      <c r="S85" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="86" spans="13:19">
+      <c r="M86" t="s">
+        <v>17</v>
+      </c>
+      <c r="N86" t="s">
+        <v>408</v>
+      </c>
+      <c r="O86" t="s">
+        <v>243</v>
+      </c>
+      <c r="P86" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>25</v>
+      </c>
+      <c r="R86" t="s">
+        <v>35</v>
+      </c>
+      <c r="S86" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="87" spans="13:19">
+      <c r="M87" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" t="s">
+        <v>410</v>
+      </c>
+      <c r="O87" t="s">
+        <v>243</v>
+      </c>
+      <c r="P87" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>25</v>
+      </c>
+      <c r="R87" t="s">
+        <v>35</v>
+      </c>
+      <c r="S87" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="88" spans="13:19">
+      <c r="M88" t="s">
+        <v>17</v>
+      </c>
+      <c r="N88" t="s">
+        <v>412</v>
+      </c>
+      <c r="O88" t="s">
+        <v>243</v>
+      </c>
+      <c r="P88" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>25</v>
+      </c>
+      <c r="R88" t="s">
+        <v>35</v>
+      </c>
+      <c r="S88" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="89" spans="13:19">
+      <c r="M89" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>414</v>
+      </c>
+      <c r="O89" t="s">
+        <v>243</v>
+      </c>
+      <c r="P89" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>25</v>
+      </c>
+      <c r="R89" t="s">
+        <v>35</v>
+      </c>
+      <c r="S89" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="90" spans="13:19">
+      <c r="M90" t="s">
+        <v>17</v>
+      </c>
+      <c r="N90" t="s">
+        <v>416</v>
+      </c>
+      <c r="O90" t="s">
+        <v>243</v>
+      </c>
+      <c r="P90" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>25</v>
+      </c>
+      <c r="R90" t="s">
+        <v>35</v>
+      </c>
+      <c r="S90" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="91" spans="13:19">
+      <c r="M91" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91" t="s">
+        <v>418</v>
+      </c>
+      <c r="O91" t="s">
+        <v>243</v>
+      </c>
+      <c r="P91" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>25</v>
+      </c>
+      <c r="R91" t="s">
+        <v>35</v>
+      </c>
+      <c r="S91" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="92" spans="13:19">
+      <c r="M92" t="s">
+        <v>17</v>
+      </c>
+      <c r="N92" t="s">
+        <v>420</v>
+      </c>
+      <c r="O92" t="s">
+        <v>243</v>
+      </c>
+      <c r="P92" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R92" t="s">
+        <v>35</v>
+      </c>
+      <c r="S92" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="93" spans="13:19">
+      <c r="M93" t="s">
+        <v>17</v>
+      </c>
+      <c r="N93" t="s">
+        <v>422</v>
+      </c>
+      <c r="O93" t="s">
+        <v>243</v>
+      </c>
+      <c r="P93" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>25</v>
+      </c>
+      <c r="R93" t="s">
+        <v>35</v>
+      </c>
+      <c r="S93" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="94" spans="13:19">
+      <c r="M94" t="s">
+        <v>17</v>
+      </c>
+      <c r="N94" t="s">
+        <v>424</v>
+      </c>
+      <c r="O94" t="s">
+        <v>243</v>
+      </c>
+      <c r="P94" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>25</v>
+      </c>
+      <c r="R94" t="s">
+        <v>35</v>
+      </c>
+      <c r="S94" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="95" spans="13:19">
+      <c r="M95" t="s">
+        <v>17</v>
+      </c>
+      <c r="N95" t="s">
+        <v>426</v>
+      </c>
+      <c r="O95" t="s">
+        <v>243</v>
+      </c>
+      <c r="P95" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>25</v>
+      </c>
+      <c r="R95" t="s">
+        <v>35</v>
+      </c>
+      <c r="S95" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="96" spans="13:19">
+      <c r="M96" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" t="s">
+        <v>428</v>
+      </c>
+      <c r="O96" t="s">
+        <v>243</v>
+      </c>
+      <c r="P96" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>25</v>
+      </c>
+      <c r="R96" t="s">
+        <v>35</v>
+      </c>
+      <c r="S96" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="97" spans="13:19">
+      <c r="M97" t="s">
+        <v>17</v>
+      </c>
+      <c r="N97" t="s">
+        <v>430</v>
+      </c>
+      <c r="O97" t="s">
+        <v>243</v>
+      </c>
+      <c r="P97" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>25</v>
+      </c>
+      <c r="R97" t="s">
+        <v>35</v>
+      </c>
+      <c r="S97" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="98" spans="13:19">
+      <c r="M98" t="s">
+        <v>17</v>
+      </c>
+      <c r="N98" t="s">
+        <v>432</v>
+      </c>
+      <c r="O98" t="s">
+        <v>243</v>
+      </c>
+      <c r="P98" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>25</v>
+      </c>
+      <c r="R98" t="s">
+        <v>35</v>
+      </c>
+      <c r="S98" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="99" spans="13:19">
+      <c r="M99" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" t="s">
+        <v>434</v>
+      </c>
+      <c r="O99" t="s">
+        <v>243</v>
+      </c>
+      <c r="P99" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>25</v>
+      </c>
+      <c r="R99" t="s">
+        <v>35</v>
+      </c>
+      <c r="S99" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="100" spans="13:19">
+      <c r="M100" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" t="s">
+        <v>436</v>
+      </c>
+      <c r="O100" t="s">
+        <v>243</v>
+      </c>
+      <c r="P100" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>25</v>
+      </c>
+      <c r="R100" t="s">
+        <v>35</v>
+      </c>
+      <c r="S100" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="101" spans="13:19">
+      <c r="M101" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" t="s">
+        <v>438</v>
+      </c>
+      <c r="O101" t="s">
+        <v>243</v>
+      </c>
+      <c r="P101" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>25</v>
+      </c>
+      <c r="R101" t="s">
+        <v>35</v>
+      </c>
+      <c r="S101" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="102" spans="13:19">
+      <c r="M102" t="s">
+        <v>17</v>
+      </c>
+      <c r="N102" t="s">
+        <v>440</v>
+      </c>
+      <c r="O102" t="s">
+        <v>243</v>
+      </c>
+      <c r="P102" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>25</v>
+      </c>
+      <c r="R102" t="s">
+        <v>35</v>
+      </c>
+      <c r="S102" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="103" spans="13:19">
+      <c r="M103" t="s">
+        <v>17</v>
+      </c>
+      <c r="N103" t="s">
+        <v>442</v>
+      </c>
+      <c r="O103" t="s">
+        <v>243</v>
+      </c>
+      <c r="P103" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>25</v>
+      </c>
+      <c r="R103" t="s">
+        <v>35</v>
+      </c>
+      <c r="S103" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="104" spans="13:19">
+      <c r="M104" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" t="s">
+        <v>444</v>
+      </c>
+      <c r="O104" t="s">
+        <v>243</v>
+      </c>
+      <c r="P104" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>25</v>
+      </c>
+      <c r="R104" t="s">
+        <v>35</v>
+      </c>
+      <c r="S104" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="105" spans="13:19">
+      <c r="M105" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" t="s">
+        <v>446</v>
+      </c>
+      <c r="O105" t="s">
+        <v>243</v>
+      </c>
+      <c r="P105" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>25</v>
+      </c>
+      <c r="R105" t="s">
+        <v>35</v>
+      </c>
+      <c r="S105" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="106" spans="13:19">
+      <c r="M106" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" t="s">
+        <v>448</v>
+      </c>
+      <c r="O106" t="s">
+        <v>243</v>
+      </c>
+      <c r="P106" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>25</v>
+      </c>
+      <c r="R106" t="s">
+        <v>35</v>
+      </c>
+      <c r="S106" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="107" spans="13:19">
+      <c r="M107" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" t="s">
+        <v>450</v>
+      </c>
+      <c r="O107" t="s">
+        <v>243</v>
+      </c>
+      <c r="P107" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>25</v>
+      </c>
+      <c r="R107" t="s">
+        <v>35</v>
+      </c>
+      <c r="S107" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="108" spans="13:19">
+      <c r="M108" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108" t="s">
+        <v>452</v>
+      </c>
+      <c r="O108" t="s">
+        <v>243</v>
+      </c>
+      <c r="P108" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>25</v>
+      </c>
+      <c r="R108" t="s">
+        <v>35</v>
+      </c>
+      <c r="S108" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="109" spans="13:19">
+      <c r="M109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>454</v>
+      </c>
+      <c r="O109" t="s">
+        <v>243</v>
+      </c>
+      <c r="P109" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>25</v>
+      </c>
+      <c r="R109" t="s">
+        <v>35</v>
+      </c>
+      <c r="S109" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="110" spans="13:19">
+      <c r="M110" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" t="s">
+        <v>456</v>
+      </c>
+      <c r="O110" t="s">
+        <v>243</v>
+      </c>
+      <c r="P110" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>25</v>
+      </c>
+      <c r="R110" t="s">
+        <v>35</v>
+      </c>
+      <c r="S110" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27360764-C30E-4474-B836-841C3FD51C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C869F5D4-FCC7-4CE1-912C-0B1DF6EBA0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="695">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -781,7 +781,7 @@
     <t>elc_spv_POL_001</t>
   </si>
   <si>
-    <t>solar electricity near Bydgoszcz (cluster 1)</t>
+    <t>solar electricity near Bialystok (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -790,283 +790,115 @@
     <t>elc_spv_POL_002</t>
   </si>
   <si>
-    <t>solar electricity near Bialystok (cluster 2)</t>
+    <t>solar electricity near Elk (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
-    <t>solar electricity near Gorzow Wielkopolski (cluster 3)</t>
+    <t>solar electricity near Rzeszow (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity near Walbrzych (cluster 4)</t>
+    <t>solar electricity near Krakow (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 5)</t>
+    <t>solar electricity near Lublin (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>solar electricity near Walbrzych (cluster 6)</t>
+    <t>solar electricity near Lublin (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 7)</t>
+    <t>solar electricity near Stargard Szczecinski (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>solar electricity near Slupsk (cluster 8)</t>
+    <t>solar electricity near Pila (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 9)</t>
+    <t>solar electricity near Torun (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity near Jelenia Gora (cluster 10)</t>
+    <t>solar electricity near Olsztyn (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity near Gdansk (cluster 11)</t>
+    <t>solar electricity near Elblag (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>solar electricity near Lomza (cluster 12)</t>
+    <t>solar electricity near Poznan (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 13)</t>
+    <t>solar electricity near Wroclaw (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Szczecin (cluster 14)</t>
+    <t>solar electricity near Legnica (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 15)</t>
+    <t>solar electricity near Zielona Gora (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Suwalki (cluster 16)</t>
+    <t>solar electricity near Wroclaw (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Piotrkow Trybunalski (cluster 17)</t>
+    <t>solar electricity near Katowice (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 18)</t>
+    <t>solar electricity near Warsaw (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity near Zamosc (cluster 19)</t>
+    <t>solar electricity near Radom (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity near Koszalin (cluster 20)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_021</t>
-  </si>
-  <si>
-    <t>solar electricity near Zielona Gora (cluster 21)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_022</t>
-  </si>
-  <si>
-    <t>solar electricity near Katowice (cluster 22)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_023</t>
-  </si>
-  <si>
-    <t>solar electricity near Tarnow (cluster 23)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_024</t>
-  </si>
-  <si>
-    <t>solar electricity near Chelm (cluster 24)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_025</t>
-  </si>
-  <si>
-    <t>solar electricity near Rzeszow (cluster 25)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_026</t>
-  </si>
-  <si>
-    <t>solar electricity near Kielce (cluster 26)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_027</t>
-  </si>
-  <si>
-    <t>solar electricity near Mielec (cluster 27)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_028</t>
-  </si>
-  <si>
-    <t>solar electricity near Rzeszow (cluster 28)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_029</t>
-  </si>
-  <si>
-    <t>solar electricity near Czestochowa (cluster 29)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_030</t>
-  </si>
-  <si>
-    <t>solar electricity near Torun (cluster 30)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_031</t>
-  </si>
-  <si>
-    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_032</t>
-  </si>
-  <si>
-    <t>solar electricity near Opole (cluster 32)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_033</t>
-  </si>
-  <si>
-    <t>solar electricity near Kalisz (cluster 33)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_034</t>
-  </si>
-  <si>
-    <t>solar electricity near Koszalin (cluster 34)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_035</t>
-  </si>
-  <si>
-    <t>solar electricity near Warsaw (cluster 35)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_036</t>
-  </si>
-  <si>
-    <t>solar electricity near Katowice (cluster 36)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_037</t>
-  </si>
-  <si>
-    <t>solar electricity near Suwalki (cluster 37)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_038</t>
-  </si>
-  <si>
-    <t>solar electricity near Pila (cluster 38)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_039</t>
-  </si>
-  <si>
-    <t>solar electricity near Kedzierzyn-Kozle (cluster 39)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_040</t>
-  </si>
-  <si>
-    <t>solar electricity near Szczecin (cluster 40)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_041</t>
-  </si>
-  <si>
-    <t>solar electricity near Krakow (cluster 41)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_042</t>
-  </si>
-  <si>
-    <t>solar electricity near Krakow (cluster 42)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_043</t>
-  </si>
-  <si>
-    <t>solar electricity near Elblag (cluster 43)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_044</t>
-  </si>
-  <si>
-    <t>solar electricity near Plock (cluster 44)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_045</t>
-  </si>
-  <si>
-    <t>solar electricity near Wroclaw (cluster 45)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_046</t>
-  </si>
-  <si>
-    <t>solar electricity near Gdansk (cluster 46)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_047</t>
-  </si>
-  <si>
-    <t>solar electricity near Krakow (cluster 47)</t>
-  </si>
-  <si>
-    <t>elc_spv_POL_048</t>
-  </si>
-  <si>
-    <t>solar electricity near Siedlce (cluster 48)</t>
+    <t>solar electricity near Lodz (cluster 20)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -1084,25 +916,25 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 3)</t>
+    <t>wind offshore electricity near Gdansk (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 4)</t>
+    <t>wind offshore electricity near Slupsk (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 5)</t>
+    <t>wind offshore electricity near Gdansk (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 6)</t>
+    <t>wind offshore electricity near Gdansk (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
@@ -1114,307 +946,133 @@
     <t>elc_wof_POL_008</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdynia (cluster 8)</t>
+    <t>wind offshore electricity near Koszalin (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 9)</t>
+    <t>wind offshore electricity near Koszalin (cluster 9)</t>
   </si>
   <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 10)</t>
+    <t>wind offshore electricity near Koszalin (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bydgoszcz (cluster 1)</t>
+    <t>wind onshore electricity near Walbrzych (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bialystok (cluster 2)</t>
+    <t>wind onshore electricity near Rybnik (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gorzow Wielkopolski (cluster 3)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 4)</t>
+    <t>wind onshore electricity near Poznan (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wroclaw (cluster 5)</t>
+    <t>wind onshore electricity near Elblag (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 6)</t>
+    <t>wind onshore electricity near Stargard Szczecinski (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 7)</t>
+    <t>wind onshore electricity near Slupsk (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Slupsk (cluster 8)</t>
+    <t>wind onshore electricity near Pila (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 9)</t>
+    <t>wind onshore electricity near Bialystok (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Jelenia Gora (cluster 10)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gdansk (cluster 11)</t>
+    <t>wind onshore electricity near Siedlce (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lomza (cluster 12)</t>
+    <t>wind onshore electricity near Warsaw (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 13)</t>
+    <t>wind onshore electricity near Kalisz (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Szczecin (cluster 14)</t>
+    <t>wind onshore electricity near Wloclawek (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Przemysl (cluster 15)</t>
+    <t>wind onshore electricity near Katowice (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Suwalki (cluster 16)</t>
+    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 17)</t>
+    <t>wind onshore electricity near Lublin (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lodz (cluster 18)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zamosc (cluster 19)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_020</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Koszalin (cluster 20)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_021</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 21)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_022</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Katowice (cluster 22)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_023</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Tarnow (cluster 23)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_024</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Chelm (cluster 24)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_025</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Rzeszow (cluster 25)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_026</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Kielce (cluster 26)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_027</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Mielec (cluster 27)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_028</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Rzeszow (cluster 28)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_029</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Czestochowa (cluster 29)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_030</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Torun (cluster 30)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_031</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_032</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Opole (cluster 32)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_033</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Konin (cluster 33)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_034</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Koszalin (cluster 34)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_035</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Warsaw (cluster 35)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_036</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Katowice (cluster 36)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_037</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Suwalki (cluster 37)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_038</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Pila (cluster 38)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_039</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 39)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_040</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Szczecin (cluster 40)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_041</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Krakow (cluster 41)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_042</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Krakow (cluster 42)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_043</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Elblag (cluster 43)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_044</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Plock (cluster 44)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_045</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Wroclaw (cluster 45)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_046</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Gdansk (cluster 46)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_047</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Krakow (cluster 47)</t>
-  </si>
-  <si>
-    <t>elc_won_POL_048</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Siedlce (cluster 48)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 19)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4500,9 +4158,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4540,7 +4198,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4646,7 +4304,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4788,7 +4446,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4862,13 +4520,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C26E361-6705-4186-BAC4-551AC7C1EA7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A03BC4-AD77-4FF1-B587-1AD45746BFA0}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>458</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4899,19 +4557,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>652</v>
+        <v>538</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>653</v>
+        <v>539</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4922,19 +4580,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>655</v>
+        <v>541</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>656</v>
+        <v>542</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4945,19 +4603,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>657</v>
+        <v>543</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>658</v>
+        <v>544</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4968,19 +4626,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>659</v>
+        <v>545</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>660</v>
+        <v>546</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4991,19 +4649,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>661</v>
+        <v>547</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>662</v>
+        <v>548</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -5014,19 +4672,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>663</v>
+        <v>549</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>664</v>
+        <v>550</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -5037,19 +4695,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>665</v>
+        <v>551</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>666</v>
+        <v>552</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -5060,19 +4718,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>667</v>
+        <v>553</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>668</v>
+        <v>554</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -5083,19 +4741,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>669</v>
+        <v>555</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>670</v>
+        <v>556</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -5106,19 +4764,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>671</v>
+        <v>557</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>672</v>
+        <v>558</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -5129,19 +4787,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>673</v>
+        <v>559</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>674</v>
+        <v>560</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -5152,19 +4810,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>675</v>
+        <v>561</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>676</v>
+        <v>562</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -5175,19 +4833,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>677</v>
+        <v>563</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>678</v>
+        <v>564</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -5198,19 +4856,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>679</v>
+        <v>565</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>680</v>
+        <v>566</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -5221,19 +4879,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>681</v>
+        <v>567</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>682</v>
+        <v>568</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -5244,19 +4902,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>683</v>
+        <v>569</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>684</v>
+        <v>570</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -5267,19 +4925,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>685</v>
+        <v>571</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>686</v>
+        <v>572</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -5290,19 +4948,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>687</v>
+        <v>573</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>688</v>
+        <v>574</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -5313,19 +4971,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>689</v>
+        <v>575</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>690</v>
+        <v>576</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -5336,19 +4994,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>691</v>
+        <v>577</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>692</v>
+        <v>578</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5359,19 +5017,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>693</v>
+        <v>579</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>694</v>
+        <v>580</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5382,19 +5040,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>696</v>
+        <v>582</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5405,19 +5063,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>697</v>
+        <v>583</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>698</v>
+        <v>584</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5428,19 +5086,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>699</v>
+        <v>585</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>700</v>
+        <v>586</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5451,19 +5109,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>701</v>
+        <v>587</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>702</v>
+        <v>588</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5474,19 +5132,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>703</v>
+        <v>589</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>704</v>
+        <v>590</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5497,19 +5155,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>705</v>
+        <v>591</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>706</v>
+        <v>592</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5520,19 +5178,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>707</v>
+        <v>593</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>708</v>
+        <v>594</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5543,19 +5201,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>709</v>
+        <v>595</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>710</v>
+        <v>596</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5566,19 +5224,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>711</v>
+        <v>597</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>712</v>
+        <v>598</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5589,19 +5247,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>713</v>
+        <v>599</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>714</v>
+        <v>600</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5612,19 +5270,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>715</v>
+        <v>601</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>716</v>
+        <v>602</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5635,19 +5293,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>717</v>
+        <v>603</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>718</v>
+        <v>604</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5658,19 +5316,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>719</v>
+        <v>605</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>720</v>
+        <v>606</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5681,19 +5339,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>721</v>
+        <v>607</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>722</v>
+        <v>608</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5704,19 +5362,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>723</v>
+        <v>609</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>724</v>
+        <v>610</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5727,19 +5385,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>725</v>
+        <v>611</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>726</v>
+        <v>612</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5750,19 +5408,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>727</v>
+        <v>613</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>728</v>
+        <v>614</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5773,19 +5431,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>729</v>
+        <v>615</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>730</v>
+        <v>616</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5796,19 +5454,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>731</v>
+        <v>617</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>732</v>
+        <v>618</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5819,19 +5477,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>733</v>
+        <v>619</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>734</v>
+        <v>620</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5842,19 +5500,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>735</v>
+        <v>621</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>736</v>
+        <v>622</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5865,19 +5523,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>737</v>
+        <v>623</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>738</v>
+        <v>624</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5888,19 +5546,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>739</v>
+        <v>625</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>740</v>
+        <v>626</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5911,19 +5569,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>741</v>
+        <v>627</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>742</v>
+        <v>628</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5934,19 +5592,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>743</v>
+        <v>629</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>744</v>
+        <v>630</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5957,19 +5615,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>745</v>
+        <v>631</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>746</v>
+        <v>632</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5980,19 +5638,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>747</v>
+        <v>633</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>748</v>
+        <v>634</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -6003,19 +5661,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>749</v>
+        <v>635</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>750</v>
+        <v>636</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -6026,19 +5684,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>751</v>
+        <v>637</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>752</v>
+        <v>638</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -6049,19 +5707,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>753</v>
+        <v>639</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>754</v>
+        <v>640</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -6072,19 +5730,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>755</v>
+        <v>641</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>756</v>
+        <v>642</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -6095,19 +5753,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>757</v>
+        <v>643</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>758</v>
+        <v>644</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -6118,19 +5776,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>759</v>
+        <v>645</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>760</v>
+        <v>646</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -6141,19 +5799,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>761</v>
+        <v>647</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>762</v>
+        <v>648</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -6164,19 +5822,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>763</v>
+        <v>649</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>764</v>
+        <v>650</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -6187,19 +5845,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>765</v>
+        <v>651</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>766</v>
+        <v>652</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -6210,19 +5868,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>767</v>
+        <v>653</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>768</v>
+        <v>654</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -6233,19 +5891,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>769</v>
+        <v>655</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>770</v>
+        <v>656</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -6256,19 +5914,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>771</v>
+        <v>657</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>772</v>
+        <v>658</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -6279,19 +5937,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>773</v>
+        <v>659</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>774</v>
+        <v>660</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -6302,19 +5960,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>775</v>
+        <v>661</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>776</v>
+        <v>662</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -6325,19 +5983,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>777</v>
+        <v>663</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>778</v>
+        <v>664</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6348,19 +6006,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>779</v>
+        <v>665</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>780</v>
+        <v>666</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6371,19 +6029,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>781</v>
+        <v>667</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>782</v>
+        <v>668</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6394,19 +6052,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>783</v>
+        <v>669</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>784</v>
+        <v>670</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6417,19 +6075,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>785</v>
+        <v>671</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>786</v>
+        <v>672</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6440,19 +6098,19 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>787</v>
+        <v>673</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>788</v>
+        <v>674</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H72" t="s">
         <v>195</v>
@@ -6463,19 +6121,19 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>789</v>
+        <v>675</v>
       </c>
       <c r="D73" t="s">
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>790</v>
+        <v>676</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H73" t="s">
         <v>195</v>
@@ -6486,19 +6144,19 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>791</v>
+        <v>677</v>
       </c>
       <c r="D74" t="s">
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>792</v>
+        <v>678</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H74" t="s">
         <v>195</v>
@@ -6509,19 +6167,19 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>793</v>
+        <v>679</v>
       </c>
       <c r="D75" t="s">
         <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>794</v>
+        <v>680</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H75" t="s">
         <v>195</v>
@@ -6532,19 +6190,19 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>795</v>
+        <v>681</v>
       </c>
       <c r="D76" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>796</v>
+        <v>682</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H76" t="s">
         <v>195</v>
@@ -6555,19 +6213,19 @@
         <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>797</v>
+        <v>683</v>
       </c>
       <c r="D77" t="s">
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>798</v>
+        <v>684</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H77" t="s">
         <v>195</v>
@@ -6578,19 +6236,19 @@
         <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>799</v>
+        <v>685</v>
       </c>
       <c r="D78" t="s">
         <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>800</v>
+        <v>686</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H78" t="s">
         <v>195</v>
@@ -6601,19 +6259,19 @@
         <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>801</v>
+        <v>687</v>
       </c>
       <c r="D79" t="s">
         <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>802</v>
+        <v>688</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H79" t="s">
         <v>195</v>
@@ -6624,19 +6282,19 @@
         <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>803</v>
+        <v>689</v>
       </c>
       <c r="D80" t="s">
         <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>804</v>
+        <v>690</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H80" t="s">
         <v>195</v>
@@ -6647,19 +6305,19 @@
         <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>805</v>
+        <v>691</v>
       </c>
       <c r="D81" t="s">
         <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>806</v>
+        <v>692</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H81" t="s">
         <v>195</v>
@@ -6670,19 +6328,19 @@
         <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>807</v>
+        <v>693</v>
       </c>
       <c r="D82" t="s">
         <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>808</v>
+        <v>694</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>654</v>
+        <v>540</v>
       </c>
       <c r="H82" t="s">
         <v>195</v>
@@ -6694,13 +6352,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225779BF-CE1E-4C54-B228-6D218E664B9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E3B025-E8E4-4DE3-AB34-65FF4B1EBC22}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>458</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6734,13 +6392,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>556</v>
+        <v>442</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>557</v>
+        <v>443</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6749,7 +6407,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -6760,13 +6418,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>558</v>
+        <v>444</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>559</v>
+        <v>445</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6775,7 +6433,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -6786,13 +6444,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>560</v>
+        <v>446</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>561</v>
+        <v>447</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6801,7 +6459,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -6812,13 +6470,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>562</v>
+        <v>448</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>563</v>
+        <v>449</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6827,7 +6485,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -6838,13 +6496,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>564</v>
+        <v>450</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>565</v>
+        <v>451</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6853,7 +6511,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -6864,13 +6522,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>566</v>
+        <v>452</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>567</v>
+        <v>453</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6879,7 +6537,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -6890,13 +6548,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>568</v>
+        <v>454</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>569</v>
+        <v>455</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6905,7 +6563,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -6916,13 +6574,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>570</v>
+        <v>456</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>571</v>
+        <v>457</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6931,7 +6589,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -6942,13 +6600,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>572</v>
+        <v>458</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>573</v>
+        <v>459</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6957,7 +6615,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -6968,13 +6626,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>574</v>
+        <v>460</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>575</v>
+        <v>461</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6983,7 +6641,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -6994,13 +6652,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>576</v>
+        <v>462</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>577</v>
+        <v>463</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -7009,7 +6667,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -7020,13 +6678,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>578</v>
+        <v>464</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>579</v>
+        <v>465</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -7035,7 +6693,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7046,13 +6704,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>580</v>
+        <v>466</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>581</v>
+        <v>467</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -7061,7 +6719,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -7072,13 +6730,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>582</v>
+        <v>468</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>583</v>
+        <v>469</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -7087,7 +6745,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -7098,13 +6756,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>584</v>
+        <v>470</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>585</v>
+        <v>471</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -7113,7 +6771,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -7124,13 +6782,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>586</v>
+        <v>472</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>587</v>
+        <v>473</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -7139,7 +6797,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -7150,13 +6808,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>588</v>
+        <v>474</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>589</v>
+        <v>475</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -7165,7 +6823,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -7176,13 +6834,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>590</v>
+        <v>476</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>591</v>
+        <v>477</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -7191,7 +6849,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -7202,13 +6860,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>592</v>
+        <v>478</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>593</v>
+        <v>479</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -7217,7 +6875,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -7228,13 +6886,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>594</v>
+        <v>480</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>595</v>
+        <v>481</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -7243,7 +6901,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -7254,13 +6912,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>596</v>
+        <v>482</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>597</v>
+        <v>483</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -7269,7 +6927,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -7280,13 +6938,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>598</v>
+        <v>484</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>599</v>
+        <v>485</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -7295,7 +6953,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -7306,13 +6964,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>600</v>
+        <v>486</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>601</v>
+        <v>487</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -7321,7 +6979,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -7332,13 +6990,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>602</v>
+        <v>488</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>603</v>
+        <v>489</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7347,7 +7005,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7358,13 +7016,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>604</v>
+        <v>490</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>605</v>
+        <v>491</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7373,7 +7031,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7384,13 +7042,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>606</v>
+        <v>492</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>607</v>
+        <v>493</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7399,7 +7057,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7410,13 +7068,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>608</v>
+        <v>494</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>609</v>
+        <v>495</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7425,7 +7083,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7436,13 +7094,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>610</v>
+        <v>496</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>611</v>
+        <v>497</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7451,7 +7109,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7462,13 +7120,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>612</v>
+        <v>498</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>613</v>
+        <v>499</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7477,7 +7135,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7488,13 +7146,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>614</v>
+        <v>500</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>615</v>
+        <v>501</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7503,7 +7161,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7514,13 +7172,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>616</v>
+        <v>502</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>617</v>
+        <v>503</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7529,7 +7187,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7540,13 +7198,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>618</v>
+        <v>504</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>619</v>
+        <v>505</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7555,7 +7213,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7566,13 +7224,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>620</v>
+        <v>506</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>621</v>
+        <v>507</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7581,7 +7239,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7592,13 +7250,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>622</v>
+        <v>508</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>623</v>
+        <v>509</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7607,7 +7265,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7618,13 +7276,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>624</v>
+        <v>510</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>625</v>
+        <v>511</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7633,7 +7291,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7644,13 +7302,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>626</v>
+        <v>512</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>627</v>
+        <v>513</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7659,7 +7317,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7670,13 +7328,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>628</v>
+        <v>514</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>629</v>
+        <v>515</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7685,7 +7343,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7696,13 +7354,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>630</v>
+        <v>516</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>631</v>
+        <v>517</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7711,7 +7369,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -7722,13 +7380,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>632</v>
+        <v>518</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>633</v>
+        <v>519</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7737,7 +7395,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -7748,13 +7406,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>634</v>
+        <v>520</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>635</v>
+        <v>521</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7763,7 +7421,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -7774,13 +7432,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>636</v>
+        <v>522</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>637</v>
+        <v>523</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7789,7 +7447,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -7800,13 +7458,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>638</v>
+        <v>524</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>639</v>
+        <v>525</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7815,7 +7473,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -7826,13 +7484,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>640</v>
+        <v>526</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>641</v>
+        <v>527</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7841,7 +7499,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -7852,13 +7510,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>642</v>
+        <v>528</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>643</v>
+        <v>529</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7867,7 +7525,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -7878,13 +7536,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>644</v>
+        <v>530</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>645</v>
+        <v>531</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7893,7 +7551,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -7904,13 +7562,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>646</v>
+        <v>532</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>647</v>
+        <v>533</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7919,7 +7577,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -7930,13 +7588,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>648</v>
+        <v>534</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>649</v>
+        <v>535</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7945,7 +7603,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -7956,13 +7614,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>650</v>
+        <v>536</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>651</v>
+        <v>537</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7971,7 +7629,7 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -7983,13 +7641,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A69EB4-A378-4D87-BFA0-7658C5139A2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3926DF71-5F25-44C0-A9CC-C9C5B2407FD3}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>458</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -8023,13 +7681,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>460</v>
+        <v>346</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -8038,7 +7696,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -8049,13 +7707,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>462</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>463</v>
+        <v>349</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -8064,7 +7722,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -8075,13 +7733,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>464</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>465</v>
+        <v>351</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -8090,7 +7748,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -8101,13 +7759,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>466</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>467</v>
+        <v>353</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -8116,7 +7774,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -8127,13 +7785,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>468</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>469</v>
+        <v>355</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -8142,7 +7800,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -8153,13 +7811,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>470</v>
+        <v>356</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>471</v>
+        <v>357</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -8168,7 +7826,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -8179,13 +7837,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>472</v>
+        <v>358</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>473</v>
+        <v>359</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -8194,7 +7852,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -8205,13 +7863,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>474</v>
+        <v>360</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>475</v>
+        <v>361</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -8220,7 +7878,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -8231,13 +7889,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>476</v>
+        <v>362</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>477</v>
+        <v>363</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -8246,7 +7904,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -8257,13 +7915,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>478</v>
+        <v>364</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>479</v>
+        <v>365</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -8272,7 +7930,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -8283,13 +7941,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>480</v>
+        <v>366</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>481</v>
+        <v>367</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -8298,7 +7956,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -8309,13 +7967,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>482</v>
+        <v>368</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>483</v>
+        <v>369</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -8324,7 +7982,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -8335,13 +7993,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>484</v>
+        <v>370</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>485</v>
+        <v>371</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8350,7 +8008,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8361,13 +8019,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>486</v>
+        <v>372</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>487</v>
+        <v>373</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8376,7 +8034,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8387,13 +8045,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>488</v>
+        <v>374</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>489</v>
+        <v>375</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8402,7 +8060,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8413,13 +8071,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>490</v>
+        <v>376</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>491</v>
+        <v>377</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8428,7 +8086,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8439,13 +8097,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>492</v>
+        <v>378</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>493</v>
+        <v>379</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8454,7 +8112,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8465,13 +8123,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>494</v>
+        <v>380</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>495</v>
+        <v>381</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8480,7 +8138,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8491,13 +8149,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>496</v>
+        <v>382</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>497</v>
+        <v>383</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8506,7 +8164,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8517,13 +8175,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>498</v>
+        <v>384</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>499</v>
+        <v>385</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8532,7 +8190,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8543,13 +8201,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>500</v>
+        <v>386</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>501</v>
+        <v>387</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8558,7 +8216,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -8569,13 +8227,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>502</v>
+        <v>388</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>503</v>
+        <v>389</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -8584,7 +8242,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -8595,13 +8253,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>504</v>
+        <v>390</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>505</v>
+        <v>391</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8610,7 +8268,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -8621,13 +8279,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>506</v>
+        <v>392</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>507</v>
+        <v>393</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8636,7 +8294,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -8647,13 +8305,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>508</v>
+        <v>394</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>509</v>
+        <v>395</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8662,7 +8320,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -8673,13 +8331,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>510</v>
+        <v>396</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>511</v>
+        <v>397</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8688,7 +8346,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -8699,13 +8357,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>512</v>
+        <v>398</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>513</v>
+        <v>399</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8714,7 +8372,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -8725,13 +8383,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>514</v>
+        <v>400</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>515</v>
+        <v>401</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -8740,7 +8398,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -8751,13 +8409,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>516</v>
+        <v>402</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>517</v>
+        <v>403</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8766,7 +8424,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -8777,13 +8435,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>518</v>
+        <v>404</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>519</v>
+        <v>405</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -8792,7 +8450,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -8803,13 +8461,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>520</v>
+        <v>406</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>521</v>
+        <v>407</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -8818,7 +8476,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -8829,13 +8487,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>522</v>
+        <v>408</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>523</v>
+        <v>409</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -8844,7 +8502,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -8855,13 +8513,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>524</v>
+        <v>410</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>525</v>
+        <v>411</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -8870,7 +8528,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -8881,13 +8539,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>526</v>
+        <v>412</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>527</v>
+        <v>413</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -8896,7 +8554,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -8907,13 +8565,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>528</v>
+        <v>414</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>529</v>
+        <v>415</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -8922,7 +8580,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -8933,13 +8591,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>530</v>
+        <v>416</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>531</v>
+        <v>417</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -8948,7 +8606,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -8959,13 +8617,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>532</v>
+        <v>418</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>533</v>
+        <v>419</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -8974,7 +8632,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -8985,13 +8643,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>534</v>
+        <v>420</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>535</v>
+        <v>421</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -9000,7 +8658,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -9011,13 +8669,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>536</v>
+        <v>422</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>537</v>
+        <v>423</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -9026,7 +8684,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -9037,13 +8695,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>538</v>
+        <v>424</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>539</v>
+        <v>425</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -9052,7 +8710,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -9063,13 +8721,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>540</v>
+        <v>426</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>541</v>
+        <v>427</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -9078,7 +8736,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -9089,13 +8747,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>542</v>
+        <v>428</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>543</v>
+        <v>429</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -9104,7 +8762,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -9115,13 +8773,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>544</v>
+        <v>430</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>545</v>
+        <v>431</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -9130,7 +8788,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -9141,13 +8799,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>546</v>
+        <v>432</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>547</v>
+        <v>433</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -9156,7 +8814,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -9167,13 +8825,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>548</v>
+        <v>434</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>549</v>
+        <v>435</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -9182,7 +8840,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -9193,13 +8851,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>550</v>
+        <v>436</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>551</v>
+        <v>437</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -9208,7 +8866,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -9219,13 +8877,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>552</v>
+        <v>438</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>553</v>
+        <v>439</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -9234,7 +8892,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -9245,13 +8903,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>554</v>
+        <v>440</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>555</v>
+        <v>441</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -9260,7 +8918,7 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -9273,7 +8931,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S110"/>
+  <dimension ref="B3:S53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -10861,1317 +10519,6 @@
         <v>35</v>
       </c>
       <c r="S53" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="54" spans="13:19">
-      <c r="M54" t="s">
-        <v>17</v>
-      </c>
-      <c r="N54" t="s">
-        <v>344</v>
-      </c>
-      <c r="O54" t="s">
-        <v>243</v>
-      </c>
-      <c r="P54" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>25</v>
-      </c>
-      <c r="R54" t="s">
-        <v>35</v>
-      </c>
-      <c r="S54" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="55" spans="13:19">
-      <c r="M55" t="s">
-        <v>17</v>
-      </c>
-      <c r="N55" t="s">
-        <v>346</v>
-      </c>
-      <c r="O55" t="s">
-        <v>243</v>
-      </c>
-      <c r="P55" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>25</v>
-      </c>
-      <c r="R55" t="s">
-        <v>35</v>
-      </c>
-      <c r="S55" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="56" spans="13:19">
-      <c r="M56" t="s">
-        <v>17</v>
-      </c>
-      <c r="N56" t="s">
-        <v>348</v>
-      </c>
-      <c r="O56" t="s">
-        <v>243</v>
-      </c>
-      <c r="P56" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>25</v>
-      </c>
-      <c r="R56" t="s">
-        <v>35</v>
-      </c>
-      <c r="S56" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" spans="13:19">
-      <c r="M57" t="s">
-        <v>17</v>
-      </c>
-      <c r="N57" t="s">
-        <v>350</v>
-      </c>
-      <c r="O57" t="s">
-        <v>243</v>
-      </c>
-      <c r="P57" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>25</v>
-      </c>
-      <c r="R57" t="s">
-        <v>35</v>
-      </c>
-      <c r="S57" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="58" spans="13:19">
-      <c r="M58" t="s">
-        <v>17</v>
-      </c>
-      <c r="N58" t="s">
-        <v>352</v>
-      </c>
-      <c r="O58" t="s">
-        <v>243</v>
-      </c>
-      <c r="P58" t="s">
-        <v>353</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>25</v>
-      </c>
-      <c r="R58" t="s">
-        <v>35</v>
-      </c>
-      <c r="S58" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" spans="13:19">
-      <c r="M59" t="s">
-        <v>17</v>
-      </c>
-      <c r="N59" t="s">
-        <v>354</v>
-      </c>
-      <c r="O59" t="s">
-        <v>243</v>
-      </c>
-      <c r="P59" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>25</v>
-      </c>
-      <c r="R59" t="s">
-        <v>35</v>
-      </c>
-      <c r="S59" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="60" spans="13:19">
-      <c r="M60" t="s">
-        <v>17</v>
-      </c>
-      <c r="N60" t="s">
-        <v>356</v>
-      </c>
-      <c r="O60" t="s">
-        <v>243</v>
-      </c>
-      <c r="P60" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>25</v>
-      </c>
-      <c r="R60" t="s">
-        <v>35</v>
-      </c>
-      <c r="S60" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="13:19">
-      <c r="M61" t="s">
-        <v>17</v>
-      </c>
-      <c r="N61" t="s">
-        <v>358</v>
-      </c>
-      <c r="O61" t="s">
-        <v>243</v>
-      </c>
-      <c r="P61" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>25</v>
-      </c>
-      <c r="R61" t="s">
-        <v>35</v>
-      </c>
-      <c r="S61" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="62" spans="13:19">
-      <c r="M62" t="s">
-        <v>17</v>
-      </c>
-      <c r="N62" t="s">
-        <v>360</v>
-      </c>
-      <c r="O62" t="s">
-        <v>243</v>
-      </c>
-      <c r="P62" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>25</v>
-      </c>
-      <c r="R62" t="s">
-        <v>35</v>
-      </c>
-      <c r="S62" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="63" spans="13:19">
-      <c r="M63" t="s">
-        <v>17</v>
-      </c>
-      <c r="N63" t="s">
-        <v>362</v>
-      </c>
-      <c r="O63" t="s">
-        <v>243</v>
-      </c>
-      <c r="P63" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>25</v>
-      </c>
-      <c r="R63" t="s">
-        <v>35</v>
-      </c>
-      <c r="S63" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="64" spans="13:19">
-      <c r="M64" t="s">
-        <v>17</v>
-      </c>
-      <c r="N64" t="s">
-        <v>364</v>
-      </c>
-      <c r="O64" t="s">
-        <v>243</v>
-      </c>
-      <c r="P64" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>25</v>
-      </c>
-      <c r="R64" t="s">
-        <v>35</v>
-      </c>
-      <c r="S64" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="65" spans="13:19">
-      <c r="M65" t="s">
-        <v>17</v>
-      </c>
-      <c r="N65" t="s">
-        <v>366</v>
-      </c>
-      <c r="O65" t="s">
-        <v>243</v>
-      </c>
-      <c r="P65" t="s">
-        <v>367</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>25</v>
-      </c>
-      <c r="R65" t="s">
-        <v>35</v>
-      </c>
-      <c r="S65" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="66" spans="13:19">
-      <c r="M66" t="s">
-        <v>17</v>
-      </c>
-      <c r="N66" t="s">
-        <v>368</v>
-      </c>
-      <c r="O66" t="s">
-        <v>243</v>
-      </c>
-      <c r="P66" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>25</v>
-      </c>
-      <c r="R66" t="s">
-        <v>35</v>
-      </c>
-      <c r="S66" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="67" spans="13:19">
-      <c r="M67" t="s">
-        <v>17</v>
-      </c>
-      <c r="N67" t="s">
-        <v>370</v>
-      </c>
-      <c r="O67" t="s">
-        <v>243</v>
-      </c>
-      <c r="P67" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>25</v>
-      </c>
-      <c r="R67" t="s">
-        <v>35</v>
-      </c>
-      <c r="S67" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="68" spans="13:19">
-      <c r="M68" t="s">
-        <v>17</v>
-      </c>
-      <c r="N68" t="s">
-        <v>372</v>
-      </c>
-      <c r="O68" t="s">
-        <v>243</v>
-      </c>
-      <c r="P68" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>25</v>
-      </c>
-      <c r="R68" t="s">
-        <v>35</v>
-      </c>
-      <c r="S68" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="69" spans="13:19">
-      <c r="M69" t="s">
-        <v>17</v>
-      </c>
-      <c r="N69" t="s">
-        <v>374</v>
-      </c>
-      <c r="O69" t="s">
-        <v>243</v>
-      </c>
-      <c r="P69" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>25</v>
-      </c>
-      <c r="R69" t="s">
-        <v>35</v>
-      </c>
-      <c r="S69" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="70" spans="13:19">
-      <c r="M70" t="s">
-        <v>17</v>
-      </c>
-      <c r="N70" t="s">
-        <v>376</v>
-      </c>
-      <c r="O70" t="s">
-        <v>243</v>
-      </c>
-      <c r="P70" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>25</v>
-      </c>
-      <c r="R70" t="s">
-        <v>35</v>
-      </c>
-      <c r="S70" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="71" spans="13:19">
-      <c r="M71" t="s">
-        <v>17</v>
-      </c>
-      <c r="N71" t="s">
-        <v>378</v>
-      </c>
-      <c r="O71" t="s">
-        <v>243</v>
-      </c>
-      <c r="P71" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>25</v>
-      </c>
-      <c r="R71" t="s">
-        <v>35</v>
-      </c>
-      <c r="S71" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="72" spans="13:19">
-      <c r="M72" t="s">
-        <v>17</v>
-      </c>
-      <c r="N72" t="s">
-        <v>380</v>
-      </c>
-      <c r="O72" t="s">
-        <v>243</v>
-      </c>
-      <c r="P72" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>25</v>
-      </c>
-      <c r="R72" t="s">
-        <v>35</v>
-      </c>
-      <c r="S72" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="73" spans="13:19">
-      <c r="M73" t="s">
-        <v>17</v>
-      </c>
-      <c r="N73" t="s">
-        <v>382</v>
-      </c>
-      <c r="O73" t="s">
-        <v>243</v>
-      </c>
-      <c r="P73" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>25</v>
-      </c>
-      <c r="R73" t="s">
-        <v>35</v>
-      </c>
-      <c r="S73" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="74" spans="13:19">
-      <c r="M74" t="s">
-        <v>17</v>
-      </c>
-      <c r="N74" t="s">
-        <v>384</v>
-      </c>
-      <c r="O74" t="s">
-        <v>243</v>
-      </c>
-      <c r="P74" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>25</v>
-      </c>
-      <c r="R74" t="s">
-        <v>35</v>
-      </c>
-      <c r="S74" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="75" spans="13:19">
-      <c r="M75" t="s">
-        <v>17</v>
-      </c>
-      <c r="N75" t="s">
-        <v>386</v>
-      </c>
-      <c r="O75" t="s">
-        <v>243</v>
-      </c>
-      <c r="P75" t="s">
-        <v>387</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>25</v>
-      </c>
-      <c r="R75" t="s">
-        <v>35</v>
-      </c>
-      <c r="S75" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="76" spans="13:19">
-      <c r="M76" t="s">
-        <v>17</v>
-      </c>
-      <c r="N76" t="s">
-        <v>388</v>
-      </c>
-      <c r="O76" t="s">
-        <v>243</v>
-      </c>
-      <c r="P76" t="s">
-        <v>389</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>25</v>
-      </c>
-      <c r="R76" t="s">
-        <v>35</v>
-      </c>
-      <c r="S76" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="77" spans="13:19">
-      <c r="M77" t="s">
-        <v>17</v>
-      </c>
-      <c r="N77" t="s">
-        <v>390</v>
-      </c>
-      <c r="O77" t="s">
-        <v>243</v>
-      </c>
-      <c r="P77" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>25</v>
-      </c>
-      <c r="R77" t="s">
-        <v>35</v>
-      </c>
-      <c r="S77" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="78" spans="13:19">
-      <c r="M78" t="s">
-        <v>17</v>
-      </c>
-      <c r="N78" t="s">
-        <v>392</v>
-      </c>
-      <c r="O78" t="s">
-        <v>243</v>
-      </c>
-      <c r="P78" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>25</v>
-      </c>
-      <c r="R78" t="s">
-        <v>35</v>
-      </c>
-      <c r="S78" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="79" spans="13:19">
-      <c r="M79" t="s">
-        <v>17</v>
-      </c>
-      <c r="N79" t="s">
-        <v>394</v>
-      </c>
-      <c r="O79" t="s">
-        <v>243</v>
-      </c>
-      <c r="P79" t="s">
-        <v>395</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>25</v>
-      </c>
-      <c r="R79" t="s">
-        <v>35</v>
-      </c>
-      <c r="S79" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="80" spans="13:19">
-      <c r="M80" t="s">
-        <v>17</v>
-      </c>
-      <c r="N80" t="s">
-        <v>396</v>
-      </c>
-      <c r="O80" t="s">
-        <v>243</v>
-      </c>
-      <c r="P80" t="s">
-        <v>397</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>25</v>
-      </c>
-      <c r="R80" t="s">
-        <v>35</v>
-      </c>
-      <c r="S80" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="81" spans="13:19">
-      <c r="M81" t="s">
-        <v>17</v>
-      </c>
-      <c r="N81" t="s">
-        <v>398</v>
-      </c>
-      <c r="O81" t="s">
-        <v>243</v>
-      </c>
-      <c r="P81" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>25</v>
-      </c>
-      <c r="R81" t="s">
-        <v>35</v>
-      </c>
-      <c r="S81" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="82" spans="13:19">
-      <c r="M82" t="s">
-        <v>17</v>
-      </c>
-      <c r="N82" t="s">
-        <v>400</v>
-      </c>
-      <c r="O82" t="s">
-        <v>243</v>
-      </c>
-      <c r="P82" t="s">
-        <v>401</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>25</v>
-      </c>
-      <c r="R82" t="s">
-        <v>35</v>
-      </c>
-      <c r="S82" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="83" spans="13:19">
-      <c r="M83" t="s">
-        <v>17</v>
-      </c>
-      <c r="N83" t="s">
-        <v>402</v>
-      </c>
-      <c r="O83" t="s">
-        <v>243</v>
-      </c>
-      <c r="P83" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>25</v>
-      </c>
-      <c r="R83" t="s">
-        <v>35</v>
-      </c>
-      <c r="S83" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="84" spans="13:19">
-      <c r="M84" t="s">
-        <v>17</v>
-      </c>
-      <c r="N84" t="s">
-        <v>404</v>
-      </c>
-      <c r="O84" t="s">
-        <v>243</v>
-      </c>
-      <c r="P84" t="s">
-        <v>405</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>25</v>
-      </c>
-      <c r="R84" t="s">
-        <v>35</v>
-      </c>
-      <c r="S84" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="85" spans="13:19">
-      <c r="M85" t="s">
-        <v>17</v>
-      </c>
-      <c r="N85" t="s">
-        <v>406</v>
-      </c>
-      <c r="O85" t="s">
-        <v>243</v>
-      </c>
-      <c r="P85" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>25</v>
-      </c>
-      <c r="R85" t="s">
-        <v>35</v>
-      </c>
-      <c r="S85" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="86" spans="13:19">
-      <c r="M86" t="s">
-        <v>17</v>
-      </c>
-      <c r="N86" t="s">
-        <v>408</v>
-      </c>
-      <c r="O86" t="s">
-        <v>243</v>
-      </c>
-      <c r="P86" t="s">
-        <v>409</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>25</v>
-      </c>
-      <c r="R86" t="s">
-        <v>35</v>
-      </c>
-      <c r="S86" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="87" spans="13:19">
-      <c r="M87" t="s">
-        <v>17</v>
-      </c>
-      <c r="N87" t="s">
-        <v>410</v>
-      </c>
-      <c r="O87" t="s">
-        <v>243</v>
-      </c>
-      <c r="P87" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>25</v>
-      </c>
-      <c r="R87" t="s">
-        <v>35</v>
-      </c>
-      <c r="S87" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="88" spans="13:19">
-      <c r="M88" t="s">
-        <v>17</v>
-      </c>
-      <c r="N88" t="s">
-        <v>412</v>
-      </c>
-      <c r="O88" t="s">
-        <v>243</v>
-      </c>
-      <c r="P88" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>25</v>
-      </c>
-      <c r="R88" t="s">
-        <v>35</v>
-      </c>
-      <c r="S88" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="89" spans="13:19">
-      <c r="M89" t="s">
-        <v>17</v>
-      </c>
-      <c r="N89" t="s">
-        <v>414</v>
-      </c>
-      <c r="O89" t="s">
-        <v>243</v>
-      </c>
-      <c r="P89" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>25</v>
-      </c>
-      <c r="R89" t="s">
-        <v>35</v>
-      </c>
-      <c r="S89" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="90" spans="13:19">
-      <c r="M90" t="s">
-        <v>17</v>
-      </c>
-      <c r="N90" t="s">
-        <v>416</v>
-      </c>
-      <c r="O90" t="s">
-        <v>243</v>
-      </c>
-      <c r="P90" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>25</v>
-      </c>
-      <c r="R90" t="s">
-        <v>35</v>
-      </c>
-      <c r="S90" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="91" spans="13:19">
-      <c r="M91" t="s">
-        <v>17</v>
-      </c>
-      <c r="N91" t="s">
-        <v>418</v>
-      </c>
-      <c r="O91" t="s">
-        <v>243</v>
-      </c>
-      <c r="P91" t="s">
-        <v>419</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>25</v>
-      </c>
-      <c r="R91" t="s">
-        <v>35</v>
-      </c>
-      <c r="S91" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="92" spans="13:19">
-      <c r="M92" t="s">
-        <v>17</v>
-      </c>
-      <c r="N92" t="s">
-        <v>420</v>
-      </c>
-      <c r="O92" t="s">
-        <v>243</v>
-      </c>
-      <c r="P92" t="s">
-        <v>421</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>25</v>
-      </c>
-      <c r="R92" t="s">
-        <v>35</v>
-      </c>
-      <c r="S92" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="93" spans="13:19">
-      <c r="M93" t="s">
-        <v>17</v>
-      </c>
-      <c r="N93" t="s">
-        <v>422</v>
-      </c>
-      <c r="O93" t="s">
-        <v>243</v>
-      </c>
-      <c r="P93" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>25</v>
-      </c>
-      <c r="R93" t="s">
-        <v>35</v>
-      </c>
-      <c r="S93" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="94" spans="13:19">
-      <c r="M94" t="s">
-        <v>17</v>
-      </c>
-      <c r="N94" t="s">
-        <v>424</v>
-      </c>
-      <c r="O94" t="s">
-        <v>243</v>
-      </c>
-      <c r="P94" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>25</v>
-      </c>
-      <c r="R94" t="s">
-        <v>35</v>
-      </c>
-      <c r="S94" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="95" spans="13:19">
-      <c r="M95" t="s">
-        <v>17</v>
-      </c>
-      <c r="N95" t="s">
-        <v>426</v>
-      </c>
-      <c r="O95" t="s">
-        <v>243</v>
-      </c>
-      <c r="P95" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>25</v>
-      </c>
-      <c r="R95" t="s">
-        <v>35</v>
-      </c>
-      <c r="S95" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="96" spans="13:19">
-      <c r="M96" t="s">
-        <v>17</v>
-      </c>
-      <c r="N96" t="s">
-        <v>428</v>
-      </c>
-      <c r="O96" t="s">
-        <v>243</v>
-      </c>
-      <c r="P96" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>25</v>
-      </c>
-      <c r="R96" t="s">
-        <v>35</v>
-      </c>
-      <c r="S96" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="97" spans="13:19">
-      <c r="M97" t="s">
-        <v>17</v>
-      </c>
-      <c r="N97" t="s">
-        <v>430</v>
-      </c>
-      <c r="O97" t="s">
-        <v>243</v>
-      </c>
-      <c r="P97" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>25</v>
-      </c>
-      <c r="R97" t="s">
-        <v>35</v>
-      </c>
-      <c r="S97" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="98" spans="13:19">
-      <c r="M98" t="s">
-        <v>17</v>
-      </c>
-      <c r="N98" t="s">
-        <v>432</v>
-      </c>
-      <c r="O98" t="s">
-        <v>243</v>
-      </c>
-      <c r="P98" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q98" t="s">
-        <v>25</v>
-      </c>
-      <c r="R98" t="s">
-        <v>35</v>
-      </c>
-      <c r="S98" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="99" spans="13:19">
-      <c r="M99" t="s">
-        <v>17</v>
-      </c>
-      <c r="N99" t="s">
-        <v>434</v>
-      </c>
-      <c r="O99" t="s">
-        <v>243</v>
-      </c>
-      <c r="P99" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>25</v>
-      </c>
-      <c r="R99" t="s">
-        <v>35</v>
-      </c>
-      <c r="S99" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="100" spans="13:19">
-      <c r="M100" t="s">
-        <v>17</v>
-      </c>
-      <c r="N100" t="s">
-        <v>436</v>
-      </c>
-      <c r="O100" t="s">
-        <v>243</v>
-      </c>
-      <c r="P100" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>25</v>
-      </c>
-      <c r="R100" t="s">
-        <v>35</v>
-      </c>
-      <c r="S100" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="101" spans="13:19">
-      <c r="M101" t="s">
-        <v>17</v>
-      </c>
-      <c r="N101" t="s">
-        <v>438</v>
-      </c>
-      <c r="O101" t="s">
-        <v>243</v>
-      </c>
-      <c r="P101" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>25</v>
-      </c>
-      <c r="R101" t="s">
-        <v>35</v>
-      </c>
-      <c r="S101" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="102" spans="13:19">
-      <c r="M102" t="s">
-        <v>17</v>
-      </c>
-      <c r="N102" t="s">
-        <v>440</v>
-      </c>
-      <c r="O102" t="s">
-        <v>243</v>
-      </c>
-      <c r="P102" t="s">
-        <v>441</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>25</v>
-      </c>
-      <c r="R102" t="s">
-        <v>35</v>
-      </c>
-      <c r="S102" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="103" spans="13:19">
-      <c r="M103" t="s">
-        <v>17</v>
-      </c>
-      <c r="N103" t="s">
-        <v>442</v>
-      </c>
-      <c r="O103" t="s">
-        <v>243</v>
-      </c>
-      <c r="P103" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>25</v>
-      </c>
-      <c r="R103" t="s">
-        <v>35</v>
-      </c>
-      <c r="S103" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="104" spans="13:19">
-      <c r="M104" t="s">
-        <v>17</v>
-      </c>
-      <c r="N104" t="s">
-        <v>444</v>
-      </c>
-      <c r="O104" t="s">
-        <v>243</v>
-      </c>
-      <c r="P104" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q104" t="s">
-        <v>25</v>
-      </c>
-      <c r="R104" t="s">
-        <v>35</v>
-      </c>
-      <c r="S104" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="105" spans="13:19">
-      <c r="M105" t="s">
-        <v>17</v>
-      </c>
-      <c r="N105" t="s">
-        <v>446</v>
-      </c>
-      <c r="O105" t="s">
-        <v>243</v>
-      </c>
-      <c r="P105" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q105" t="s">
-        <v>25</v>
-      </c>
-      <c r="R105" t="s">
-        <v>35</v>
-      </c>
-      <c r="S105" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="106" spans="13:19">
-      <c r="M106" t="s">
-        <v>17</v>
-      </c>
-      <c r="N106" t="s">
-        <v>448</v>
-      </c>
-      <c r="O106" t="s">
-        <v>243</v>
-      </c>
-      <c r="P106" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q106" t="s">
-        <v>25</v>
-      </c>
-      <c r="R106" t="s">
-        <v>35</v>
-      </c>
-      <c r="S106" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="107" spans="13:19">
-      <c r="M107" t="s">
-        <v>17</v>
-      </c>
-      <c r="N107" t="s">
-        <v>450</v>
-      </c>
-      <c r="O107" t="s">
-        <v>243</v>
-      </c>
-      <c r="P107" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>25</v>
-      </c>
-      <c r="R107" t="s">
-        <v>35</v>
-      </c>
-      <c r="S107" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="108" spans="13:19">
-      <c r="M108" t="s">
-        <v>17</v>
-      </c>
-      <c r="N108" t="s">
-        <v>452</v>
-      </c>
-      <c r="O108" t="s">
-        <v>243</v>
-      </c>
-      <c r="P108" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>25</v>
-      </c>
-      <c r="R108" t="s">
-        <v>35</v>
-      </c>
-      <c r="S108" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="109" spans="13:19">
-      <c r="M109" t="s">
-        <v>17</v>
-      </c>
-      <c r="N109" t="s">
-        <v>454</v>
-      </c>
-      <c r="O109" t="s">
-        <v>243</v>
-      </c>
-      <c r="P109" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>25</v>
-      </c>
-      <c r="R109" t="s">
-        <v>35</v>
-      </c>
-      <c r="S109" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="110" spans="13:19">
-      <c r="M110" t="s">
-        <v>17</v>
-      </c>
-      <c r="N110" t="s">
-        <v>456</v>
-      </c>
-      <c r="O110" t="s">
-        <v>243</v>
-      </c>
-      <c r="P110" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>25</v>
-      </c>
-      <c r="R110" t="s">
-        <v>35</v>
-      </c>
-      <c r="S110" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C869F5D4-FCC7-4CE1-912C-0B1DF6EBA0C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6452122F-E617-4C2C-9417-032CBF1102EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="803">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -781,7 +781,7 @@
     <t>elc_spv_POL_001</t>
   </si>
   <si>
-    <t>solar electricity near Bialystok (cluster 1)</t>
+    <t>solar electricity near Bydgoszcz (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -790,115 +790,283 @@
     <t>elc_spv_POL_002</t>
   </si>
   <si>
-    <t>solar electricity near Elk (cluster 2)</t>
+    <t>solar electricity near Bialystok (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_POL_003</t>
   </si>
   <si>
-    <t>solar electricity near Rzeszow (cluster 3)</t>
+    <t>solar electricity near Gorzow Wielkopolski (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_POL_004</t>
   </si>
   <si>
-    <t>solar electricity near Krakow (cluster 4)</t>
+    <t>solar electricity near Wroclaw (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_POL_005</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 5)</t>
+    <t>solar electricity near Wroclaw (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_POL_006</t>
   </si>
   <si>
-    <t>solar electricity near Lublin (cluster 6)</t>
+    <t>solar electricity near Wroclaw (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_POL_007</t>
   </si>
   <si>
-    <t>solar electricity near Stargard Szczecinski (cluster 7)</t>
+    <t>solar electricity near Olsztyn (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_POL_008</t>
   </si>
   <si>
-    <t>solar electricity near Pila (cluster 8)</t>
+    <t>solar electricity near Slupsk (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_POL_009</t>
   </si>
   <si>
-    <t>solar electricity near Torun (cluster 9)</t>
+    <t>solar electricity near Olsztyn (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_POL_010</t>
   </si>
   <si>
-    <t>solar electricity near Olsztyn (cluster 10)</t>
+    <t>solar electricity near Legnica (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_POL_011</t>
   </si>
   <si>
-    <t>solar electricity near Elblag (cluster 11)</t>
+    <t>solar electricity near Gdansk (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_POL_012</t>
   </si>
   <si>
-    <t>solar electricity near Poznan (cluster 12)</t>
+    <t>solar electricity near Lomza (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_POL_013</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 13)</t>
+    <t>solar electricity near Zielona Gora (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_POL_014</t>
   </si>
   <si>
-    <t>solar electricity near Legnica (cluster 14)</t>
+    <t>solar electricity near Szczecin (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_POL_015</t>
   </si>
   <si>
-    <t>solar electricity near Zielona Gora (cluster 15)</t>
+    <t>solar electricity near Rzeszow (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_POL_016</t>
   </si>
   <si>
-    <t>solar electricity near Wroclaw (cluster 16)</t>
+    <t>solar electricity near Suwalki (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_POL_017</t>
   </si>
   <si>
-    <t>solar electricity near Katowice (cluster 17)</t>
+    <t>solar electricity near Lodz (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_POL_018</t>
   </si>
   <si>
-    <t>solar electricity near Warsaw (cluster 18)</t>
+    <t>solar electricity near Lodz (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_POL_019</t>
   </si>
   <si>
-    <t>solar electricity near Radom (cluster 19)</t>
+    <t>solar electricity near Zamosc (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_POL_020</t>
   </si>
   <si>
-    <t>solar electricity near Lodz (cluster 20)</t>
+    <t>solar electricity near Koszalin (cluster 20)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_021</t>
+  </si>
+  <si>
+    <t>solar electricity near Zielona Gora (cluster 21)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_022</t>
+  </si>
+  <si>
+    <t>solar electricity near Katowice (cluster 22)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_023</t>
+  </si>
+  <si>
+    <t>solar electricity near Tarnow (cluster 23)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_024</t>
+  </si>
+  <si>
+    <t>solar electricity near Lublin (cluster 24)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_025</t>
+  </si>
+  <si>
+    <t>solar electricity near Rzeszow (cluster 25)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_026</t>
+  </si>
+  <si>
+    <t>solar electricity near Kielce (cluster 26)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_027</t>
+  </si>
+  <si>
+    <t>solar electricity near Mielec (cluster 27)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_028</t>
+  </si>
+  <si>
+    <t>solar electricity near Stalowa Wola (cluster 28)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_029</t>
+  </si>
+  <si>
+    <t>solar electricity near Czestochowa (cluster 29)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_030</t>
+  </si>
+  <si>
+    <t>solar electricity near Torun (cluster 30)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_031</t>
+  </si>
+  <si>
+    <t>solar electricity near Ostrowiec Swietokrzyski (cluster 31)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_032</t>
+  </si>
+  <si>
+    <t>solar electricity near Opole (cluster 32)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_033</t>
+  </si>
+  <si>
+    <t>solar electricity near Konin (cluster 33)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_034</t>
+  </si>
+  <si>
+    <t>solar electricity near Koszalin (cluster 34)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_035</t>
+  </si>
+  <si>
+    <t>solar electricity near Warsaw (cluster 35)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_036</t>
+  </si>
+  <si>
+    <t>solar electricity near Katowice (cluster 36)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_037</t>
+  </si>
+  <si>
+    <t>solar electricity near Elk (cluster 37)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_038</t>
+  </si>
+  <si>
+    <t>solar electricity near Poznan (cluster 38)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_039</t>
+  </si>
+  <si>
+    <t>solar electricity near Opole (cluster 39)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_040</t>
+  </si>
+  <si>
+    <t>solar electricity near Szczecin (cluster 40)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_041</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 41)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_042</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 42)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_043</t>
+  </si>
+  <si>
+    <t>solar electricity near Elblag (cluster 43)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_044</t>
+  </si>
+  <si>
+    <t>solar electricity near Plock (cluster 44)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_045</t>
+  </si>
+  <si>
+    <t>solar electricity near Wroclaw (cluster 45)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_046</t>
+  </si>
+  <si>
+    <t>solar electricity near Gdansk (cluster 46)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_047</t>
+  </si>
+  <si>
+    <t>solar electricity near Krakow (cluster 47)</t>
+  </si>
+  <si>
+    <t>elc_spv_POL_048</t>
+  </si>
+  <si>
+    <t>solar electricity near Lublin (cluster 48)</t>
   </si>
   <si>
     <t>elc_wof_POL_001</t>
@@ -916,25 +1084,25 @@
     <t>elc_wof_POL_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 3)</t>
+    <t>wind offshore electricity near Koszalin (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_POL_004</t>
   </si>
   <si>
-    <t>wind offshore electricity near Slupsk (cluster 4)</t>
+    <t>wind offshore electricity near Koszalin (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_POL_005</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 5)</t>
+    <t>wind offshore electricity near Koszalin (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_POL_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Gdansk (cluster 6)</t>
+    <t>wind offshore electricity near Koszalin (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_POL_007</t>
@@ -946,133 +1114,289 @@
     <t>elc_wof_POL_008</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 8)</t>
+    <t>wind offshore electricity near Gdynia (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_POL_009</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 9)</t>
+    <t>wind offshore electricity near Gdansk (cluster 9)</t>
   </si>
   <si>
     <t>elc_wof_POL_010</t>
   </si>
   <si>
-    <t>wind offshore electricity near Koszalin (cluster 10)</t>
+    <t>wind offshore electricity near Gdansk (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_001</t>
   </si>
   <si>
-    <t>wind onshore electricity near Walbrzych (cluster 1)</t>
+    <t>wind onshore electricity near Bydgoszcz (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_POL_002</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rybnik (cluster 2)</t>
+    <t>wind onshore electricity near Bialystok (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_POL_003</t>
   </si>
   <si>
-    <t>wind onshore electricity near Zielona Gora (cluster 3)</t>
+    <t>wind onshore electricity near Gorzow Wielkopolski (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_POL_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Poznan (cluster 4)</t>
+    <t>wind onshore electricity near Legnica (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Elblag (cluster 5)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Stargard Szczecinski (cluster 6)</t>
+    <t>wind onshore electricity near Wroclaw (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Slupsk (cluster 7)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_POL_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Pila (cluster 8)</t>
+    <t>wind onshore electricity near Slupsk (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_POL_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bialystok (cluster 9)</t>
+    <t>wind onshore electricity near Olsztyn (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Olsztyn (cluster 10)</t>
+    <t>wind onshore electricity near Legnica (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Siedlce (cluster 11)</t>
+    <t>wind onshore electricity near Gdansk (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_POL_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Warsaw (cluster 12)</t>
+    <t>wind onshore electricity near Lomza (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_POL_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kalisz (cluster 13)</t>
+    <t>wind onshore electricity near Zielona Gora (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_POL_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Wloclawek (cluster 14)</t>
+    <t>wind onshore electricity near Szczecin (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_POL_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katowice (cluster 15)</t>
+    <t>wind onshore electricity near Rzeszow (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_POL_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Piotrkow Trybunalski (cluster 16)</t>
+    <t>wind onshore electricity near Suwalki (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_POL_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Lublin (cluster 17)</t>
+    <t>wind onshore electricity near Lodz (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_POL_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 18)</t>
+    <t>wind onshore electricity near Lodz (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rzeszow (cluster 19)</t>
+    <t>wind onshore electricity near Zamosc (cluster 19)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_020</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Koszalin (cluster 20)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_021</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Zielona Gora (cluster 21)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_022</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Tarnow (cluster 22)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_023</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Lublin (cluster 23)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_024</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Rzeszow (cluster 24)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_025</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Radom (cluster 25)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_026</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Mielec (cluster 26)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_027</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Stalowa Wola (cluster 27)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_028</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Czestochowa (cluster 28)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_029</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Torun (cluster 29)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_030</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Radom (cluster 30)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_031</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Konin (cluster 31)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_032</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Koszalin (cluster 32)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_033</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Warsaw (cluster 33)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_034</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Katowice (cluster 34)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_035</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Elk (cluster 35)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_036</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Poznan (cluster 36)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_037</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Kedzierzyn-Kozle (cluster 37)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_038</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Szczecin (cluster 38)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_039</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 39)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_040</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Elblag (cluster 40)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_041</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Plock (cluster 41)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_042</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Kalisz (cluster 42)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_043</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Gdansk (cluster 43)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_044</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Krakow (cluster 44)</t>
+  </si>
+  <si>
+    <t>elc_won_POL_045</t>
+  </si>
+  <si>
+    <t>wind onshore electricity near Lublin (cluster 45)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4520,13 +4844,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A03BC4-AD77-4FF1-B587-1AD45746BFA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998A17F4-64D4-494F-B45A-8E188B4FDBBC}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:8">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -4557,19 +4881,19 @@
         <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>538</v>
+        <v>646</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>539</v>
+        <v>647</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H5" t="s">
         <v>195</v>
@@ -4580,19 +4904,19 @@
         <v>192</v>
       </c>
       <c r="C6" t="s">
-        <v>541</v>
+        <v>649</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>542</v>
+        <v>650</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H6" t="s">
         <v>195</v>
@@ -4603,19 +4927,19 @@
         <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>543</v>
+        <v>651</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>544</v>
+        <v>652</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H7" t="s">
         <v>195</v>
@@ -4626,19 +4950,19 @@
         <v>192</v>
       </c>
       <c r="C8" t="s">
-        <v>545</v>
+        <v>653</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>546</v>
+        <v>654</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H8" t="s">
         <v>195</v>
@@ -4649,19 +4973,19 @@
         <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>547</v>
+        <v>655</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>548</v>
+        <v>656</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H9" t="s">
         <v>195</v>
@@ -4672,19 +4996,19 @@
         <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>549</v>
+        <v>657</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>550</v>
+        <v>658</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H10" t="s">
         <v>195</v>
@@ -4695,19 +5019,19 @@
         <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>551</v>
+        <v>659</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>552</v>
+        <v>660</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H11" t="s">
         <v>195</v>
@@ -4718,19 +5042,19 @@
         <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>553</v>
+        <v>661</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>554</v>
+        <v>662</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H12" t="s">
         <v>195</v>
@@ -4741,19 +5065,19 @@
         <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>555</v>
+        <v>663</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>556</v>
+        <v>664</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H13" t="s">
         <v>195</v>
@@ -4764,19 +5088,19 @@
         <v>192</v>
       </c>
       <c r="C14" t="s">
-        <v>557</v>
+        <v>665</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>558</v>
+        <v>666</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H14" t="s">
         <v>195</v>
@@ -4787,19 +5111,19 @@
         <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>559</v>
+        <v>667</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>560</v>
+        <v>668</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
       </c>
       <c r="G15" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H15" t="s">
         <v>195</v>
@@ -4810,19 +5134,19 @@
         <v>192</v>
       </c>
       <c r="C16" t="s">
-        <v>561</v>
+        <v>669</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>562</v>
+        <v>670</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H16" t="s">
         <v>195</v>
@@ -4833,19 +5157,19 @@
         <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>563</v>
+        <v>671</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>564</v>
+        <v>672</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
       </c>
       <c r="G17" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H17" t="s">
         <v>195</v>
@@ -4856,19 +5180,19 @@
         <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>565</v>
+        <v>673</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>566</v>
+        <v>674</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
       </c>
       <c r="G18" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H18" t="s">
         <v>195</v>
@@ -4879,19 +5203,19 @@
         <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>567</v>
+        <v>675</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>568</v>
+        <v>676</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H19" t="s">
         <v>195</v>
@@ -4902,19 +5226,19 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>569</v>
+        <v>677</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>570</v>
+        <v>678</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H20" t="s">
         <v>195</v>
@@ -4925,19 +5249,19 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>571</v>
+        <v>679</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>572</v>
+        <v>680</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H21" t="s">
         <v>195</v>
@@ -4948,19 +5272,19 @@
         <v>192</v>
       </c>
       <c r="C22" t="s">
-        <v>573</v>
+        <v>681</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>574</v>
+        <v>682</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H22" t="s">
         <v>195</v>
@@ -4971,19 +5295,19 @@
         <v>192</v>
       </c>
       <c r="C23" t="s">
-        <v>575</v>
+        <v>683</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>576</v>
+        <v>684</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
       </c>
       <c r="G23" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H23" t="s">
         <v>195</v>
@@ -4994,19 +5318,19 @@
         <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>577</v>
+        <v>685</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>578</v>
+        <v>686</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H24" t="s">
         <v>195</v>
@@ -5017,19 +5341,19 @@
         <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>579</v>
+        <v>687</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>580</v>
+        <v>688</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
       </c>
       <c r="G25" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H25" t="s">
         <v>195</v>
@@ -5040,19 +5364,19 @@
         <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>581</v>
+        <v>689</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>582</v>
+        <v>690</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
       </c>
       <c r="G26" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H26" t="s">
         <v>195</v>
@@ -5063,19 +5387,19 @@
         <v>192</v>
       </c>
       <c r="C27" t="s">
-        <v>583</v>
+        <v>691</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>584</v>
+        <v>692</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H27" t="s">
         <v>195</v>
@@ -5086,19 +5410,19 @@
         <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>585</v>
+        <v>693</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>586</v>
+        <v>694</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H28" t="s">
         <v>195</v>
@@ -5109,19 +5433,19 @@
         <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>587</v>
+        <v>695</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>588</v>
+        <v>696</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
       </c>
       <c r="G29" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H29" t="s">
         <v>195</v>
@@ -5132,19 +5456,19 @@
         <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>589</v>
+        <v>697</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>590</v>
+        <v>698</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
       </c>
       <c r="G30" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H30" t="s">
         <v>195</v>
@@ -5155,19 +5479,19 @@
         <v>192</v>
       </c>
       <c r="C31" t="s">
-        <v>591</v>
+        <v>699</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>592</v>
+        <v>700</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
       </c>
       <c r="G31" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H31" t="s">
         <v>195</v>
@@ -5178,19 +5502,19 @@
         <v>192</v>
       </c>
       <c r="C32" t="s">
-        <v>593</v>
+        <v>701</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>594</v>
+        <v>702</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
       </c>
       <c r="G32" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H32" t="s">
         <v>195</v>
@@ -5201,19 +5525,19 @@
         <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>595</v>
+        <v>703</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>596</v>
+        <v>704</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
       </c>
       <c r="G33" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H33" t="s">
         <v>195</v>
@@ -5224,19 +5548,19 @@
         <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>597</v>
+        <v>705</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>598</v>
+        <v>706</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H34" t="s">
         <v>195</v>
@@ -5247,19 +5571,19 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>599</v>
+        <v>707</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>600</v>
+        <v>708</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H35" t="s">
         <v>195</v>
@@ -5270,19 +5594,19 @@
         <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>601</v>
+        <v>709</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>602</v>
+        <v>710</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
       </c>
       <c r="G36" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H36" t="s">
         <v>195</v>
@@ -5293,19 +5617,19 @@
         <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>603</v>
+        <v>711</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>604</v>
+        <v>712</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
       </c>
       <c r="G37" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H37" t="s">
         <v>195</v>
@@ -5316,19 +5640,19 @@
         <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>605</v>
+        <v>713</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>606</v>
+        <v>714</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
       </c>
       <c r="G38" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H38" t="s">
         <v>195</v>
@@ -5339,19 +5663,19 @@
         <v>192</v>
       </c>
       <c r="C39" t="s">
-        <v>607</v>
+        <v>715</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>608</v>
+        <v>716</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
       </c>
       <c r="G39" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H39" t="s">
         <v>195</v>
@@ -5362,19 +5686,19 @@
         <v>192</v>
       </c>
       <c r="C40" t="s">
-        <v>609</v>
+        <v>717</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>610</v>
+        <v>718</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
       </c>
       <c r="G40" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H40" t="s">
         <v>195</v>
@@ -5385,19 +5709,19 @@
         <v>192</v>
       </c>
       <c r="C41" t="s">
-        <v>611</v>
+        <v>719</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>612</v>
+        <v>720</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -5408,19 +5732,19 @@
         <v>192</v>
       </c>
       <c r="C42" t="s">
-        <v>613</v>
+        <v>721</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>614</v>
+        <v>722</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
       </c>
       <c r="G42" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -5431,19 +5755,19 @@
         <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>615</v>
+        <v>723</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>616</v>
+        <v>724</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H43" t="s">
         <v>195</v>
@@ -5454,19 +5778,19 @@
         <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>617</v>
+        <v>725</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>618</v>
+        <v>726</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H44" t="s">
         <v>195</v>
@@ -5477,19 +5801,19 @@
         <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>619</v>
+        <v>727</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>620</v>
+        <v>728</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
       </c>
       <c r="G45" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H45" t="s">
         <v>195</v>
@@ -5500,19 +5824,19 @@
         <v>192</v>
       </c>
       <c r="C46" t="s">
-        <v>621</v>
+        <v>729</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>622</v>
+        <v>730</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H46" t="s">
         <v>195</v>
@@ -5523,19 +5847,19 @@
         <v>192</v>
       </c>
       <c r="C47" t="s">
-        <v>623</v>
+        <v>731</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>624</v>
+        <v>732</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
       </c>
       <c r="G47" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H47" t="s">
         <v>195</v>
@@ -5546,19 +5870,19 @@
         <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>625</v>
+        <v>733</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>626</v>
+        <v>734</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
       </c>
       <c r="G48" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H48" t="s">
         <v>195</v>
@@ -5569,19 +5893,19 @@
         <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>627</v>
+        <v>735</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>628</v>
+        <v>736</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
       </c>
       <c r="G49" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H49" t="s">
         <v>195</v>
@@ -5592,19 +5916,19 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>629</v>
+        <v>737</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>630</v>
+        <v>738</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H50" t="s">
         <v>195</v>
@@ -5615,19 +5939,19 @@
         <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>631</v>
+        <v>739</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>632</v>
+        <v>740</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
       </c>
       <c r="G51" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H51" t="s">
         <v>195</v>
@@ -5638,19 +5962,19 @@
         <v>192</v>
       </c>
       <c r="C52" t="s">
-        <v>633</v>
+        <v>741</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>634</v>
+        <v>742</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H52" t="s">
         <v>195</v>
@@ -5661,19 +5985,19 @@
         <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>635</v>
+        <v>743</v>
       </c>
       <c r="D53" t="s">
         <v>243</v>
       </c>
       <c r="E53" t="s">
-        <v>636</v>
+        <v>744</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
       </c>
       <c r="G53" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H53" t="s">
         <v>195</v>
@@ -5684,19 +6008,19 @@
         <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>637</v>
+        <v>745</v>
       </c>
       <c r="D54" t="s">
         <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>638</v>
+        <v>746</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
       </c>
       <c r="G54" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H54" t="s">
         <v>195</v>
@@ -5707,19 +6031,19 @@
         <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>639</v>
+        <v>747</v>
       </c>
       <c r="D55" t="s">
         <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>640</v>
+        <v>748</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H55" t="s">
         <v>195</v>
@@ -5730,19 +6054,19 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>641</v>
+        <v>749</v>
       </c>
       <c r="D56" t="s">
         <v>243</v>
       </c>
       <c r="E56" t="s">
-        <v>642</v>
+        <v>750</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H56" t="s">
         <v>195</v>
@@ -5753,19 +6077,19 @@
         <v>192</v>
       </c>
       <c r="C57" t="s">
-        <v>643</v>
+        <v>751</v>
       </c>
       <c r="D57" t="s">
         <v>243</v>
       </c>
       <c r="E57" t="s">
-        <v>644</v>
+        <v>752</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H57" t="s">
         <v>195</v>
@@ -5776,19 +6100,19 @@
         <v>192</v>
       </c>
       <c r="C58" t="s">
-        <v>645</v>
+        <v>753</v>
       </c>
       <c r="D58" t="s">
         <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>646</v>
+        <v>754</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H58" t="s">
         <v>195</v>
@@ -5799,19 +6123,19 @@
         <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>647</v>
+        <v>755</v>
       </c>
       <c r="D59" t="s">
         <v>243</v>
       </c>
       <c r="E59" t="s">
-        <v>648</v>
+        <v>756</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H59" t="s">
         <v>195</v>
@@ -5822,19 +6146,19 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>649</v>
+        <v>757</v>
       </c>
       <c r="D60" t="s">
         <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>650</v>
+        <v>758</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H60" t="s">
         <v>195</v>
@@ -5845,19 +6169,19 @@
         <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>651</v>
+        <v>759</v>
       </c>
       <c r="D61" t="s">
         <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>652</v>
+        <v>760</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H61" t="s">
         <v>195</v>
@@ -5868,19 +6192,19 @@
         <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>653</v>
+        <v>761</v>
       </c>
       <c r="D62" t="s">
         <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>654</v>
+        <v>762</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
       </c>
       <c r="G62" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H62" t="s">
         <v>195</v>
@@ -5891,19 +6215,19 @@
         <v>192</v>
       </c>
       <c r="C63" t="s">
-        <v>655</v>
+        <v>763</v>
       </c>
       <c r="D63" t="s">
         <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>656</v>
+        <v>764</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H63" t="s">
         <v>195</v>
@@ -5914,19 +6238,19 @@
         <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>657</v>
+        <v>765</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>658</v>
+        <v>766</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H64" t="s">
         <v>195</v>
@@ -5937,19 +6261,19 @@
         <v>192</v>
       </c>
       <c r="C65" t="s">
-        <v>659</v>
+        <v>767</v>
       </c>
       <c r="D65" t="s">
         <v>243</v>
       </c>
       <c r="E65" t="s">
-        <v>660</v>
+        <v>768</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H65" t="s">
         <v>195</v>
@@ -5960,19 +6284,19 @@
         <v>192</v>
       </c>
       <c r="C66" t="s">
-        <v>661</v>
+        <v>769</v>
       </c>
       <c r="D66" t="s">
         <v>243</v>
       </c>
       <c r="E66" t="s">
-        <v>662</v>
+        <v>770</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H66" t="s">
         <v>195</v>
@@ -5983,19 +6307,19 @@
         <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>663</v>
+        <v>771</v>
       </c>
       <c r="D67" t="s">
         <v>243</v>
       </c>
       <c r="E67" t="s">
-        <v>664</v>
+        <v>772</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
       </c>
       <c r="G67" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H67" t="s">
         <v>195</v>
@@ -6006,19 +6330,19 @@
         <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>665</v>
+        <v>773</v>
       </c>
       <c r="D68" t="s">
         <v>243</v>
       </c>
       <c r="E68" t="s">
-        <v>666</v>
+        <v>774</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H68" t="s">
         <v>195</v>
@@ -6029,19 +6353,19 @@
         <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>667</v>
+        <v>775</v>
       </c>
       <c r="D69" t="s">
         <v>243</v>
       </c>
       <c r="E69" t="s">
-        <v>668</v>
+        <v>776</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
       </c>
       <c r="G69" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H69" t="s">
         <v>195</v>
@@ -6052,19 +6376,19 @@
         <v>192</v>
       </c>
       <c r="C70" t="s">
-        <v>669</v>
+        <v>777</v>
       </c>
       <c r="D70" t="s">
         <v>243</v>
       </c>
       <c r="E70" t="s">
-        <v>670</v>
+        <v>778</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H70" t="s">
         <v>195</v>
@@ -6075,19 +6399,19 @@
         <v>192</v>
       </c>
       <c r="C71" t="s">
-        <v>671</v>
+        <v>779</v>
       </c>
       <c r="D71" t="s">
         <v>243</v>
       </c>
       <c r="E71" t="s">
-        <v>672</v>
+        <v>780</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H71" t="s">
         <v>195</v>
@@ -6098,19 +6422,19 @@
         <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>673</v>
+        <v>781</v>
       </c>
       <c r="D72" t="s">
         <v>243</v>
       </c>
       <c r="E72" t="s">
-        <v>674</v>
+        <v>782</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H72" t="s">
         <v>195</v>
@@ -6121,19 +6445,19 @@
         <v>192</v>
       </c>
       <c r="C73" t="s">
-        <v>675</v>
+        <v>783</v>
       </c>
       <c r="D73" t="s">
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>676</v>
+        <v>784</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
       </c>
       <c r="G73" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H73" t="s">
         <v>195</v>
@@ -6144,19 +6468,19 @@
         <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>677</v>
+        <v>785</v>
       </c>
       <c r="D74" t="s">
         <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>678</v>
+        <v>786</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
       </c>
       <c r="G74" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H74" t="s">
         <v>195</v>
@@ -6167,19 +6491,19 @@
         <v>192</v>
       </c>
       <c r="C75" t="s">
-        <v>679</v>
+        <v>787</v>
       </c>
       <c r="D75" t="s">
         <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>680</v>
+        <v>788</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
       </c>
       <c r="G75" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H75" t="s">
         <v>195</v>
@@ -6190,19 +6514,19 @@
         <v>192</v>
       </c>
       <c r="C76" t="s">
-        <v>681</v>
+        <v>789</v>
       </c>
       <c r="D76" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>682</v>
+        <v>790</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H76" t="s">
         <v>195</v>
@@ -6213,19 +6537,19 @@
         <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>683</v>
+        <v>791</v>
       </c>
       <c r="D77" t="s">
         <v>243</v>
       </c>
       <c r="E77" t="s">
-        <v>684</v>
+        <v>792</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
       </c>
       <c r="G77" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H77" t="s">
         <v>195</v>
@@ -6236,19 +6560,19 @@
         <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>685</v>
+        <v>793</v>
       </c>
       <c r="D78" t="s">
         <v>243</v>
       </c>
       <c r="E78" t="s">
-        <v>686</v>
+        <v>794</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H78" t="s">
         <v>195</v>
@@ -6259,19 +6583,19 @@
         <v>192</v>
       </c>
       <c r="C79" t="s">
-        <v>687</v>
+        <v>795</v>
       </c>
       <c r="D79" t="s">
         <v>243</v>
       </c>
       <c r="E79" t="s">
-        <v>688</v>
+        <v>796</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
       </c>
       <c r="G79" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H79" t="s">
         <v>195</v>
@@ -6282,19 +6606,19 @@
         <v>192</v>
       </c>
       <c r="C80" t="s">
-        <v>689</v>
+        <v>797</v>
       </c>
       <c r="D80" t="s">
         <v>243</v>
       </c>
       <c r="E80" t="s">
-        <v>690</v>
+        <v>798</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
       </c>
       <c r="G80" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H80" t="s">
         <v>195</v>
@@ -6305,19 +6629,19 @@
         <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>691</v>
+        <v>799</v>
       </c>
       <c r="D81" t="s">
         <v>243</v>
       </c>
       <c r="E81" t="s">
-        <v>692</v>
+        <v>800</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
       </c>
       <c r="G81" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H81" t="s">
         <v>195</v>
@@ -6328,19 +6652,19 @@
         <v>192</v>
       </c>
       <c r="C82" t="s">
-        <v>693</v>
+        <v>801</v>
       </c>
       <c r="D82" t="s">
         <v>243</v>
       </c>
       <c r="E82" t="s">
-        <v>694</v>
+        <v>802</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>540</v>
+        <v>648</v>
       </c>
       <c r="H82" t="s">
         <v>195</v>
@@ -6352,13 +6676,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E3B025-E8E4-4DE3-AB34-65FF4B1EBC22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C211FDF-42D1-40C2-B89C-5BB2729B9EEC}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -6392,13 +6716,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>550</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>443</v>
+        <v>551</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -6407,7 +6731,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -6418,13 +6742,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>444</v>
+        <v>552</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>445</v>
+        <v>553</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -6433,7 +6757,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -6444,13 +6768,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>446</v>
+        <v>554</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>447</v>
+        <v>555</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -6459,7 +6783,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -6470,13 +6794,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>448</v>
+        <v>556</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>449</v>
+        <v>557</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -6485,7 +6809,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -6496,13 +6820,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>450</v>
+        <v>558</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>451</v>
+        <v>559</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -6511,7 +6835,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -6522,13 +6846,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>452</v>
+        <v>560</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>453</v>
+        <v>561</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -6537,7 +6861,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -6548,13 +6872,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>454</v>
+        <v>562</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>455</v>
+        <v>563</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -6563,7 +6887,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -6574,13 +6898,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>456</v>
+        <v>564</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>457</v>
+        <v>565</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -6589,7 +6913,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -6600,13 +6924,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>458</v>
+        <v>566</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>459</v>
+        <v>567</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -6615,7 +6939,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -6626,13 +6950,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>460</v>
+        <v>568</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>461</v>
+        <v>569</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -6641,7 +6965,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -6652,13 +6976,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>462</v>
+        <v>570</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>463</v>
+        <v>571</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -6667,7 +6991,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -6678,13 +7002,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>464</v>
+        <v>572</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>465</v>
+        <v>573</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -6693,7 +7017,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -6704,13 +7028,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>466</v>
+        <v>574</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>467</v>
+        <v>575</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -6719,7 +7043,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -6730,13 +7054,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>468</v>
+        <v>576</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>469</v>
+        <v>577</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -6745,7 +7069,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -6756,13 +7080,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>470</v>
+        <v>578</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>471</v>
+        <v>579</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -6771,7 +7095,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -6782,13 +7106,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>472</v>
+        <v>580</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>473</v>
+        <v>581</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -6797,7 +7121,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -6808,13 +7132,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>474</v>
+        <v>582</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>475</v>
+        <v>583</v>
       </c>
       <c r="F21" t="s">
         <v>233</v>
@@ -6823,7 +7147,7 @@
         <v>232</v>
       </c>
       <c r="H21" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -6834,13 +7158,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>476</v>
+        <v>584</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="F22" t="s">
         <v>233</v>
@@ -6849,7 +7173,7 @@
         <v>232</v>
       </c>
       <c r="H22" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -6860,13 +7184,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>478</v>
+        <v>586</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>479</v>
+        <v>587</v>
       </c>
       <c r="F23" t="s">
         <v>233</v>
@@ -6875,7 +7199,7 @@
         <v>232</v>
       </c>
       <c r="H23" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -6886,13 +7210,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>480</v>
+        <v>588</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>481</v>
+        <v>589</v>
       </c>
       <c r="F24" t="s">
         <v>233</v>
@@ -6901,7 +7225,7 @@
         <v>232</v>
       </c>
       <c r="H24" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -6912,13 +7236,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>482</v>
+        <v>590</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>483</v>
+        <v>591</v>
       </c>
       <c r="F25" t="s">
         <v>233</v>
@@ -6927,7 +7251,7 @@
         <v>232</v>
       </c>
       <c r="H25" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -6938,13 +7262,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>484</v>
+        <v>592</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>485</v>
+        <v>593</v>
       </c>
       <c r="F26" t="s">
         <v>233</v>
@@ -6953,7 +7277,7 @@
         <v>232</v>
       </c>
       <c r="H26" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -6964,13 +7288,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>486</v>
+        <v>594</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>487</v>
+        <v>595</v>
       </c>
       <c r="F27" t="s">
         <v>233</v>
@@ -6979,7 +7303,7 @@
         <v>232</v>
       </c>
       <c r="H27" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -6990,13 +7314,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>488</v>
+        <v>596</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>489</v>
+        <v>597</v>
       </c>
       <c r="F28" t="s">
         <v>233</v>
@@ -7005,7 +7329,7 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -7016,13 +7340,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>490</v>
+        <v>598</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>491</v>
+        <v>599</v>
       </c>
       <c r="F29" t="s">
         <v>233</v>
@@ -7031,7 +7355,7 @@
         <v>232</v>
       </c>
       <c r="H29" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -7042,13 +7366,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>492</v>
+        <v>600</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>493</v>
+        <v>601</v>
       </c>
       <c r="F30" t="s">
         <v>233</v>
@@ -7057,7 +7381,7 @@
         <v>232</v>
       </c>
       <c r="H30" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -7068,13 +7392,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>494</v>
+        <v>602</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>495</v>
+        <v>603</v>
       </c>
       <c r="F31" t="s">
         <v>233</v>
@@ -7083,7 +7407,7 @@
         <v>232</v>
       </c>
       <c r="H31" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -7094,13 +7418,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>496</v>
+        <v>604</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>497</v>
+        <v>605</v>
       </c>
       <c r="F32" t="s">
         <v>233</v>
@@ -7109,7 +7433,7 @@
         <v>232</v>
       </c>
       <c r="H32" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -7120,13 +7444,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>498</v>
+        <v>606</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>499</v>
+        <v>607</v>
       </c>
       <c r="F33" t="s">
         <v>233</v>
@@ -7135,7 +7459,7 @@
         <v>232</v>
       </c>
       <c r="H33" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -7146,13 +7470,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>500</v>
+        <v>608</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>501</v>
+        <v>609</v>
       </c>
       <c r="F34" t="s">
         <v>233</v>
@@ -7161,7 +7485,7 @@
         <v>232</v>
       </c>
       <c r="H34" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -7172,13 +7496,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>502</v>
+        <v>610</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>503</v>
+        <v>611</v>
       </c>
       <c r="F35" t="s">
         <v>233</v>
@@ -7187,7 +7511,7 @@
         <v>232</v>
       </c>
       <c r="H35" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -7198,13 +7522,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>504</v>
+        <v>612</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>505</v>
+        <v>613</v>
       </c>
       <c r="F36" t="s">
         <v>233</v>
@@ -7213,7 +7537,7 @@
         <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -7224,13 +7548,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>506</v>
+        <v>614</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>507</v>
+        <v>615</v>
       </c>
       <c r="F37" t="s">
         <v>233</v>
@@ -7239,7 +7563,7 @@
         <v>232</v>
       </c>
       <c r="H37" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -7250,13 +7574,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>508</v>
+        <v>616</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>509</v>
+        <v>617</v>
       </c>
       <c r="F38" t="s">
         <v>233</v>
@@ -7265,7 +7589,7 @@
         <v>232</v>
       </c>
       <c r="H38" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -7276,13 +7600,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>510</v>
+        <v>618</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>511</v>
+        <v>619</v>
       </c>
       <c r="F39" t="s">
         <v>233</v>
@@ -7291,7 +7615,7 @@
         <v>232</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -7302,13 +7626,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>512</v>
+        <v>620</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>513</v>
+        <v>621</v>
       </c>
       <c r="F40" t="s">
         <v>233</v>
@@ -7317,7 +7641,7 @@
         <v>232</v>
       </c>
       <c r="H40" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -7328,13 +7652,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>514</v>
+        <v>622</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>515</v>
+        <v>623</v>
       </c>
       <c r="F41" t="s">
         <v>233</v>
@@ -7343,7 +7667,7 @@
         <v>232</v>
       </c>
       <c r="H41" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -7354,13 +7678,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>516</v>
+        <v>624</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>517</v>
+        <v>625</v>
       </c>
       <c r="F42" t="s">
         <v>233</v>
@@ -7369,7 +7693,7 @@
         <v>232</v>
       </c>
       <c r="H42" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -7380,13 +7704,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>518</v>
+        <v>626</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>519</v>
+        <v>627</v>
       </c>
       <c r="F43" t="s">
         <v>233</v>
@@ -7395,7 +7719,7 @@
         <v>232</v>
       </c>
       <c r="H43" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -7406,13 +7730,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>520</v>
+        <v>628</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>521</v>
+        <v>629</v>
       </c>
       <c r="F44" t="s">
         <v>233</v>
@@ -7421,7 +7745,7 @@
         <v>232</v>
       </c>
       <c r="H44" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -7432,13 +7756,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>522</v>
+        <v>630</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>523</v>
+        <v>631</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -7447,7 +7771,7 @@
         <v>232</v>
       </c>
       <c r="H45" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -7458,13 +7782,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>524</v>
+        <v>632</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>525</v>
+        <v>633</v>
       </c>
       <c r="F46" t="s">
         <v>233</v>
@@ -7473,7 +7797,7 @@
         <v>232</v>
       </c>
       <c r="H46" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -7484,13 +7808,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>526</v>
+        <v>634</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>527</v>
+        <v>635</v>
       </c>
       <c r="F47" t="s">
         <v>233</v>
@@ -7499,7 +7823,7 @@
         <v>232</v>
       </c>
       <c r="H47" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -7510,13 +7834,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>528</v>
+        <v>636</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>529</v>
+        <v>637</v>
       </c>
       <c r="F48" t="s">
         <v>233</v>
@@ -7525,7 +7849,7 @@
         <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -7536,13 +7860,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>530</v>
+        <v>638</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>531</v>
+        <v>639</v>
       </c>
       <c r="F49" t="s">
         <v>233</v>
@@ -7551,7 +7875,7 @@
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -7562,13 +7886,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>532</v>
+        <v>640</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>533</v>
+        <v>641</v>
       </c>
       <c r="F50" t="s">
         <v>233</v>
@@ -7577,7 +7901,7 @@
         <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -7588,13 +7912,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>534</v>
+        <v>642</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>535</v>
+        <v>643</v>
       </c>
       <c r="F51" t="s">
         <v>233</v>
@@ -7603,7 +7927,7 @@
         <v>232</v>
       </c>
       <c r="H51" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -7614,13 +7938,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>536</v>
+        <v>644</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>537</v>
+        <v>645</v>
       </c>
       <c r="F52" t="s">
         <v>233</v>
@@ -7629,7 +7953,7 @@
         <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -7641,13 +7965,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3926DF71-5F25-44C0-A9CC-C9C5B2407FD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BEF2B2B-4E39-4BCD-9FDD-0D4D7604889F}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>344</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -7681,13 +8005,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>453</v>
       </c>
       <c r="D5" t="s">
         <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>346</v>
+        <v>454</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -7696,7 +8020,7 @@
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I5" t="s">
         <v>247</v>
@@ -7707,13 +8031,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>348</v>
+        <v>456</v>
       </c>
       <c r="D6" t="s">
         <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>349</v>
+        <v>457</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -7722,7 +8046,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I6" t="s">
         <v>247</v>
@@ -7733,13 +8057,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>350</v>
+        <v>458</v>
       </c>
       <c r="D7" t="s">
         <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>351</v>
+        <v>459</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -7748,7 +8072,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I7" t="s">
         <v>247</v>
@@ -7759,13 +8083,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>352</v>
+        <v>460</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>353</v>
+        <v>461</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -7774,7 +8098,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I8" t="s">
         <v>247</v>
@@ -7785,13 +8109,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>354</v>
+        <v>462</v>
       </c>
       <c r="D9" t="s">
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>355</v>
+        <v>463</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -7800,7 +8124,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I9" t="s">
         <v>247</v>
@@ -7811,13 +8135,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>356</v>
+        <v>464</v>
       </c>
       <c r="D10" t="s">
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>357</v>
+        <v>465</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -7826,7 +8150,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I10" t="s">
         <v>247</v>
@@ -7837,13 +8161,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>466</v>
       </c>
       <c r="D11" t="s">
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>359</v>
+        <v>467</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -7852,7 +8176,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I11" t="s">
         <v>247</v>
@@ -7863,13 +8187,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>360</v>
+        <v>468</v>
       </c>
       <c r="D12" t="s">
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>361</v>
+        <v>469</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -7878,7 +8202,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I12" t="s">
         <v>247</v>
@@ -7889,13 +8213,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>470</v>
       </c>
       <c r="D13" t="s">
         <v>243</v>
       </c>
       <c r="E13" t="s">
-        <v>363</v>
+        <v>471</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -7904,7 +8228,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I13" t="s">
         <v>247</v>
@@ -7915,13 +8239,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>364</v>
+        <v>472</v>
       </c>
       <c r="D14" t="s">
         <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>365</v>
+        <v>473</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -7930,7 +8254,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I14" t="s">
         <v>247</v>
@@ -7941,13 +8265,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>366</v>
+        <v>474</v>
       </c>
       <c r="D15" t="s">
         <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>367</v>
+        <v>475</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -7956,7 +8280,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I15" t="s">
         <v>247</v>
@@ -7967,13 +8291,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>368</v>
+        <v>476</v>
       </c>
       <c r="D16" t="s">
         <v>243</v>
       </c>
       <c r="E16" t="s">
-        <v>369</v>
+        <v>477</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -7982,7 +8306,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I16" t="s">
         <v>247</v>
@@ -7993,13 +8317,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>370</v>
+        <v>478</v>
       </c>
       <c r="D17" t="s">
         <v>243</v>
       </c>
       <c r="E17" t="s">
-        <v>371</v>
+        <v>479</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -8008,7 +8332,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I17" t="s">
         <v>247</v>
@@ -8019,13 +8343,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>372</v>
+        <v>480</v>
       </c>
       <c r="D18" t="s">
         <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>373</v>
+        <v>481</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -8034,7 +8358,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I18" t="s">
         <v>247</v>
@@ -8045,13 +8369,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>374</v>
+        <v>482</v>
       </c>
       <c r="D19" t="s">
         <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>375</v>
+        <v>483</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -8060,7 +8384,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I19" t="s">
         <v>247</v>
@@ -8071,13 +8395,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>484</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>377</v>
+        <v>485</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -8086,7 +8410,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I20" t="s">
         <v>247</v>
@@ -8097,13 +8421,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>378</v>
+        <v>486</v>
       </c>
       <c r="D21" t="s">
         <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -8112,7 +8436,7 @@
         <v>35</v>
       </c>
       <c r="H21" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I21" t="s">
         <v>247</v>
@@ -8123,13 +8447,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>380</v>
+        <v>488</v>
       </c>
       <c r="D22" t="s">
         <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>381</v>
+        <v>489</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
@@ -8138,7 +8462,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I22" t="s">
         <v>247</v>
@@ -8149,13 +8473,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>382</v>
+        <v>490</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>383</v>
+        <v>491</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
@@ -8164,7 +8488,7 @@
         <v>35</v>
       </c>
       <c r="H23" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I23" t="s">
         <v>247</v>
@@ -8175,13 +8499,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>384</v>
+        <v>492</v>
       </c>
       <c r="D24" t="s">
         <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>385</v>
+        <v>493</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
@@ -8190,7 +8514,7 @@
         <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I24" t="s">
         <v>247</v>
@@ -8201,13 +8525,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>386</v>
+        <v>494</v>
       </c>
       <c r="D25" t="s">
         <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>387</v>
+        <v>495</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
@@ -8216,7 +8540,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I25" t="s">
         <v>247</v>
@@ -8227,13 +8551,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>388</v>
+        <v>496</v>
       </c>
       <c r="D26" t="s">
         <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>389</v>
+        <v>497</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
@@ -8242,7 +8566,7 @@
         <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I26" t="s">
         <v>247</v>
@@ -8253,13 +8577,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>390</v>
+        <v>498</v>
       </c>
       <c r="D27" t="s">
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>391</v>
+        <v>499</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
@@ -8268,7 +8592,7 @@
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I27" t="s">
         <v>247</v>
@@ -8279,13 +8603,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>392</v>
+        <v>500</v>
       </c>
       <c r="D28" t="s">
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>393</v>
+        <v>501</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
@@ -8294,7 +8618,7 @@
         <v>35</v>
       </c>
       <c r="H28" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I28" t="s">
         <v>247</v>
@@ -8305,13 +8629,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>394</v>
+        <v>502</v>
       </c>
       <c r="D29" t="s">
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>395</v>
+        <v>503</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
@@ -8320,7 +8644,7 @@
         <v>35</v>
       </c>
       <c r="H29" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I29" t="s">
         <v>247</v>
@@ -8331,13 +8655,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>396</v>
+        <v>504</v>
       </c>
       <c r="D30" t="s">
         <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>397</v>
+        <v>505</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
@@ -8346,7 +8670,7 @@
         <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I30" t="s">
         <v>247</v>
@@ -8357,13 +8681,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>398</v>
+        <v>506</v>
       </c>
       <c r="D31" t="s">
         <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>399</v>
+        <v>507</v>
       </c>
       <c r="F31" t="s">
         <v>25</v>
@@ -8372,7 +8696,7 @@
         <v>35</v>
       </c>
       <c r="H31" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I31" t="s">
         <v>247</v>
@@ -8383,13 +8707,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>400</v>
+        <v>508</v>
       </c>
       <c r="D32" t="s">
         <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>401</v>
+        <v>509</v>
       </c>
       <c r="F32" t="s">
         <v>25</v>
@@ -8398,7 +8722,7 @@
         <v>35</v>
       </c>
       <c r="H32" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I32" t="s">
         <v>247</v>
@@ -8409,13 +8733,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>402</v>
+        <v>510</v>
       </c>
       <c r="D33" t="s">
         <v>243</v>
       </c>
       <c r="E33" t="s">
-        <v>403</v>
+        <v>511</v>
       </c>
       <c r="F33" t="s">
         <v>25</v>
@@ -8424,7 +8748,7 @@
         <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I33" t="s">
         <v>247</v>
@@ -8435,13 +8759,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>404</v>
+        <v>512</v>
       </c>
       <c r="D34" t="s">
         <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>405</v>
+        <v>513</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -8450,7 +8774,7 @@
         <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I34" t="s">
         <v>247</v>
@@ -8461,13 +8785,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>406</v>
+        <v>514</v>
       </c>
       <c r="D35" t="s">
         <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>407</v>
+        <v>515</v>
       </c>
       <c r="F35" t="s">
         <v>25</v>
@@ -8476,7 +8800,7 @@
         <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I35" t="s">
         <v>247</v>
@@ -8487,13 +8811,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>408</v>
+        <v>516</v>
       </c>
       <c r="D36" t="s">
         <v>243</v>
       </c>
       <c r="E36" t="s">
-        <v>409</v>
+        <v>517</v>
       </c>
       <c r="F36" t="s">
         <v>25</v>
@@ -8502,7 +8826,7 @@
         <v>35</v>
       </c>
       <c r="H36" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I36" t="s">
         <v>247</v>
@@ -8513,13 +8837,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>410</v>
+        <v>518</v>
       </c>
       <c r="D37" t="s">
         <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>411</v>
+        <v>519</v>
       </c>
       <c r="F37" t="s">
         <v>25</v>
@@ -8528,7 +8852,7 @@
         <v>35</v>
       </c>
       <c r="H37" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I37" t="s">
         <v>247</v>
@@ -8539,13 +8863,13 @@
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>412</v>
+        <v>520</v>
       </c>
       <c r="D38" t="s">
         <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>413</v>
+        <v>521</v>
       </c>
       <c r="F38" t="s">
         <v>25</v>
@@ -8554,7 +8878,7 @@
         <v>35</v>
       </c>
       <c r="H38" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I38" t="s">
         <v>247</v>
@@ -8565,13 +8889,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>414</v>
+        <v>522</v>
       </c>
       <c r="D39" t="s">
         <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>415</v>
+        <v>523</v>
       </c>
       <c r="F39" t="s">
         <v>25</v>
@@ -8580,7 +8904,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I39" t="s">
         <v>247</v>
@@ -8591,13 +8915,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>416</v>
+        <v>524</v>
       </c>
       <c r="D40" t="s">
         <v>243</v>
       </c>
       <c r="E40" t="s">
-        <v>417</v>
+        <v>525</v>
       </c>
       <c r="F40" t="s">
         <v>25</v>
@@ -8606,7 +8930,7 @@
         <v>35</v>
       </c>
       <c r="H40" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I40" t="s">
         <v>247</v>
@@ -8617,13 +8941,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>418</v>
+        <v>526</v>
       </c>
       <c r="D41" t="s">
         <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>419</v>
+        <v>527</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -8632,7 +8956,7 @@
         <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I41" t="s">
         <v>247</v>
@@ -8643,13 +8967,13 @@
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>420</v>
+        <v>528</v>
       </c>
       <c r="D42" t="s">
         <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>421</v>
+        <v>529</v>
       </c>
       <c r="F42" t="s">
         <v>25</v>
@@ -8658,7 +8982,7 @@
         <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I42" t="s">
         <v>247</v>
@@ -8669,13 +8993,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>422</v>
+        <v>530</v>
       </c>
       <c r="D43" t="s">
         <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>423</v>
+        <v>531</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
@@ -8684,7 +9008,7 @@
         <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I43" t="s">
         <v>247</v>
@@ -8695,13 +9019,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>424</v>
+        <v>532</v>
       </c>
       <c r="D44" t="s">
         <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>425</v>
+        <v>533</v>
       </c>
       <c r="F44" t="s">
         <v>25</v>
@@ -8710,7 +9034,7 @@
         <v>35</v>
       </c>
       <c r="H44" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I44" t="s">
         <v>247</v>
@@ -8721,13 +9045,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>426</v>
+        <v>534</v>
       </c>
       <c r="D45" t="s">
         <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>427</v>
+        <v>535</v>
       </c>
       <c r="F45" t="s">
         <v>25</v>
@@ -8736,7 +9060,7 @@
         <v>35</v>
       </c>
       <c r="H45" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I45" t="s">
         <v>247</v>
@@ -8747,13 +9071,13 @@
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>428</v>
+        <v>536</v>
       </c>
       <c r="D46" t="s">
         <v>243</v>
       </c>
       <c r="E46" t="s">
-        <v>429</v>
+        <v>537</v>
       </c>
       <c r="F46" t="s">
         <v>25</v>
@@ -8762,7 +9086,7 @@
         <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I46" t="s">
         <v>247</v>
@@ -8773,13 +9097,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>430</v>
+        <v>538</v>
       </c>
       <c r="D47" t="s">
         <v>243</v>
       </c>
       <c r="E47" t="s">
-        <v>431</v>
+        <v>539</v>
       </c>
       <c r="F47" t="s">
         <v>25</v>
@@ -8788,7 +9112,7 @@
         <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I47" t="s">
         <v>247</v>
@@ -8799,13 +9123,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>432</v>
+        <v>540</v>
       </c>
       <c r="D48" t="s">
         <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>433</v>
+        <v>541</v>
       </c>
       <c r="F48" t="s">
         <v>25</v>
@@ -8814,7 +9138,7 @@
         <v>35</v>
       </c>
       <c r="H48" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I48" t="s">
         <v>247</v>
@@ -8825,13 +9149,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>434</v>
+        <v>542</v>
       </c>
       <c r="D49" t="s">
         <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>435</v>
+        <v>543</v>
       </c>
       <c r="F49" t="s">
         <v>25</v>
@@ -8840,7 +9164,7 @@
         <v>35</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I49" t="s">
         <v>247</v>
@@ -8851,13 +9175,13 @@
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>436</v>
+        <v>544</v>
       </c>
       <c r="D50" t="s">
         <v>243</v>
       </c>
       <c r="E50" t="s">
-        <v>437</v>
+        <v>545</v>
       </c>
       <c r="F50" t="s">
         <v>25</v>
@@ -8866,7 +9190,7 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I50" t="s">
         <v>247</v>
@@ -8877,13 +9201,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>438</v>
+        <v>546</v>
       </c>
       <c r="D51" t="s">
         <v>243</v>
       </c>
       <c r="E51" t="s">
-        <v>439</v>
+        <v>547</v>
       </c>
       <c r="F51" t="s">
         <v>25</v>
@@ -8892,7 +9216,7 @@
         <v>35</v>
       </c>
       <c r="H51" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I51" t="s">
         <v>247</v>
@@ -8903,13 +9227,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>440</v>
+        <v>548</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>441</v>
+        <v>549</v>
       </c>
       <c r="F52" t="s">
         <v>25</v>
@@ -8918,7 +9242,7 @@
         <v>35</v>
       </c>
       <c r="H52" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="I52" t="s">
         <v>247</v>
@@ -8931,7 +9255,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S53"/>
+  <dimension ref="B3:S107"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -10519,6 +10843,1248 @@
         <v>35</v>
       </c>
       <c r="S53" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="13:19">
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>344</v>
+      </c>
+      <c r="O54" t="s">
+        <v>243</v>
+      </c>
+      <c r="P54" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>25</v>
+      </c>
+      <c r="R54" t="s">
+        <v>35</v>
+      </c>
+      <c r="S54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="13:19">
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>346</v>
+      </c>
+      <c r="O55" t="s">
+        <v>243</v>
+      </c>
+      <c r="P55" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>25</v>
+      </c>
+      <c r="R55" t="s">
+        <v>35</v>
+      </c>
+      <c r="S55" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="13:19">
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>348</v>
+      </c>
+      <c r="O56" t="s">
+        <v>243</v>
+      </c>
+      <c r="P56" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>25</v>
+      </c>
+      <c r="R56" t="s">
+        <v>35</v>
+      </c>
+      <c r="S56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="13:19">
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>350</v>
+      </c>
+      <c r="O57" t="s">
+        <v>243</v>
+      </c>
+      <c r="P57" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>25</v>
+      </c>
+      <c r="R57" t="s">
+        <v>35</v>
+      </c>
+      <c r="S57" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="13:19">
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>352</v>
+      </c>
+      <c r="O58" t="s">
+        <v>243</v>
+      </c>
+      <c r="P58" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>25</v>
+      </c>
+      <c r="R58" t="s">
+        <v>35</v>
+      </c>
+      <c r="S58" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="13:19">
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>354</v>
+      </c>
+      <c r="O59" t="s">
+        <v>243</v>
+      </c>
+      <c r="P59" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>25</v>
+      </c>
+      <c r="R59" t="s">
+        <v>35</v>
+      </c>
+      <c r="S59" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="13:19">
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>356</v>
+      </c>
+      <c r="O60" t="s">
+        <v>243</v>
+      </c>
+      <c r="P60" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>25</v>
+      </c>
+      <c r="R60" t="s">
+        <v>35</v>
+      </c>
+      <c r="S60" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="13:19">
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>358</v>
+      </c>
+      <c r="O61" t="s">
+        <v>243</v>
+      </c>
+      <c r="P61" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>25</v>
+      </c>
+      <c r="R61" t="s">
+        <v>35</v>
+      </c>
+      <c r="S61" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="62" spans="13:19">
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>360</v>
+      </c>
+      <c r="O62" t="s">
+        <v>243</v>
+      </c>
+      <c r="P62" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>25</v>
+      </c>
+      <c r="R62" t="s">
+        <v>35</v>
+      </c>
+      <c r="S62" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="63" spans="13:19">
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>362</v>
+      </c>
+      <c r="O63" t="s">
+        <v>243</v>
+      </c>
+      <c r="P63" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>25</v>
+      </c>
+      <c r="R63" t="s">
+        <v>35</v>
+      </c>
+      <c r="S63" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="64" spans="13:19">
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>364</v>
+      </c>
+      <c r="O64" t="s">
+        <v>243</v>
+      </c>
+      <c r="P64" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>25</v>
+      </c>
+      <c r="R64" t="s">
+        <v>35</v>
+      </c>
+      <c r="S64" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="65" spans="13:19">
+      <c r="M65" t="s">
+        <v>17</v>
+      </c>
+      <c r="N65" t="s">
+        <v>366</v>
+      </c>
+      <c r="O65" t="s">
+        <v>243</v>
+      </c>
+      <c r="P65" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>25</v>
+      </c>
+      <c r="R65" t="s">
+        <v>35</v>
+      </c>
+      <c r="S65" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" spans="13:19">
+      <c r="M66" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" t="s">
+        <v>368</v>
+      </c>
+      <c r="O66" t="s">
+        <v>243</v>
+      </c>
+      <c r="P66" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>25</v>
+      </c>
+      <c r="R66" t="s">
+        <v>35</v>
+      </c>
+      <c r="S66" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="67" spans="13:19">
+      <c r="M67" t="s">
+        <v>17</v>
+      </c>
+      <c r="N67" t="s">
+        <v>370</v>
+      </c>
+      <c r="O67" t="s">
+        <v>243</v>
+      </c>
+      <c r="P67" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>25</v>
+      </c>
+      <c r="R67" t="s">
+        <v>35</v>
+      </c>
+      <c r="S67" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="68" spans="13:19">
+      <c r="M68" t="s">
+        <v>17</v>
+      </c>
+      <c r="N68" t="s">
+        <v>372</v>
+      </c>
+      <c r="O68" t="s">
+        <v>243</v>
+      </c>
+      <c r="P68" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>25</v>
+      </c>
+      <c r="R68" t="s">
+        <v>35</v>
+      </c>
+      <c r="S68" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="69" spans="13:19">
+      <c r="M69" t="s">
+        <v>17</v>
+      </c>
+      <c r="N69" t="s">
+        <v>374</v>
+      </c>
+      <c r="O69" t="s">
+        <v>243</v>
+      </c>
+      <c r="P69" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>25</v>
+      </c>
+      <c r="R69" t="s">
+        <v>35</v>
+      </c>
+      <c r="S69" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="70" spans="13:19">
+      <c r="M70" t="s">
+        <v>17</v>
+      </c>
+      <c r="N70" t="s">
+        <v>376</v>
+      </c>
+      <c r="O70" t="s">
+        <v>243</v>
+      </c>
+      <c r="P70" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>25</v>
+      </c>
+      <c r="R70" t="s">
+        <v>35</v>
+      </c>
+      <c r="S70" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="71" spans="13:19">
+      <c r="M71" t="s">
+        <v>17</v>
+      </c>
+      <c r="N71" t="s">
+        <v>378</v>
+      </c>
+      <c r="O71" t="s">
+        <v>243</v>
+      </c>
+      <c r="P71" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>25</v>
+      </c>
+      <c r="R71" t="s">
+        <v>35</v>
+      </c>
+      <c r="S71" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="72" spans="13:19">
+      <c r="M72" t="s">
+        <v>17</v>
+      </c>
+      <c r="N72" t="s">
+        <v>380</v>
+      </c>
+      <c r="O72" t="s">
+        <v>243</v>
+      </c>
+      <c r="P72" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>25</v>
+      </c>
+      <c r="R72" t="s">
+        <v>35</v>
+      </c>
+      <c r="S72" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="73" spans="13:19">
+      <c r="M73" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73" t="s">
+        <v>382</v>
+      </c>
+      <c r="O73" t="s">
+        <v>243</v>
+      </c>
+      <c r="P73" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>25</v>
+      </c>
+      <c r="R73" t="s">
+        <v>35</v>
+      </c>
+      <c r="S73" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="74" spans="13:19">
+      <c r="M74" t="s">
+        <v>17</v>
+      </c>
+      <c r="N74" t="s">
+        <v>384</v>
+      </c>
+      <c r="O74" t="s">
+        <v>243</v>
+      </c>
+      <c r="P74" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>25</v>
+      </c>
+      <c r="R74" t="s">
+        <v>35</v>
+      </c>
+      <c r="S74" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75" spans="13:19">
+      <c r="M75" t="s">
+        <v>17</v>
+      </c>
+      <c r="N75" t="s">
+        <v>386</v>
+      </c>
+      <c r="O75" t="s">
+        <v>243</v>
+      </c>
+      <c r="P75" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>25</v>
+      </c>
+      <c r="R75" t="s">
+        <v>35</v>
+      </c>
+      <c r="S75" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="76" spans="13:19">
+      <c r="M76" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" t="s">
+        <v>388</v>
+      </c>
+      <c r="O76" t="s">
+        <v>243</v>
+      </c>
+      <c r="P76" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>25</v>
+      </c>
+      <c r="R76" t="s">
+        <v>35</v>
+      </c>
+      <c r="S76" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="13:19">
+      <c r="M77" t="s">
+        <v>17</v>
+      </c>
+      <c r="N77" t="s">
+        <v>390</v>
+      </c>
+      <c r="O77" t="s">
+        <v>243</v>
+      </c>
+      <c r="P77" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>25</v>
+      </c>
+      <c r="R77" t="s">
+        <v>35</v>
+      </c>
+      <c r="S77" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="78" spans="13:19">
+      <c r="M78" t="s">
+        <v>17</v>
+      </c>
+      <c r="N78" t="s">
+        <v>392</v>
+      </c>
+      <c r="O78" t="s">
+        <v>243</v>
+      </c>
+      <c r="P78" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>25</v>
+      </c>
+      <c r="R78" t="s">
+        <v>35</v>
+      </c>
+      <c r="S78" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="79" spans="13:19">
+      <c r="M79" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79" t="s">
+        <v>394</v>
+      </c>
+      <c r="O79" t="s">
+        <v>243</v>
+      </c>
+      <c r="P79" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>25</v>
+      </c>
+      <c r="R79" t="s">
+        <v>35</v>
+      </c>
+      <c r="S79" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="80" spans="13:19">
+      <c r="M80" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80" t="s">
+        <v>396</v>
+      </c>
+      <c r="O80" t="s">
+        <v>243</v>
+      </c>
+      <c r="P80" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>25</v>
+      </c>
+      <c r="R80" t="s">
+        <v>35</v>
+      </c>
+      <c r="S80" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81" spans="13:19">
+      <c r="M81" t="s">
+        <v>17</v>
+      </c>
+      <c r="N81" t="s">
+        <v>398</v>
+      </c>
+      <c r="O81" t="s">
+        <v>243</v>
+      </c>
+      <c r="P81" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>25</v>
+      </c>
+      <c r="R81" t="s">
+        <v>35</v>
+      </c>
+      <c r="S81" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="82" spans="13:19">
+      <c r="M82" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82" t="s">
+        <v>400</v>
+      </c>
+      <c r="O82" t="s">
+        <v>243</v>
+      </c>
+      <c r="P82" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>25</v>
+      </c>
+      <c r="R82" t="s">
+        <v>35</v>
+      </c>
+      <c r="S82" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="83" spans="13:19">
+      <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" t="s">
+        <v>402</v>
+      </c>
+      <c r="O83" t="s">
+        <v>243</v>
+      </c>
+      <c r="P83" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>25</v>
+      </c>
+      <c r="R83" t="s">
+        <v>35</v>
+      </c>
+      <c r="S83" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="84" spans="13:19">
+      <c r="M84" t="s">
+        <v>17</v>
+      </c>
+      <c r="N84" t="s">
+        <v>404</v>
+      </c>
+      <c r="O84" t="s">
+        <v>243</v>
+      </c>
+      <c r="P84" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>25</v>
+      </c>
+      <c r="R84" t="s">
+        <v>35</v>
+      </c>
+      <c r="S84" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="85" spans="13:19">
+      <c r="M85" t="s">
+        <v>17</v>
+      </c>
+      <c r="N85" t="s">
+        <v>406</v>
+      </c>
+      <c r="O85" t="s">
+        <v>243</v>
+      </c>
+      <c r="P85" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>25</v>
+      </c>
+      <c r="R85" t="s">
+        <v>35</v>
+      </c>
+      <c r="S85" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="86" spans="13:19">
+      <c r="M86" t="s">
+        <v>17</v>
+      </c>
+      <c r="N86" t="s">
+        <v>408</v>
+      </c>
+      <c r="O86" t="s">
+        <v>243</v>
+      </c>
+      <c r="P86" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>25</v>
+      </c>
+      <c r="R86" t="s">
+        <v>35</v>
+      </c>
+      <c r="S86" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="87" spans="13:19">
+      <c r="M87" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" t="s">
+        <v>410</v>
+      </c>
+      <c r="O87" t="s">
+        <v>243</v>
+      </c>
+      <c r="P87" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>25</v>
+      </c>
+      <c r="R87" t="s">
+        <v>35</v>
+      </c>
+      <c r="S87" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="88" spans="13:19">
+      <c r="M88" t="s">
+        <v>17</v>
+      </c>
+      <c r="N88" t="s">
+        <v>412</v>
+      </c>
+      <c r="O88" t="s">
+        <v>243</v>
+      </c>
+      <c r="P88" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>25</v>
+      </c>
+      <c r="R88" t="s">
+        <v>35</v>
+      </c>
+      <c r="S88" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="89" spans="13:19">
+      <c r="M89" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>414</v>
+      </c>
+      <c r="O89" t="s">
+        <v>243</v>
+      </c>
+      <c r="P89" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>25</v>
+      </c>
+      <c r="R89" t="s">
+        <v>35</v>
+      </c>
+      <c r="S89" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="90" spans="13:19">
+      <c r="M90" t="s">
+        <v>17</v>
+      </c>
+      <c r="N90" t="s">
+        <v>416</v>
+      </c>
+      <c r="O90" t="s">
+        <v>243</v>
+      </c>
+      <c r="P90" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>25</v>
+      </c>
+      <c r="R90" t="s">
+        <v>35</v>
+      </c>
+      <c r="S90" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="91" spans="13:19">
+      <c r="M91" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91" t="s">
+        <v>418</v>
+      </c>
+      <c r="O91" t="s">
+        <v>243</v>
+      </c>
+      <c r="P91" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>25</v>
+      </c>
+      <c r="R91" t="s">
+        <v>35</v>
+      </c>
+      <c r="S91" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="92" spans="13:19">
+      <c r="M92" t="s">
+        <v>17</v>
+      </c>
+      <c r="N92" t="s">
+        <v>420</v>
+      </c>
+      <c r="O92" t="s">
+        <v>243</v>
+      </c>
+      <c r="P92" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>25</v>
+      </c>
+      <c r="R92" t="s">
+        <v>35</v>
+      </c>
+      <c r="S92" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="93" spans="13:19">
+      <c r="M93" t="s">
+        <v>17</v>
+      </c>
+      <c r="N93" t="s">
+        <v>422</v>
+      </c>
+      <c r="O93" t="s">
+        <v>243</v>
+      </c>
+      <c r="P93" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>25</v>
+      </c>
+      <c r="R93" t="s">
+        <v>35</v>
+      </c>
+      <c r="S93" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="94" spans="13:19">
+      <c r="M94" t="s">
+        <v>17</v>
+      </c>
+      <c r="N94" t="s">
+        <v>424</v>
+      </c>
+      <c r="O94" t="s">
+        <v>243</v>
+      </c>
+      <c r="P94" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>25</v>
+      </c>
+      <c r="R94" t="s">
+        <v>35</v>
+      </c>
+      <c r="S94" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="95" spans="13:19">
+      <c r="M95" t="s">
+        <v>17</v>
+      </c>
+      <c r="N95" t="s">
+        <v>426</v>
+      </c>
+      <c r="O95" t="s">
+        <v>243</v>
+      </c>
+      <c r="P95" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>25</v>
+      </c>
+      <c r="R95" t="s">
+        <v>35</v>
+      </c>
+      <c r="S95" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="96" spans="13:19">
+      <c r="M96" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" t="s">
+        <v>428</v>
+      </c>
+      <c r="O96" t="s">
+        <v>243</v>
+      </c>
+      <c r="P96" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>25</v>
+      </c>
+      <c r="R96" t="s">
+        <v>35</v>
+      </c>
+      <c r="S96" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="97" spans="13:19">
+      <c r="M97" t="s">
+        <v>17</v>
+      </c>
+      <c r="N97" t="s">
+        <v>430</v>
+      </c>
+      <c r="O97" t="s">
+        <v>243</v>
+      </c>
+      <c r="P97" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>25</v>
+      </c>
+      <c r="R97" t="s">
+        <v>35</v>
+      </c>
+      <c r="S97" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="98" spans="13:19">
+      <c r="M98" t="s">
+        <v>17</v>
+      </c>
+      <c r="N98" t="s">
+        <v>432</v>
+      </c>
+      <c r="O98" t="s">
+        <v>243</v>
+      </c>
+      <c r="P98" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>25</v>
+      </c>
+      <c r="R98" t="s">
+        <v>35</v>
+      </c>
+      <c r="S98" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="99" spans="13:19">
+      <c r="M99" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" t="s">
+        <v>434</v>
+      </c>
+      <c r="O99" t="s">
+        <v>243</v>
+      </c>
+      <c r="P99" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>25</v>
+      </c>
+      <c r="R99" t="s">
+        <v>35</v>
+      </c>
+      <c r="S99" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="100" spans="13:19">
+      <c r="M100" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" t="s">
+        <v>436</v>
+      </c>
+      <c r="O100" t="s">
+        <v>243</v>
+      </c>
+      <c r="P100" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>25</v>
+      </c>
+      <c r="R100" t="s">
+        <v>35</v>
+      </c>
+      <c r="S100" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="101" spans="13:19">
+      <c r="M101" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" t="s">
+        <v>438</v>
+      </c>
+      <c r="O101" t="s">
+        <v>243</v>
+      </c>
+      <c r="P101" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>25</v>
+      </c>
+      <c r="R101" t="s">
+        <v>35</v>
+      </c>
+      <c r="S101" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="102" spans="13:19">
+      <c r="M102" t="s">
+        <v>17</v>
+      </c>
+      <c r="N102" t="s">
+        <v>440</v>
+      </c>
+      <c r="O102" t="s">
+        <v>243</v>
+      </c>
+      <c r="P102" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>25</v>
+      </c>
+      <c r="R102" t="s">
+        <v>35</v>
+      </c>
+      <c r="S102" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="103" spans="13:19">
+      <c r="M103" t="s">
+        <v>17</v>
+      </c>
+      <c r="N103" t="s">
+        <v>442</v>
+      </c>
+      <c r="O103" t="s">
+        <v>243</v>
+      </c>
+      <c r="P103" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>25</v>
+      </c>
+      <c r="R103" t="s">
+        <v>35</v>
+      </c>
+      <c r="S103" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="104" spans="13:19">
+      <c r="M104" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" t="s">
+        <v>444</v>
+      </c>
+      <c r="O104" t="s">
+        <v>243</v>
+      </c>
+      <c r="P104" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>25</v>
+      </c>
+      <c r="R104" t="s">
+        <v>35</v>
+      </c>
+      <c r="S104" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="105" spans="13:19">
+      <c r="M105" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" t="s">
+        <v>446</v>
+      </c>
+      <c r="O105" t="s">
+        <v>243</v>
+      </c>
+      <c r="P105" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>25</v>
+      </c>
+      <c r="R105" t="s">
+        <v>35</v>
+      </c>
+      <c r="S105" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="106" spans="13:19">
+      <c r="M106" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" t="s">
+        <v>448</v>
+      </c>
+      <c r="O106" t="s">
+        <v>243</v>
+      </c>
+      <c r="P106" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>25</v>
+      </c>
+      <c r="R106" t="s">
+        <v>35</v>
+      </c>
+      <c r="S106" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="107" spans="13:19">
+      <c r="M107" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" t="s">
+        <v>450</v>
+      </c>
+      <c r="O107" t="s">
+        <v>243</v>
+      </c>
+      <c r="P107" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>25</v>
+      </c>
+      <c r="R107" t="s">
+        <v>35</v>
+      </c>
+      <c r="S107" t="s">
         <v>247</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6452122F-E617-4C2C-9417-032CBF1102EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D132E7B6-90EB-42E2-B216-D607FBFE2513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4844,7 +4844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998A17F4-64D4-494F-B45A-8E188B4FDBBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F7B196-FB77-4156-A72F-6197B3013C84}">
   <dimension ref="B3:H82"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6676,7 +6676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C211FDF-42D1-40C2-B89C-5BB2729B9EEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88C1B4F-C4AD-47BE-9F7D-63B8ADA6B425}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7965,7 +7965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BEF2B2B-4E39-4BCD-9FDD-0D4D7604889F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D5B8311-A7E9-42EF-B49B-10C96D5F9BB3}">
   <dimension ref="B3:I52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
